--- a/skills/wbs-generator/template/WBS_template.xlsx
+++ b/skills/wbs-generator/template/WBS_template.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="표지" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="사용안내" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="WBS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="공휴일" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="요약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="WBS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="공휴일" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="HOLIDAYS">#REF!</definedName>
-    <definedName name="HOLIDAYS" localSheetId="2">#REF!</definedName>
+    <definedName name="HOLIDAYS" localSheetId="3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -822,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1203,6 +1204,10 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1359,9 +1364,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29817,7 +29819,7 @@
     <row r="4">
       <c r="B4" s="135" t="inlineStr">
         <is>
-          <t>프로젝트 작업분해구조(WBS)입니다. 시트 구성: 표지 · WBS · 공휴일 · 사용안내</t>
+          <t>프로젝트 작업분해구조(WBS)입니다. 시트 구성: 표지 · 사용안내 · 요약 · WBS · 공휴일</t>
         </is>
       </c>
     </row>
@@ -29975,6 +29977,61 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="104" min="1" max="1"/>
+    <col width="26" customWidth="1" style="104" min="2" max="2"/>
+    <col width="12" customWidth="1" style="104" min="3" max="3"/>
+    <col width="10" customWidth="1" style="104" min="4" max="4"/>
+    <col width="10" customWidth="1" style="104" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="138" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="139" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B3" s="139" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C3" s="139" t="inlineStr">
+        <is>
+          <t>목표진척율</t>
+        </is>
+      </c>
+      <c r="D3" s="139" t="inlineStr">
+        <is>
+          <t>진척율</t>
+        </is>
+      </c>
+      <c r="E3" s="139" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30396,7 +30453,7 @@
       <c r="M1" s="12" t="n"/>
       <c r="N1" s="12" t="n"/>
       <c r="O1" s="12" t="n"/>
-      <c r="P1" s="138" t="n"/>
+      <c r="P1" s="140" t="n"/>
       <c r="Q1" s="12" t="n"/>
       <c r="R1" s="12" t="n"/>
       <c r="S1" s="12" t="n"/>
@@ -30540,13 +30597,13 @@
       <c r="M2" s="13" t="n"/>
       <c r="N2" s="13" t="n"/>
       <c r="O2" s="13" t="n"/>
-      <c r="P2" s="139" t="n"/>
+      <c r="P2" s="141" t="n"/>
       <c r="Q2" s="13" t="n"/>
       <c r="R2" s="13" t="n"/>
       <c r="S2" s="13" t="n"/>
       <c r="T2" s="13" t="n"/>
       <c r="U2" s="13" t="n"/>
-      <c r="V2" s="140" t="n"/>
+      <c r="V2" s="142" t="n"/>
       <c r="W2" s="14" t="n"/>
       <c r="X2" s="14" t="n"/>
       <c r="Y2" s="14" t="n"/>
@@ -30681,42 +30738,42 @@
           <t>시작일</t>
         </is>
       </c>
-      <c r="M3" s="141" t="n"/>
+      <c r="M3" s="143" t="n"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t>종료일</t>
         </is>
       </c>
-      <c r="R3" s="141" t="n"/>
+      <c r="R3" s="143" t="n"/>
       <c r="S3" s="21" t="inlineStr">
         <is>
           <t>기준일</t>
         </is>
       </c>
-      <c r="T3" s="142" t="n"/>
-      <c r="V3" s="143" t="n"/>
-      <c r="W3" s="144" t="inlineStr">
+      <c r="T3" s="144" t="n"/>
+      <c r="V3" s="145" t="n"/>
+      <c r="W3" s="146" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
       </c>
-      <c r="Y3" s="145" t="n"/>
-      <c r="AB3" s="146" t="n"/>
-      <c r="AC3" s="144" t="inlineStr">
+      <c r="Y3" s="147" t="n"/>
+      <c r="AB3" s="148" t="n"/>
+      <c r="AC3" s="146" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="AE3" s="145" t="n"/>
-      <c r="AH3" s="147" t="n"/>
-      <c r="AI3" s="144" t="inlineStr">
+      <c r="AE3" s="147" t="n"/>
+      <c r="AH3" s="149" t="n"/>
+      <c r="AI3" s="146" t="inlineStr">
         <is>
           <t>잔여</t>
         </is>
       </c>
-      <c r="AK3" s="148" t="n"/>
-      <c r="AN3" s="149" t="n"/>
-      <c r="AO3" s="144" t="inlineStr">
+      <c r="AK3" s="150" t="n"/>
+      <c r="AN3" s="151" t="n"/>
+      <c r="AO3" s="146" t="inlineStr">
         <is>
           <t>대기</t>
         </is>
@@ -30724,8 +30781,8 @@
       <c r="AQ3" s="14" t="n"/>
       <c r="AR3" s="14" t="n"/>
       <c r="AS3" s="14" t="n"/>
-      <c r="AT3" s="150" t="n"/>
-      <c r="AU3" s="144" t="inlineStr">
+      <c r="AT3" s="152" t="n"/>
+      <c r="AU3" s="146" t="inlineStr">
         <is>
           <t>보류</t>
         </is>
@@ -30734,8 +30791,8 @@
       <c r="AW3" s="14" t="n"/>
       <c r="AX3" s="14" t="n"/>
       <c r="AY3" s="14" t="n"/>
-      <c r="AZ3" s="151" t="n"/>
-      <c r="BA3" s="144" t="inlineStr">
+      <c r="AZ3" s="153" t="n"/>
+      <c r="BA3" s="146" t="inlineStr">
         <is>
           <t>주말/공휴일</t>
         </is>
@@ -30744,8 +30801,8 @@
       <c r="BC3" s="14" t="n"/>
       <c r="BD3" s="14" t="n"/>
       <c r="BE3" s="14" t="n"/>
-      <c r="BF3" s="152" t="n"/>
-      <c r="BG3" s="144" t="inlineStr">
+      <c r="BF3" s="154" t="n"/>
+      <c r="BG3" s="146" t="inlineStr">
         <is>
           <t>기준일</t>
         </is>
@@ -30837,8 +30894,8 @@
     </row>
     <row r="4" ht="14.25" customHeight="1" s="104">
       <c r="A4" s="24" t="n"/>
-      <c r="B4" s="153" t="n"/>
-      <c r="C4" s="153" t="n"/>
+      <c r="B4" s="155" t="n"/>
+      <c r="C4" s="155" t="n"/>
       <c r="D4" s="24" t="n"/>
       <c r="E4" s="24" t="n"/>
       <c r="F4" s="24" t="n"/>
@@ -30851,1489 +30908,1489 @@
       <c r="M4" s="24" t="n"/>
       <c r="N4" s="24" t="n"/>
       <c r="O4" s="24" t="n"/>
-      <c r="P4" s="154" t="n"/>
+      <c r="P4" s="156" t="n"/>
       <c r="Q4" s="24" t="n"/>
       <c r="R4" s="24" t="n"/>
       <c r="S4" s="24" t="n"/>
       <c r="T4" s="24" t="n"/>
       <c r="U4" s="123" t="n"/>
-      <c r="V4" s="155">
+      <c r="V4" s="157">
         <f>IF(V5="","",IF(OR(V5=$M$3,DAY(V5)=1),MONTH(V5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="W4" s="156">
+      <c r="W4" s="158">
         <f>IF(W5="","",IF(OR(W5=$M$3,DAY(W5)=1),MONTH(W5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="X4" s="156">
+      <c r="X4" s="158">
         <f>IF(X5="","",IF(OR(X5=$M$3,DAY(X5)=1),MONTH(X5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="Y4" s="156">
+      <c r="Y4" s="158">
         <f>IF(Y5="","",IF(OR(Y5=$M$3,DAY(Y5)=1),MONTH(Y5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="Z4" s="156">
+      <c r="Z4" s="158">
         <f>IF(Z5="","",IF(OR(Z5=$M$3,DAY(Z5)=1),MONTH(Z5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AA4" s="156">
+      <c r="AA4" s="158">
         <f>IF(AA5="","",IF(OR(AA5=$M$3,DAY(AA5)=1),MONTH(AA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AB4" s="156">
+      <c r="AB4" s="158">
         <f>IF(AB5="","",IF(OR(AB5=$M$3,DAY(AB5)=1),MONTH(AB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AC4" s="156">
+      <c r="AC4" s="158">
         <f>IF(AC5="","",IF(OR(AC5=$M$3,DAY(AC5)=1),MONTH(AC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AD4" s="156">
+      <c r="AD4" s="158">
         <f>IF(AD5="","",IF(OR(AD5=$M$3,DAY(AD5)=1),MONTH(AD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AE4" s="156">
+      <c r="AE4" s="158">
         <f>IF(AE5="","",IF(OR(AE5=$M$3,DAY(AE5)=1),MONTH(AE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AF4" s="156">
+      <c r="AF4" s="158">
         <f>IF(AF5="","",IF(OR(AF5=$M$3,DAY(AF5)=1),MONTH(AF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AG4" s="156">
+      <c r="AG4" s="158">
         <f>IF(AG5="","",IF(OR(AG5=$M$3,DAY(AG5)=1),MONTH(AG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AH4" s="156">
+      <c r="AH4" s="158">
         <f>IF(AH5="","",IF(OR(AH5=$M$3,DAY(AH5)=1),MONTH(AH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AI4" s="156">
+      <c r="AI4" s="158">
         <f>IF(AI5="","",IF(OR(AI5=$M$3,DAY(AI5)=1),MONTH(AI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AJ4" s="156">
+      <c r="AJ4" s="158">
         <f>IF(AJ5="","",IF(OR(AJ5=$M$3,DAY(AJ5)=1),MONTH(AJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AK4" s="156">
+      <c r="AK4" s="158">
         <f>IF(AK5="","",IF(OR(AK5=$M$3,DAY(AK5)=1),MONTH(AK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AL4" s="155">
+      <c r="AL4" s="157">
         <f>IF(AL5="","",IF(OR(AL5=$M$3,DAY(AL5)=1),MONTH(AL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AM4" s="156">
+      <c r="AM4" s="158">
         <f>IF(AM5="","",IF(OR(AM5=$M$3,DAY(AM5)=1),MONTH(AM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AN4" s="156">
+      <c r="AN4" s="158">
         <f>IF(AN5="","",IF(OR(AN5=$M$3,DAY(AN5)=1),MONTH(AN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AO4" s="156">
+      <c r="AO4" s="158">
         <f>IF(AO5="","",IF(OR(AO5=$M$3,DAY(AO5)=1),MONTH(AO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AP4" s="156">
+      <c r="AP4" s="158">
         <f>IF(AP5="","",IF(OR(AP5=$M$3,DAY(AP5)=1),MONTH(AP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AQ4" s="156">
+      <c r="AQ4" s="158">
         <f>IF(AQ5="","",IF(OR(AQ5=$M$3,DAY(AQ5)=1),MONTH(AQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AR4" s="156">
+      <c r="AR4" s="158">
         <f>IF(AR5="","",IF(OR(AR5=$M$3,DAY(AR5)=1),MONTH(AR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AS4" s="156">
+      <c r="AS4" s="158">
         <f>IF(AS5="","",IF(OR(AS5=$M$3,DAY(AS5)=1),MONTH(AS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AT4" s="156">
+      <c r="AT4" s="158">
         <f>IF(AT5="","",IF(OR(AT5=$M$3,DAY(AT5)=1),MONTH(AT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AU4" s="156">
+      <c r="AU4" s="158">
         <f>IF(AU5="","",IF(OR(AU5=$M$3,DAY(AU5)=1),MONTH(AU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AV4" s="156">
+      <c r="AV4" s="158">
         <f>IF(AV5="","",IF(OR(AV5=$M$3,DAY(AV5)=1),MONTH(AV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AW4" s="156">
+      <c r="AW4" s="158">
         <f>IF(AW5="","",IF(OR(AW5=$M$3,DAY(AW5)=1),MONTH(AW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AX4" s="156">
+      <c r="AX4" s="158">
         <f>IF(AX5="","",IF(OR(AX5=$M$3,DAY(AX5)=1),MONTH(AX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AY4" s="156">
+      <c r="AY4" s="158">
         <f>IF(AY5="","",IF(OR(AY5=$M$3,DAY(AY5)=1),MONTH(AY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="AZ4" s="156">
+      <c r="AZ4" s="158">
         <f>IF(AZ5="","",IF(OR(AZ5=$M$3,DAY(AZ5)=1),MONTH(AZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BA4" s="156">
+      <c r="BA4" s="158">
         <f>IF(BA5="","",IF(OR(BA5=$M$3,DAY(BA5)=1),MONTH(BA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BB4" s="156">
+      <c r="BB4" s="158">
         <f>IF(BB5="","",IF(OR(BB5=$M$3,DAY(BB5)=1),MONTH(BB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BC4" s="156">
+      <c r="BC4" s="158">
         <f>IF(BC5="","",IF(OR(BC5=$M$3,DAY(BC5)=1),MONTH(BC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BD4" s="156">
+      <c r="BD4" s="158">
         <f>IF(BD5="","",IF(OR(BD5=$M$3,DAY(BD5)=1),MONTH(BD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BE4" s="156">
+      <c r="BE4" s="158">
         <f>IF(BE5="","",IF(OR(BE5=$M$3,DAY(BE5)=1),MONTH(BE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BF4" s="156">
+      <c r="BF4" s="158">
         <f>IF(BF5="","",IF(OR(BF5=$M$3,DAY(BF5)=1),MONTH(BF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BG4" s="156">
+      <c r="BG4" s="158">
         <f>IF(BG5="","",IF(OR(BG5=$M$3,DAY(BG5)=1),MONTH(BG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BH4" s="156">
+      <c r="BH4" s="158">
         <f>IF(BH5="","",IF(OR(BH5=$M$3,DAY(BH5)=1),MONTH(BH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BI4" s="156">
+      <c r="BI4" s="158">
         <f>IF(BI5="","",IF(OR(BI5=$M$3,DAY(BI5)=1),MONTH(BI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BJ4" s="156">
+      <c r="BJ4" s="158">
         <f>IF(BJ5="","",IF(OR(BJ5=$M$3,DAY(BJ5)=1),MONTH(BJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BK4" s="156">
+      <c r="BK4" s="158">
         <f>IF(BK5="","",IF(OR(BK5=$M$3,DAY(BK5)=1),MONTH(BK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BL4" s="156">
+      <c r="BL4" s="158">
         <f>IF(BL5="","",IF(OR(BL5=$M$3,DAY(BL5)=1),MONTH(BL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BM4" s="156">
+      <c r="BM4" s="158">
         <f>IF(BM5="","",IF(OR(BM5=$M$3,DAY(BM5)=1),MONTH(BM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BN4" s="156">
+      <c r="BN4" s="158">
         <f>IF(BN5="","",IF(OR(BN5=$M$3,DAY(BN5)=1),MONTH(BN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BO4" s="156">
+      <c r="BO4" s="158">
         <f>IF(BO5="","",IF(OR(BO5=$M$3,DAY(BO5)=1),MONTH(BO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BP4" s="156">
+      <c r="BP4" s="158">
         <f>IF(BP5="","",IF(OR(BP5=$M$3,DAY(BP5)=1),MONTH(BP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BQ4" s="155">
+      <c r="BQ4" s="157">
         <f>IF(BQ5="","",IF(OR(BQ5=$M$3,DAY(BQ5)=1),MONTH(BQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BR4" s="156">
+      <c r="BR4" s="158">
         <f>IF(BR5="","",IF(OR(BR5=$M$3,DAY(BR5)=1),MONTH(BR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BS4" s="156">
+      <c r="BS4" s="158">
         <f>IF(BS5="","",IF(OR(BS5=$M$3,DAY(BS5)=1),MONTH(BS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BT4" s="156">
+      <c r="BT4" s="158">
         <f>IF(BT5="","",IF(OR(BT5=$M$3,DAY(BT5)=1),MONTH(BT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BU4" s="156">
+      <c r="BU4" s="158">
         <f>IF(BU5="","",IF(OR(BU5=$M$3,DAY(BU5)=1),MONTH(BU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BV4" s="156">
+      <c r="BV4" s="158">
         <f>IF(BV5="","",IF(OR(BV5=$M$3,DAY(BV5)=1),MONTH(BV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BW4" s="156">
+      <c r="BW4" s="158">
         <f>IF(BW5="","",IF(OR(BW5=$M$3,DAY(BW5)=1),MONTH(BW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BX4" s="156">
+      <c r="BX4" s="158">
         <f>IF(BX5="","",IF(OR(BX5=$M$3,DAY(BX5)=1),MONTH(BX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BY4" s="156">
+      <c r="BY4" s="158">
         <f>IF(BY5="","",IF(OR(BY5=$M$3,DAY(BY5)=1),MONTH(BY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="BZ4" s="156">
+      <c r="BZ4" s="158">
         <f>IF(BZ5="","",IF(OR(BZ5=$M$3,DAY(BZ5)=1),MONTH(BZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CA4" s="156">
+      <c r="CA4" s="158">
         <f>IF(CA5="","",IF(OR(CA5=$M$3,DAY(CA5)=1),MONTH(CA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CB4" s="156">
+      <c r="CB4" s="158">
         <f>IF(CB5="","",IF(OR(CB5=$M$3,DAY(CB5)=1),MONTH(CB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CC4" s="156">
+      <c r="CC4" s="158">
         <f>IF(CC5="","",IF(OR(CC5=$M$3,DAY(CC5)=1),MONTH(CC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CD4" s="156">
+      <c r="CD4" s="158">
         <f>IF(CD5="","",IF(OR(CD5=$M$3,DAY(CD5)=1),MONTH(CD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CE4" s="156">
+      <c r="CE4" s="158">
         <f>IF(CE5="","",IF(OR(CE5=$M$3,DAY(CE5)=1),MONTH(CE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CF4" s="156">
+      <c r="CF4" s="158">
         <f>IF(CF5="","",IF(OR(CF5=$M$3,DAY(CF5)=1),MONTH(CF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CG4" s="156">
+      <c r="CG4" s="158">
         <f>IF(CG5="","",IF(OR(CG5=$M$3,DAY(CG5)=1),MONTH(CG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CH4" s="156">
+      <c r="CH4" s="158">
         <f>IF(CH5="","",IF(OR(CH5=$M$3,DAY(CH5)=1),MONTH(CH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CI4" s="156">
+      <c r="CI4" s="158">
         <f>IF(CI5="","",IF(OR(CI5=$M$3,DAY(CI5)=1),MONTH(CI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CJ4" s="156">
+      <c r="CJ4" s="158">
         <f>IF(CJ5="","",IF(OR(CJ5=$M$3,DAY(CJ5)=1),MONTH(CJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CK4" s="156">
+      <c r="CK4" s="158">
         <f>IF(CK5="","",IF(OR(CK5=$M$3,DAY(CK5)=1),MONTH(CK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CL4" s="156">
+      <c r="CL4" s="158">
         <f>IF(CL5="","",IF(OR(CL5=$M$3,DAY(CL5)=1),MONTH(CL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CM4" s="156">
+      <c r="CM4" s="158">
         <f>IF(CM5="","",IF(OR(CM5=$M$3,DAY(CM5)=1),MONTH(CM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CN4" s="156">
+      <c r="CN4" s="158">
         <f>IF(CN5="","",IF(OR(CN5=$M$3,DAY(CN5)=1),MONTH(CN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CO4" s="156">
+      <c r="CO4" s="158">
         <f>IF(CO5="","",IF(OR(CO5=$M$3,DAY(CO5)=1),MONTH(CO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CP4" s="156">
+      <c r="CP4" s="158">
         <f>IF(CP5="","",IF(OR(CP5=$M$3,DAY(CP5)=1),MONTH(CP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CQ4" s="156">
+      <c r="CQ4" s="158">
         <f>IF(CQ5="","",IF(OR(CQ5=$M$3,DAY(CQ5)=1),MONTH(CQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CR4" s="156">
+      <c r="CR4" s="158">
         <f>IF(CR5="","",IF(OR(CR5=$M$3,DAY(CR5)=1),MONTH(CR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CS4" s="156">
+      <c r="CS4" s="158">
         <f>IF(CS5="","",IF(OR(CS5=$M$3,DAY(CS5)=1),MONTH(CS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CT4" s="156">
+      <c r="CT4" s="158">
         <f>IF(CT5="","",IF(OR(CT5=$M$3,DAY(CT5)=1),MONTH(CT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CU4" s="156">
+      <c r="CU4" s="158">
         <f>IF(CU5="","",IF(OR(CU5=$M$3,DAY(CU5)=1),MONTH(CU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CV4" s="155">
+      <c r="CV4" s="157">
         <f>IF(CV5="","",IF(OR(CV5=$M$3,DAY(CV5)=1),MONTH(CV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CW4" s="156">
+      <c r="CW4" s="158">
         <f>IF(CW5="","",IF(OR(CW5=$M$3,DAY(CW5)=1),MONTH(CW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CX4" s="156">
+      <c r="CX4" s="158">
         <f>IF(CX5="","",IF(OR(CX5=$M$3,DAY(CX5)=1),MONTH(CX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CY4" s="156">
+      <c r="CY4" s="158">
         <f>IF(CY5="","",IF(OR(CY5=$M$3,DAY(CY5)=1),MONTH(CY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="CZ4" s="156">
+      <c r="CZ4" s="158">
         <f>IF(CZ5="","",IF(OR(CZ5=$M$3,DAY(CZ5)=1),MONTH(CZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DA4" s="156">
+      <c r="DA4" s="158">
         <f>IF(DA5="","",IF(OR(DA5=$M$3,DAY(DA5)=1),MONTH(DA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DB4" s="156">
+      <c r="DB4" s="158">
         <f>IF(DB5="","",IF(OR(DB5=$M$3,DAY(DB5)=1),MONTH(DB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DC4" s="156">
+      <c r="DC4" s="158">
         <f>IF(DC5="","",IF(OR(DC5=$M$3,DAY(DC5)=1),MONTH(DC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DD4" s="156">
+      <c r="DD4" s="158">
         <f>IF(DD5="","",IF(OR(DD5=$M$3,DAY(DD5)=1),MONTH(DD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DE4" s="156">
+      <c r="DE4" s="158">
         <f>IF(DE5="","",IF(OR(DE5=$M$3,DAY(DE5)=1),MONTH(DE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DF4" s="156">
+      <c r="DF4" s="158">
         <f>IF(DF5="","",IF(OR(DF5=$M$3,DAY(DF5)=1),MONTH(DF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DG4" s="156">
+      <c r="DG4" s="158">
         <f>IF(DG5="","",IF(OR(DG5=$M$3,DAY(DG5)=1),MONTH(DG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DH4" s="156">
+      <c r="DH4" s="158">
         <f>IF(DH5="","",IF(OR(DH5=$M$3,DAY(DH5)=1),MONTH(DH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DI4" s="156">
+      <c r="DI4" s="158">
         <f>IF(DI5="","",IF(OR(DI5=$M$3,DAY(DI5)=1),MONTH(DI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DJ4" s="156">
+      <c r="DJ4" s="158">
         <f>IF(DJ5="","",IF(OR(DJ5=$M$3,DAY(DJ5)=1),MONTH(DJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DK4" s="156">
+      <c r="DK4" s="158">
         <f>IF(DK5="","",IF(OR(DK5=$M$3,DAY(DK5)=1),MONTH(DK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DL4" s="156">
+      <c r="DL4" s="158">
         <f>IF(DL5="","",IF(OR(DL5=$M$3,DAY(DL5)=1),MONTH(DL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DM4" s="156">
+      <c r="DM4" s="158">
         <f>IF(DM5="","",IF(OR(DM5=$M$3,DAY(DM5)=1),MONTH(DM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DN4" s="156">
+      <c r="DN4" s="158">
         <f>IF(DN5="","",IF(OR(DN5=$M$3,DAY(DN5)=1),MONTH(DN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DO4" s="156">
+      <c r="DO4" s="158">
         <f>IF(DO5="","",IF(OR(DO5=$M$3,DAY(DO5)=1),MONTH(DO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DP4" s="156">
+      <c r="DP4" s="158">
         <f>IF(DP5="","",IF(OR(DP5=$M$3,DAY(DP5)=1),MONTH(DP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DQ4" s="156">
+      <c r="DQ4" s="158">
         <f>IF(DQ5="","",IF(OR(DQ5=$M$3,DAY(DQ5)=1),MONTH(DQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DR4" s="156">
+      <c r="DR4" s="158">
         <f>IF(DR5="","",IF(OR(DR5=$M$3,DAY(DR5)=1),MONTH(DR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DS4" s="156">
+      <c r="DS4" s="158">
         <f>IF(DS5="","",IF(OR(DS5=$M$3,DAY(DS5)=1),MONTH(DS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DT4" s="156">
+      <c r="DT4" s="158">
         <f>IF(DT5="","",IF(OR(DT5=$M$3,DAY(DT5)=1),MONTH(DT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DU4" s="156">
+      <c r="DU4" s="158">
         <f>IF(DU5="","",IF(OR(DU5=$M$3,DAY(DU5)=1),MONTH(DU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DV4" s="156">
+      <c r="DV4" s="158">
         <f>IF(DV5="","",IF(OR(DV5=$M$3,DAY(DV5)=1),MONTH(DV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DW4" s="156">
+      <c r="DW4" s="158">
         <f>IF(DW5="","",IF(OR(DW5=$M$3,DAY(DW5)=1),MONTH(DW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DX4" s="156">
+      <c r="DX4" s="158">
         <f>IF(DX5="","",IF(OR(DX5=$M$3,DAY(DX5)=1),MONTH(DX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DY4" s="156">
+      <c r="DY4" s="158">
         <f>IF(DY5="","",IF(OR(DY5=$M$3,DAY(DY5)=1),MONTH(DY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="DZ4" s="155">
+      <c r="DZ4" s="157">
         <f>IF(DZ5="","",IF(OR(DZ5=$M$3,DAY(DZ5)=1),MONTH(DZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EA4" s="156">
+      <c r="EA4" s="158">
         <f>IF(EA5="","",IF(OR(EA5=$M$3,DAY(EA5)=1),MONTH(EA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EB4" s="156">
+      <c r="EB4" s="158">
         <f>IF(EB5="","",IF(OR(EB5=$M$3,DAY(EB5)=1),MONTH(EB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EC4" s="156">
+      <c r="EC4" s="158">
         <f>IF(EC5="","",IF(OR(EC5=$M$3,DAY(EC5)=1),MONTH(EC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ED4" s="156">
+      <c r="ED4" s="158">
         <f>IF(ED5="","",IF(OR(ED5=$M$3,DAY(ED5)=1),MONTH(ED5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EE4" s="156">
+      <c r="EE4" s="158">
         <f>IF(EE5="","",IF(OR(EE5=$M$3,DAY(EE5)=1),MONTH(EE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EF4" s="156">
+      <c r="EF4" s="158">
         <f>IF(EF5="","",IF(OR(EF5=$M$3,DAY(EF5)=1),MONTH(EF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EG4" s="156">
+      <c r="EG4" s="158">
         <f>IF(EG5="","",IF(OR(EG5=$M$3,DAY(EG5)=1),MONTH(EG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EH4" s="156">
+      <c r="EH4" s="158">
         <f>IF(EH5="","",IF(OR(EH5=$M$3,DAY(EH5)=1),MONTH(EH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EI4" s="156">
+      <c r="EI4" s="158">
         <f>IF(EI5="","",IF(OR(EI5=$M$3,DAY(EI5)=1),MONTH(EI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EJ4" s="156">
+      <c r="EJ4" s="158">
         <f>IF(EJ5="","",IF(OR(EJ5=$M$3,DAY(EJ5)=1),MONTH(EJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EK4" s="156">
+      <c r="EK4" s="158">
         <f>IF(EK5="","",IF(OR(EK5=$M$3,DAY(EK5)=1),MONTH(EK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EL4" s="156">
+      <c r="EL4" s="158">
         <f>IF(EL5="","",IF(OR(EL5=$M$3,DAY(EL5)=1),MONTH(EL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EM4" s="156">
+      <c r="EM4" s="158">
         <f>IF(EM5="","",IF(OR(EM5=$M$3,DAY(EM5)=1),MONTH(EM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EN4" s="156">
+      <c r="EN4" s="158">
         <f>IF(EN5="","",IF(OR(EN5=$M$3,DAY(EN5)=1),MONTH(EN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EO4" s="156">
+      <c r="EO4" s="158">
         <f>IF(EO5="","",IF(OR(EO5=$M$3,DAY(EO5)=1),MONTH(EO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EP4" s="156">
+      <c r="EP4" s="158">
         <f>IF(EP5="","",IF(OR(EP5=$M$3,DAY(EP5)=1),MONTH(EP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EQ4" s="156">
+      <c r="EQ4" s="158">
         <f>IF(EQ5="","",IF(OR(EQ5=$M$3,DAY(EQ5)=1),MONTH(EQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ER4" s="156">
+      <c r="ER4" s="158">
         <f>IF(ER5="","",IF(OR(ER5=$M$3,DAY(ER5)=1),MONTH(ER5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ES4" s="156">
+      <c r="ES4" s="158">
         <f>IF(ES5="","",IF(OR(ES5=$M$3,DAY(ES5)=1),MONTH(ES5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ET4" s="156">
+      <c r="ET4" s="158">
         <f>IF(ET5="","",IF(OR(ET5=$M$3,DAY(ET5)=1),MONTH(ET5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EU4" s="156">
+      <c r="EU4" s="158">
         <f>IF(EU5="","",IF(OR(EU5=$M$3,DAY(EU5)=1),MONTH(EU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EV4" s="156">
+      <c r="EV4" s="158">
         <f>IF(EV5="","",IF(OR(EV5=$M$3,DAY(EV5)=1),MONTH(EV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EW4" s="156">
+      <c r="EW4" s="158">
         <f>IF(EW5="","",IF(OR(EW5=$M$3,DAY(EW5)=1),MONTH(EW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EX4" s="156">
+      <c r="EX4" s="158">
         <f>IF(EX5="","",IF(OR(EX5=$M$3,DAY(EX5)=1),MONTH(EX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EY4" s="156">
+      <c r="EY4" s="158">
         <f>IF(EY5="","",IF(OR(EY5=$M$3,DAY(EY5)=1),MONTH(EY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="EZ4" s="156">
+      <c r="EZ4" s="158">
         <f>IF(EZ5="","",IF(OR(EZ5=$M$3,DAY(EZ5)=1),MONTH(EZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FA4" s="156">
+      <c r="FA4" s="158">
         <f>IF(FA5="","",IF(OR(FA5=$M$3,DAY(FA5)=1),MONTH(FA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FB4" s="156">
+      <c r="FB4" s="158">
         <f>IF(FB5="","",IF(OR(FB5=$M$3,DAY(FB5)=1),MONTH(FB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FC4" s="156">
+      <c r="FC4" s="158">
         <f>IF(FC5="","",IF(OR(FC5=$M$3,DAY(FC5)=1),MONTH(FC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FD4" s="156">
+      <c r="FD4" s="158">
         <f>IF(FD5="","",IF(OR(FD5=$M$3,DAY(FD5)=1),MONTH(FD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FE4" s="156">
+      <c r="FE4" s="158">
         <f>IF(FE5="","",IF(OR(FE5=$M$3,DAY(FE5)=1),MONTH(FE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FF4" s="156">
+      <c r="FF4" s="158">
         <f>IF(FF5="","",IF(OR(FF5=$M$3,DAY(FF5)=1),MONTH(FF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FG4" s="156">
+      <c r="FG4" s="158">
         <f>IF(FG5="","",IF(OR(FG5=$M$3,DAY(FG5)=1),MONTH(FG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FH4" s="156">
+      <c r="FH4" s="158">
         <f>IF(FH5="","",IF(OR(FH5=$M$3,DAY(FH5)=1),MONTH(FH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FI4" s="156">
+      <c r="FI4" s="158">
         <f>IF(FI5="","",IF(OR(FI5=$M$3,DAY(FI5)=1),MONTH(FI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FJ4" s="156">
+      <c r="FJ4" s="158">
         <f>IF(FJ5="","",IF(OR(FJ5=$M$3,DAY(FJ5)=1),MONTH(FJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FK4" s="156">
+      <c r="FK4" s="158">
         <f>IF(FK5="","",IF(OR(FK5=$M$3,DAY(FK5)=1),MONTH(FK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FL4" s="156">
+      <c r="FL4" s="158">
         <f>IF(FL5="","",IF(OR(FL5=$M$3,DAY(FL5)=1),MONTH(FL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FM4" s="156">
+      <c r="FM4" s="158">
         <f>IF(FM5="","",IF(OR(FM5=$M$3,DAY(FM5)=1),MONTH(FM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FN4" s="156">
+      <c r="FN4" s="158">
         <f>IF(FN5="","",IF(OR(FN5=$M$3,DAY(FN5)=1),MONTH(FN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FO4" s="156">
+      <c r="FO4" s="158">
         <f>IF(FO5="","",IF(OR(FO5=$M$3,DAY(FO5)=1),MONTH(FO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FP4" s="156">
+      <c r="FP4" s="158">
         <f>IF(FP5="","",IF(OR(FP5=$M$3,DAY(FP5)=1),MONTH(FP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FQ4" s="156">
+      <c r="FQ4" s="158">
         <f>IF(FQ5="","",IF(OR(FQ5=$M$3,DAY(FQ5)=1),MONTH(FQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FR4" s="156">
+      <c r="FR4" s="158">
         <f>IF(FR5="","",IF(OR(FR5=$M$3,DAY(FR5)=1),MONTH(FR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FS4" s="156">
+      <c r="FS4" s="158">
         <f>IF(FS5="","",IF(OR(FS5=$M$3,DAY(FS5)=1),MONTH(FS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FT4" s="156">
+      <c r="FT4" s="158">
         <f>IF(FT5="","",IF(OR(FT5=$M$3,DAY(FT5)=1),MONTH(FT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FU4" s="156">
+      <c r="FU4" s="158">
         <f>IF(FU5="","",IF(OR(FU5=$M$3,DAY(FU5)=1),MONTH(FU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FV4" s="156">
+      <c r="FV4" s="158">
         <f>IF(FV5="","",IF(OR(FV5=$M$3,DAY(FV5)=1),MONTH(FV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FW4" s="156">
+      <c r="FW4" s="158">
         <f>IF(FW5="","",IF(OR(FW5=$M$3,DAY(FW5)=1),MONTH(FW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FX4" s="156">
+      <c r="FX4" s="158">
         <f>IF(FX5="","",IF(OR(FX5=$M$3,DAY(FX5)=1),MONTH(FX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FY4" s="156">
+      <c r="FY4" s="158">
         <f>IF(FY5="","",IF(OR(FY5=$M$3,DAY(FY5)=1),MONTH(FY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="FZ4" s="156">
+      <c r="FZ4" s="158">
         <f>IF(FZ5="","",IF(OR(FZ5=$M$3,DAY(FZ5)=1),MONTH(FZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GA4" s="156">
+      <c r="GA4" s="158">
         <f>IF(GA5="","",IF(OR(GA5=$M$3,DAY(GA5)=1),MONTH(GA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GB4" s="156">
+      <c r="GB4" s="158">
         <f>IF(GB5="","",IF(OR(GB5=$M$3,DAY(GB5)=1),MONTH(GB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GC4" s="156">
+      <c r="GC4" s="158">
         <f>IF(GC5="","",IF(OR(GC5=$M$3,DAY(GC5)=1),MONTH(GC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GD4" s="156">
+      <c r="GD4" s="158">
         <f>IF(GD5="","",IF(OR(GD5=$M$3,DAY(GD5)=1),MONTH(GD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GE4" s="156">
+      <c r="GE4" s="158">
         <f>IF(GE5="","",IF(OR(GE5=$M$3,DAY(GE5)=1),MONTH(GE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GF4" s="156">
+      <c r="GF4" s="158">
         <f>IF(GF5="","",IF(OR(GF5=$M$3,DAY(GF5)=1),MONTH(GF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GG4" s="156">
+      <c r="GG4" s="158">
         <f>IF(GG5="","",IF(OR(GG5=$M$3,DAY(GG5)=1),MONTH(GG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GH4" s="156">
+      <c r="GH4" s="158">
         <f>IF(GH5="","",IF(OR(GH5=$M$3,DAY(GH5)=1),MONTH(GH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GI4" s="156">
+      <c r="GI4" s="158">
         <f>IF(GI5="","",IF(OR(GI5=$M$3,DAY(GI5)=1),MONTH(GI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GJ4" s="156">
+      <c r="GJ4" s="158">
         <f>IF(GJ5="","",IF(OR(GJ5=$M$3,DAY(GJ5)=1),MONTH(GJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GK4" s="156">
+      <c r="GK4" s="158">
         <f>IF(GK5="","",IF(OR(GK5=$M$3,DAY(GK5)=1),MONTH(GK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GL4" s="156">
+      <c r="GL4" s="158">
         <f>IF(GL5="","",IF(OR(GL5=$M$3,DAY(GL5)=1),MONTH(GL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GM4" s="156">
+      <c r="GM4" s="158">
         <f>IF(GM5="","",IF(OR(GM5=$M$3,DAY(GM5)=1),MONTH(GM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GN4" s="156">
+      <c r="GN4" s="158">
         <f>IF(GN5="","",IF(OR(GN5=$M$3,DAY(GN5)=1),MONTH(GN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GO4" s="156">
+      <c r="GO4" s="158">
         <f>IF(GO5="","",IF(OR(GO5=$M$3,DAY(GO5)=1),MONTH(GO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GP4" s="156">
+      <c r="GP4" s="158">
         <f>IF(GP5="","",IF(OR(GP5=$M$3,DAY(GP5)=1),MONTH(GP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GQ4" s="156">
+      <c r="GQ4" s="158">
         <f>IF(GQ5="","",IF(OR(GQ5=$M$3,DAY(GQ5)=1),MONTH(GQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GR4" s="156">
+      <c r="GR4" s="158">
         <f>IF(GR5="","",IF(OR(GR5=$M$3,DAY(GR5)=1),MONTH(GR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GS4" s="156">
+      <c r="GS4" s="158">
         <f>IF(GS5="","",IF(OR(GS5=$M$3,DAY(GS5)=1),MONTH(GS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GT4" s="156">
+      <c r="GT4" s="158">
         <f>IF(GT5="","",IF(OR(GT5=$M$3,DAY(GT5)=1),MONTH(GT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GU4" s="156">
+      <c r="GU4" s="158">
         <f>IF(GU5="","",IF(OR(GU5=$M$3,DAY(GU5)=1),MONTH(GU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GV4" s="156">
+      <c r="GV4" s="158">
         <f>IF(GV5="","",IF(OR(GV5=$M$3,DAY(GV5)=1),MONTH(GV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GW4" s="156">
+      <c r="GW4" s="158">
         <f>IF(GW5="","",IF(OR(GW5=$M$3,DAY(GW5)=1),MONTH(GW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GX4" s="156">
+      <c r="GX4" s="158">
         <f>IF(GX5="","",IF(OR(GX5=$M$3,DAY(GX5)=1),MONTH(GX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GY4" s="156">
+      <c r="GY4" s="158">
         <f>IF(GY5="","",IF(OR(GY5=$M$3,DAY(GY5)=1),MONTH(GY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="GZ4" s="156">
+      <c r="GZ4" s="158">
         <f>IF(GZ5="","",IF(OR(GZ5=$M$3,DAY(GZ5)=1),MONTH(GZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HA4" s="156">
+      <c r="HA4" s="158">
         <f>IF(HA5="","",IF(OR(HA5=$M$3,DAY(HA5)=1),MONTH(HA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HB4" s="156">
+      <c r="HB4" s="158">
         <f>IF(HB5="","",IF(OR(HB5=$M$3,DAY(HB5)=1),MONTH(HB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HC4" s="156">
+      <c r="HC4" s="158">
         <f>IF(HC5="","",IF(OR(HC5=$M$3,DAY(HC5)=1),MONTH(HC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HD4" s="156">
+      <c r="HD4" s="158">
         <f>IF(HD5="","",IF(OR(HD5=$M$3,DAY(HD5)=1),MONTH(HD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HE4" s="156">
+      <c r="HE4" s="158">
         <f>IF(HE5="","",IF(OR(HE5=$M$3,DAY(HE5)=1),MONTH(HE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HF4" s="156">
+      <c r="HF4" s="158">
         <f>IF(HF5="","",IF(OR(HF5=$M$3,DAY(HF5)=1),MONTH(HF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HG4" s="156">
+      <c r="HG4" s="158">
         <f>IF(HG5="","",IF(OR(HG5=$M$3,DAY(HG5)=1),MONTH(HG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HH4" s="156">
+      <c r="HH4" s="158">
         <f>IF(HH5="","",IF(OR(HH5=$M$3,DAY(HH5)=1),MONTH(HH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HI4" s="156">
+      <c r="HI4" s="158">
         <f>IF(HI5="","",IF(OR(HI5=$M$3,DAY(HI5)=1),MONTH(HI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HJ4" s="156">
+      <c r="HJ4" s="158">
         <f>IF(HJ5="","",IF(OR(HJ5=$M$3,DAY(HJ5)=1),MONTH(HJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HK4" s="156">
+      <c r="HK4" s="158">
         <f>IF(HK5="","",IF(OR(HK5=$M$3,DAY(HK5)=1),MONTH(HK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HL4" s="156">
+      <c r="HL4" s="158">
         <f>IF(HL5="","",IF(OR(HL5=$M$3,DAY(HL5)=1),MONTH(HL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HM4" s="156">
+      <c r="HM4" s="158">
         <f>IF(HM5="","",IF(OR(HM5=$M$3,DAY(HM5)=1),MONTH(HM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HN4" s="156">
+      <c r="HN4" s="158">
         <f>IF(HN5="","",IF(OR(HN5=$M$3,DAY(HN5)=1),MONTH(HN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HO4" s="156">
+      <c r="HO4" s="158">
         <f>IF(HO5="","",IF(OR(HO5=$M$3,DAY(HO5)=1),MONTH(HO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HP4" s="156">
+      <c r="HP4" s="158">
         <f>IF(HP5="","",IF(OR(HP5=$M$3,DAY(HP5)=1),MONTH(HP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HQ4" s="156">
+      <c r="HQ4" s="158">
         <f>IF(HQ5="","",IF(OR(HQ5=$M$3,DAY(HQ5)=1),MONTH(HQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HR4" s="156">
+      <c r="HR4" s="158">
         <f>IF(HR5="","",IF(OR(HR5=$M$3,DAY(HR5)=1),MONTH(HR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HS4" s="156">
+      <c r="HS4" s="158">
         <f>IF(HS5="","",IF(OR(HS5=$M$3,DAY(HS5)=1),MONTH(HS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HT4" s="156">
+      <c r="HT4" s="158">
         <f>IF(HT5="","",IF(OR(HT5=$M$3,DAY(HT5)=1),MONTH(HT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HU4" s="156">
+      <c r="HU4" s="158">
         <f>IF(HU5="","",IF(OR(HU5=$M$3,DAY(HU5)=1),MONTH(HU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HV4" s="156">
+      <c r="HV4" s="158">
         <f>IF(HV5="","",IF(OR(HV5=$M$3,DAY(HV5)=1),MONTH(HV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HW4" s="156">
+      <c r="HW4" s="158">
         <f>IF(HW5="","",IF(OR(HW5=$M$3,DAY(HW5)=1),MONTH(HW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HX4" s="156">
+      <c r="HX4" s="158">
         <f>IF(HX5="","",IF(OR(HX5=$M$3,DAY(HX5)=1),MONTH(HX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HY4" s="156">
+      <c r="HY4" s="158">
         <f>IF(HY5="","",IF(OR(HY5=$M$3,DAY(HY5)=1),MONTH(HY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="HZ4" s="156">
+      <c r="HZ4" s="158">
         <f>IF(HZ5="","",IF(OR(HZ5=$M$3,DAY(HZ5)=1),MONTH(HZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IA4" s="156">
+      <c r="IA4" s="158">
         <f>IF(IA5="","",IF(OR(IA5=$M$3,DAY(IA5)=1),MONTH(IA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IB4" s="156">
+      <c r="IB4" s="158">
         <f>IF(IB5="","",IF(OR(IB5=$M$3,DAY(IB5)=1),MONTH(IB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IC4" s="156">
+      <c r="IC4" s="158">
         <f>IF(IC5="","",IF(OR(IC5=$M$3,DAY(IC5)=1),MONTH(IC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ID4" s="156">
+      <c r="ID4" s="158">
         <f>IF(ID5="","",IF(OR(ID5=$M$3,DAY(ID5)=1),MONTH(ID5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IE4" s="156">
+      <c r="IE4" s="158">
         <f>IF(IE5="","",IF(OR(IE5=$M$3,DAY(IE5)=1),MONTH(IE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IF4" s="156">
+      <c r="IF4" s="158">
         <f>IF(IF5="","",IF(OR(IF5=$M$3,DAY(IF5)=1),MONTH(IF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IG4" s="156">
+      <c r="IG4" s="158">
         <f>IF(IG5="","",IF(OR(IG5=$M$3,DAY(IG5)=1),MONTH(IG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IH4" s="156">
+      <c r="IH4" s="158">
         <f>IF(IH5="","",IF(OR(IH5=$M$3,DAY(IH5)=1),MONTH(IH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="II4" s="156">
+      <c r="II4" s="158">
         <f>IF(II5="","",IF(OR(II5=$M$3,DAY(II5)=1),MONTH(II5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IJ4" s="156">
+      <c r="IJ4" s="158">
         <f>IF(IJ5="","",IF(OR(IJ5=$M$3,DAY(IJ5)=1),MONTH(IJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IK4" s="156">
+      <c r="IK4" s="158">
         <f>IF(IK5="","",IF(OR(IK5=$M$3,DAY(IK5)=1),MONTH(IK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IL4" s="156">
+      <c r="IL4" s="158">
         <f>IF(IL5="","",IF(OR(IL5=$M$3,DAY(IL5)=1),MONTH(IL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IM4" s="156">
+      <c r="IM4" s="158">
         <f>IF(IM5="","",IF(OR(IM5=$M$3,DAY(IM5)=1),MONTH(IM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IN4" s="156">
+      <c r="IN4" s="158">
         <f>IF(IN5="","",IF(OR(IN5=$M$3,DAY(IN5)=1),MONTH(IN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IO4" s="156">
+      <c r="IO4" s="158">
         <f>IF(IO5="","",IF(OR(IO5=$M$3,DAY(IO5)=1),MONTH(IO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IP4" s="156">
+      <c r="IP4" s="158">
         <f>IF(IP5="","",IF(OR(IP5=$M$3,DAY(IP5)=1),MONTH(IP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IQ4" s="156">
+      <c r="IQ4" s="158">
         <f>IF(IQ5="","",IF(OR(IQ5=$M$3,DAY(IQ5)=1),MONTH(IQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IR4" s="156">
+      <c r="IR4" s="158">
         <f>IF(IR5="","",IF(OR(IR5=$M$3,DAY(IR5)=1),MONTH(IR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IS4" s="156">
+      <c r="IS4" s="158">
         <f>IF(IS5="","",IF(OR(IS5=$M$3,DAY(IS5)=1),MONTH(IS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IT4" s="156">
+      <c r="IT4" s="158">
         <f>IF(IT5="","",IF(OR(IT5=$M$3,DAY(IT5)=1),MONTH(IT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IU4" s="156">
+      <c r="IU4" s="158">
         <f>IF(IU5="","",IF(OR(IU5=$M$3,DAY(IU5)=1),MONTH(IU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IV4" s="156">
+      <c r="IV4" s="158">
         <f>IF(IV5="","",IF(OR(IV5=$M$3,DAY(IV5)=1),MONTH(IV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IW4" s="156">
+      <c r="IW4" s="158">
         <f>IF(IW5="","",IF(OR(IW5=$M$3,DAY(IW5)=1),MONTH(IW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IX4" s="156">
+      <c r="IX4" s="158">
         <f>IF(IX5="","",IF(OR(IX5=$M$3,DAY(IX5)=1),MONTH(IX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IY4" s="156">
+      <c r="IY4" s="158">
         <f>IF(IY5="","",IF(OR(IY5=$M$3,DAY(IY5)=1),MONTH(IY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="IZ4" s="156">
+      <c r="IZ4" s="158">
         <f>IF(IZ5="","",IF(OR(IZ5=$M$3,DAY(IZ5)=1),MONTH(IZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JA4" s="156">
+      <c r="JA4" s="158">
         <f>IF(JA5="","",IF(OR(JA5=$M$3,DAY(JA5)=1),MONTH(JA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JB4" s="156">
+      <c r="JB4" s="158">
         <f>IF(JB5="","",IF(OR(JB5=$M$3,DAY(JB5)=1),MONTH(JB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JC4" s="156">
+      <c r="JC4" s="158">
         <f>IF(JC5="","",IF(OR(JC5=$M$3,DAY(JC5)=1),MONTH(JC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JD4" s="156">
+      <c r="JD4" s="158">
         <f>IF(JD5="","",IF(OR(JD5=$M$3,DAY(JD5)=1),MONTH(JD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JE4" s="156">
+      <c r="JE4" s="158">
         <f>IF(JE5="","",IF(OR(JE5=$M$3,DAY(JE5)=1),MONTH(JE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JF4" s="156">
+      <c r="JF4" s="158">
         <f>IF(JF5="","",IF(OR(JF5=$M$3,DAY(JF5)=1),MONTH(JF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JG4" s="156">
+      <c r="JG4" s="158">
         <f>IF(JG5="","",IF(OR(JG5=$M$3,DAY(JG5)=1),MONTH(JG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JH4" s="156">
+      <c r="JH4" s="158">
         <f>IF(JH5="","",IF(OR(JH5=$M$3,DAY(JH5)=1),MONTH(JH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JI4" s="156">
+      <c r="JI4" s="158">
         <f>IF(JI5="","",IF(OR(JI5=$M$3,DAY(JI5)=1),MONTH(JI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JJ4" s="156">
+      <c r="JJ4" s="158">
         <f>IF(JJ5="","",IF(OR(JJ5=$M$3,DAY(JJ5)=1),MONTH(JJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JK4" s="156">
+      <c r="JK4" s="158">
         <f>IF(JK5="","",IF(OR(JK5=$M$3,DAY(JK5)=1),MONTH(JK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JL4" s="156">
+      <c r="JL4" s="158">
         <f>IF(JL5="","",IF(OR(JL5=$M$3,DAY(JL5)=1),MONTH(JL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JM4" s="156">
+      <c r="JM4" s="158">
         <f>IF(JM5="","",IF(OR(JM5=$M$3,DAY(JM5)=1),MONTH(JM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JN4" s="156">
+      <c r="JN4" s="158">
         <f>IF(JN5="","",IF(OR(JN5=$M$3,DAY(JN5)=1),MONTH(JN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JO4" s="156">
+      <c r="JO4" s="158">
         <f>IF(JO5="","",IF(OR(JO5=$M$3,DAY(JO5)=1),MONTH(JO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JP4" s="156">
+      <c r="JP4" s="158">
         <f>IF(JP5="","",IF(OR(JP5=$M$3,DAY(JP5)=1),MONTH(JP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JQ4" s="156">
+      <c r="JQ4" s="158">
         <f>IF(JQ5="","",IF(OR(JQ5=$M$3,DAY(JQ5)=1),MONTH(JQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JR4" s="156">
+      <c r="JR4" s="158">
         <f>IF(JR5="","",IF(OR(JR5=$M$3,DAY(JR5)=1),MONTH(JR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JS4" s="156">
+      <c r="JS4" s="158">
         <f>IF(JS5="","",IF(OR(JS5=$M$3,DAY(JS5)=1),MONTH(JS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JT4" s="156">
+      <c r="JT4" s="158">
         <f>IF(JT5="","",IF(OR(JT5=$M$3,DAY(JT5)=1),MONTH(JT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JU4" s="156">
+      <c r="JU4" s="158">
         <f>IF(JU5="","",IF(OR(JU5=$M$3,DAY(JU5)=1),MONTH(JU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JV4" s="156">
+      <c r="JV4" s="158">
         <f>IF(JV5="","",IF(OR(JV5=$M$3,DAY(JV5)=1),MONTH(JV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JW4" s="156">
+      <c r="JW4" s="158">
         <f>IF(JW5="","",IF(OR(JW5=$M$3,DAY(JW5)=1),MONTH(JW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JX4" s="156">
+      <c r="JX4" s="158">
         <f>IF(JX5="","",IF(OR(JX5=$M$3,DAY(JX5)=1),MONTH(JX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JY4" s="156">
+      <c r="JY4" s="158">
         <f>IF(JY5="","",IF(OR(JY5=$M$3,DAY(JY5)=1),MONTH(JY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="JZ4" s="156">
+      <c r="JZ4" s="158">
         <f>IF(JZ5="","",IF(OR(JZ5=$M$3,DAY(JZ5)=1),MONTH(JZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KA4" s="156">
+      <c r="KA4" s="158">
         <f>IF(KA5="","",IF(OR(KA5=$M$3,DAY(KA5)=1),MONTH(KA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KB4" s="156">
+      <c r="KB4" s="158">
         <f>IF(KB5="","",IF(OR(KB5=$M$3,DAY(KB5)=1),MONTH(KB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KC4" s="156">
+      <c r="KC4" s="158">
         <f>IF(KC5="","",IF(OR(KC5=$M$3,DAY(KC5)=1),MONTH(KC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KD4" s="156">
+      <c r="KD4" s="158">
         <f>IF(KD5="","",IF(OR(KD5=$M$3,DAY(KD5)=1),MONTH(KD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KE4" s="156">
+      <c r="KE4" s="158">
         <f>IF(KE5="","",IF(OR(KE5=$M$3,DAY(KE5)=1),MONTH(KE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KF4" s="156">
+      <c r="KF4" s="158">
         <f>IF(KF5="","",IF(OR(KF5=$M$3,DAY(KF5)=1),MONTH(KF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KG4" s="156">
+      <c r="KG4" s="158">
         <f>IF(KG5="","",IF(OR(KG5=$M$3,DAY(KG5)=1),MONTH(KG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KH4" s="156">
+      <c r="KH4" s="158">
         <f>IF(KH5="","",IF(OR(KH5=$M$3,DAY(KH5)=1),MONTH(KH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KI4" s="156">
+      <c r="KI4" s="158">
         <f>IF(KI5="","",IF(OR(KI5=$M$3,DAY(KI5)=1),MONTH(KI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KJ4" s="156">
+      <c r="KJ4" s="158">
         <f>IF(KJ5="","",IF(OR(KJ5=$M$3,DAY(KJ5)=1),MONTH(KJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KK4" s="156">
+      <c r="KK4" s="158">
         <f>IF(KK5="","",IF(OR(KK5=$M$3,DAY(KK5)=1),MONTH(KK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KL4" s="156">
+      <c r="KL4" s="158">
         <f>IF(KL5="","",IF(OR(KL5=$M$3,DAY(KL5)=1),MONTH(KL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KM4" s="156">
+      <c r="KM4" s="158">
         <f>IF(KM5="","",IF(OR(KM5=$M$3,DAY(KM5)=1),MONTH(KM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KN4" s="156">
+      <c r="KN4" s="158">
         <f>IF(KN5="","",IF(OR(KN5=$M$3,DAY(KN5)=1),MONTH(KN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KO4" s="156">
+      <c r="KO4" s="158">
         <f>IF(KO5="","",IF(OR(KO5=$M$3,DAY(KO5)=1),MONTH(KO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KP4" s="156">
+      <c r="KP4" s="158">
         <f>IF(KP5="","",IF(OR(KP5=$M$3,DAY(KP5)=1),MONTH(KP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KQ4" s="156">
+      <c r="KQ4" s="158">
         <f>IF(KQ5="","",IF(OR(KQ5=$M$3,DAY(KQ5)=1),MONTH(KQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KR4" s="156">
+      <c r="KR4" s="158">
         <f>IF(KR5="","",IF(OR(KR5=$M$3,DAY(KR5)=1),MONTH(KR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KS4" s="156">
+      <c r="KS4" s="158">
         <f>IF(KS5="","",IF(OR(KS5=$M$3,DAY(KS5)=1),MONTH(KS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KT4" s="156">
+      <c r="KT4" s="158">
         <f>IF(KT5="","",IF(OR(KT5=$M$3,DAY(KT5)=1),MONTH(KT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KU4" s="156">
+      <c r="KU4" s="158">
         <f>IF(KU5="","",IF(OR(KU5=$M$3,DAY(KU5)=1),MONTH(KU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KV4" s="156">
+      <c r="KV4" s="158">
         <f>IF(KV5="","",IF(OR(KV5=$M$3,DAY(KV5)=1),MONTH(KV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KW4" s="156">
+      <c r="KW4" s="158">
         <f>IF(KW5="","",IF(OR(KW5=$M$3,DAY(KW5)=1),MONTH(KW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KX4" s="156">
+      <c r="KX4" s="158">
         <f>IF(KX5="","",IF(OR(KX5=$M$3,DAY(KX5)=1),MONTH(KX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KY4" s="156">
+      <c r="KY4" s="158">
         <f>IF(KY5="","",IF(OR(KY5=$M$3,DAY(KY5)=1),MONTH(KY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="KZ4" s="156">
+      <c r="KZ4" s="158">
         <f>IF(KZ5="","",IF(OR(KZ5=$M$3,DAY(KZ5)=1),MONTH(KZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LA4" s="156">
+      <c r="LA4" s="158">
         <f>IF(LA5="","",IF(OR(LA5=$M$3,DAY(LA5)=1),MONTH(LA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LB4" s="156">
+      <c r="LB4" s="158">
         <f>IF(LB5="","",IF(OR(LB5=$M$3,DAY(LB5)=1),MONTH(LB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LC4" s="156">
+      <c r="LC4" s="158">
         <f>IF(LC5="","",IF(OR(LC5=$M$3,DAY(LC5)=1),MONTH(LC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LD4" s="156">
+      <c r="LD4" s="158">
         <f>IF(LD5="","",IF(OR(LD5=$M$3,DAY(LD5)=1),MONTH(LD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LE4" s="156">
+      <c r="LE4" s="158">
         <f>IF(LE5="","",IF(OR(LE5=$M$3,DAY(LE5)=1),MONTH(LE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LF4" s="156">
+      <c r="LF4" s="158">
         <f>IF(LF5="","",IF(OR(LF5=$M$3,DAY(LF5)=1),MONTH(LF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LG4" s="156">
+      <c r="LG4" s="158">
         <f>IF(LG5="","",IF(OR(LG5=$M$3,DAY(LG5)=1),MONTH(LG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LH4" s="156">
+      <c r="LH4" s="158">
         <f>IF(LH5="","",IF(OR(LH5=$M$3,DAY(LH5)=1),MONTH(LH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LI4" s="156">
+      <c r="LI4" s="158">
         <f>IF(LI5="","",IF(OR(LI5=$M$3,DAY(LI5)=1),MONTH(LI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LJ4" s="156">
+      <c r="LJ4" s="158">
         <f>IF(LJ5="","",IF(OR(LJ5=$M$3,DAY(LJ5)=1),MONTH(LJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LK4" s="156">
+      <c r="LK4" s="158">
         <f>IF(LK5="","",IF(OR(LK5=$M$3,DAY(LK5)=1),MONTH(LK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LL4" s="156">
+      <c r="LL4" s="158">
         <f>IF(LL5="","",IF(OR(LL5=$M$3,DAY(LL5)=1),MONTH(LL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LM4" s="156">
+      <c r="LM4" s="158">
         <f>IF(LM5="","",IF(OR(LM5=$M$3,DAY(LM5)=1),MONTH(LM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LN4" s="156">
+      <c r="LN4" s="158">
         <f>IF(LN5="","",IF(OR(LN5=$M$3,DAY(LN5)=1),MONTH(LN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LO4" s="156">
+      <c r="LO4" s="158">
         <f>IF(LO5="","",IF(OR(LO5=$M$3,DAY(LO5)=1),MONTH(LO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LP4" s="156">
+      <c r="LP4" s="158">
         <f>IF(LP5="","",IF(OR(LP5=$M$3,DAY(LP5)=1),MONTH(LP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LQ4" s="156">
+      <c r="LQ4" s="158">
         <f>IF(LQ5="","",IF(OR(LQ5=$M$3,DAY(LQ5)=1),MONTH(LQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LR4" s="156">
+      <c r="LR4" s="158">
         <f>IF(LR5="","",IF(OR(LR5=$M$3,DAY(LR5)=1),MONTH(LR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LS4" s="156">
+      <c r="LS4" s="158">
         <f>IF(LS5="","",IF(OR(LS5=$M$3,DAY(LS5)=1),MONTH(LS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LT4" s="156">
+      <c r="LT4" s="158">
         <f>IF(LT5="","",IF(OR(LT5=$M$3,DAY(LT5)=1),MONTH(LT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LU4" s="156">
+      <c r="LU4" s="158">
         <f>IF(LU5="","",IF(OR(LU5=$M$3,DAY(LU5)=1),MONTH(LU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LV4" s="156">
+      <c r="LV4" s="158">
         <f>IF(LV5="","",IF(OR(LV5=$M$3,DAY(LV5)=1),MONTH(LV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LW4" s="156">
+      <c r="LW4" s="158">
         <f>IF(LW5="","",IF(OR(LW5=$M$3,DAY(LW5)=1),MONTH(LW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LX4" s="156">
+      <c r="LX4" s="158">
         <f>IF(LX5="","",IF(OR(LX5=$M$3,DAY(LX5)=1),MONTH(LX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LY4" s="156">
+      <c r="LY4" s="158">
         <f>IF(LY5="","",IF(OR(LY5=$M$3,DAY(LY5)=1),MONTH(LY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="LZ4" s="156">
+      <c r="LZ4" s="158">
         <f>IF(LZ5="","",IF(OR(LZ5=$M$3,DAY(LZ5)=1),MONTH(LZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MA4" s="156">
+      <c r="MA4" s="158">
         <f>IF(MA5="","",IF(OR(MA5=$M$3,DAY(MA5)=1),MONTH(MA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MB4" s="156">
+      <c r="MB4" s="158">
         <f>IF(MB5="","",IF(OR(MB5=$M$3,DAY(MB5)=1),MONTH(MB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MC4" s="156">
+      <c r="MC4" s="158">
         <f>IF(MC5="","",IF(OR(MC5=$M$3,DAY(MC5)=1),MONTH(MC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MD4" s="156">
+      <c r="MD4" s="158">
         <f>IF(MD5="","",IF(OR(MD5=$M$3,DAY(MD5)=1),MONTH(MD5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ME4" s="156">
+      <c r="ME4" s="158">
         <f>IF(ME5="","",IF(OR(ME5=$M$3,DAY(ME5)=1),MONTH(ME5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MF4" s="156">
+      <c r="MF4" s="158">
         <f>IF(MF5="","",IF(OR(MF5=$M$3,DAY(MF5)=1),MONTH(MF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MG4" s="156">
+      <c r="MG4" s="158">
         <f>IF(MG5="","",IF(OR(MG5=$M$3,DAY(MG5)=1),MONTH(MG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MH4" s="156">
+      <c r="MH4" s="158">
         <f>IF(MH5="","",IF(OR(MH5=$M$3,DAY(MH5)=1),MONTH(MH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MI4" s="156">
+      <c r="MI4" s="158">
         <f>IF(MI5="","",IF(OR(MI5=$M$3,DAY(MI5)=1),MONTH(MI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MJ4" s="156">
+      <c r="MJ4" s="158">
         <f>IF(MJ5="","",IF(OR(MJ5=$M$3,DAY(MJ5)=1),MONTH(MJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MK4" s="156">
+      <c r="MK4" s="158">
         <f>IF(MK5="","",IF(OR(MK5=$M$3,DAY(MK5)=1),MONTH(MK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ML4" s="156">
+      <c r="ML4" s="158">
         <f>IF(ML5="","",IF(OR(ML5=$M$3,DAY(ML5)=1),MONTH(ML5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MM4" s="156">
+      <c r="MM4" s="158">
         <f>IF(MM5="","",IF(OR(MM5=$M$3,DAY(MM5)=1),MONTH(MM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MN4" s="156">
+      <c r="MN4" s="158">
         <f>IF(MN5="","",IF(OR(MN5=$M$3,DAY(MN5)=1),MONTH(MN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MO4" s="156">
+      <c r="MO4" s="158">
         <f>IF(MO5="","",IF(OR(MO5=$M$3,DAY(MO5)=1),MONTH(MO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MP4" s="156">
+      <c r="MP4" s="158">
         <f>IF(MP5="","",IF(OR(MP5=$M$3,DAY(MP5)=1),MONTH(MP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MQ4" s="156">
+      <c r="MQ4" s="158">
         <f>IF(MQ5="","",IF(OR(MQ5=$M$3,DAY(MQ5)=1),MONTH(MQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MR4" s="156">
+      <c r="MR4" s="158">
         <f>IF(MR5="","",IF(OR(MR5=$M$3,DAY(MR5)=1),MONTH(MR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MS4" s="156">
+      <c r="MS4" s="158">
         <f>IF(MS5="","",IF(OR(MS5=$M$3,DAY(MS5)=1),MONTH(MS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MT4" s="156">
+      <c r="MT4" s="158">
         <f>IF(MT5="","",IF(OR(MT5=$M$3,DAY(MT5)=1),MONTH(MT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MU4" s="156">
+      <c r="MU4" s="158">
         <f>IF(MU5="","",IF(OR(MU5=$M$3,DAY(MU5)=1),MONTH(MU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MV4" s="156">
+      <c r="MV4" s="158">
         <f>IF(MV5="","",IF(OR(MV5=$M$3,DAY(MV5)=1),MONTH(MV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MW4" s="156">
+      <c r="MW4" s="158">
         <f>IF(MW5="","",IF(OR(MW5=$M$3,DAY(MW5)=1),MONTH(MW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MX4" s="156">
+      <c r="MX4" s="158">
         <f>IF(MX5="","",IF(OR(MX5=$M$3,DAY(MX5)=1),MONTH(MX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MY4" s="156">
+      <c r="MY4" s="158">
         <f>IF(MY5="","",IF(OR(MY5=$M$3,DAY(MY5)=1),MONTH(MY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="MZ4" s="156">
+      <c r="MZ4" s="158">
         <f>IF(MZ5="","",IF(OR(MZ5=$M$3,DAY(MZ5)=1),MONTH(MZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NA4" s="156">
+      <c r="NA4" s="158">
         <f>IF(NA5="","",IF(OR(NA5=$M$3,DAY(NA5)=1),MONTH(NA5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NB4" s="156">
+      <c r="NB4" s="158">
         <f>IF(NB5="","",IF(OR(NB5=$M$3,DAY(NB5)=1),MONTH(NB5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NC4" s="156">
+      <c r="NC4" s="158">
         <f>IF(NC5="","",IF(OR(NC5=$M$3,DAY(NC5)=1),MONTH(NC5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="ND4" s="156">
+      <c r="ND4" s="158">
         <f>IF(ND5="","",IF(OR(ND5=$M$3,DAY(ND5)=1),MONTH(ND5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NE4" s="156">
+      <c r="NE4" s="158">
         <f>IF(NE5="","",IF(OR(NE5=$M$3,DAY(NE5)=1),MONTH(NE5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NF4" s="156">
+      <c r="NF4" s="158">
         <f>IF(NF5="","",IF(OR(NF5=$M$3,DAY(NF5)=1),MONTH(NF5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NG4" s="156">
+      <c r="NG4" s="158">
         <f>IF(NG5="","",IF(OR(NG5=$M$3,DAY(NG5)=1),MONTH(NG5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NH4" s="156">
+      <c r="NH4" s="158">
         <f>IF(NH5="","",IF(OR(NH5=$M$3,DAY(NH5)=1),MONTH(NH5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NI4" s="156">
+      <c r="NI4" s="158">
         <f>IF(NI5="","",IF(OR(NI5=$M$3,DAY(NI5)=1),MONTH(NI5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NJ4" s="156">
+      <c r="NJ4" s="158">
         <f>IF(NJ5="","",IF(OR(NJ5=$M$3,DAY(NJ5)=1),MONTH(NJ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NK4" s="156">
+      <c r="NK4" s="158">
         <f>IF(NK5="","",IF(OR(NK5=$M$3,DAY(NK5)=1),MONTH(NK5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NL4" s="156">
+      <c r="NL4" s="158">
         <f>IF(NL5="","",IF(OR(NL5=$M$3,DAY(NL5)=1),MONTH(NL5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NM4" s="156">
+      <c r="NM4" s="158">
         <f>IF(NM5="","",IF(OR(NM5=$M$3,DAY(NM5)=1),MONTH(NM5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NN4" s="156">
+      <c r="NN4" s="158">
         <f>IF(NN5="","",IF(OR(NN5=$M$3,DAY(NN5)=1),MONTH(NN5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NO4" s="156">
+      <c r="NO4" s="158">
         <f>IF(NO5="","",IF(OR(NO5=$M$3,DAY(NO5)=1),MONTH(NO5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NP4" s="156">
+      <c r="NP4" s="158">
         <f>IF(NP5="","",IF(OR(NP5=$M$3,DAY(NP5)=1),MONTH(NP5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NQ4" s="156">
+      <c r="NQ4" s="158">
         <f>IF(NQ5="","",IF(OR(NQ5=$M$3,DAY(NQ5)=1),MONTH(NQ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NR4" s="156">
+      <c r="NR4" s="158">
         <f>IF(NR5="","",IF(OR(NR5=$M$3,DAY(NR5)=1),MONTH(NR5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NS4" s="156">
+      <c r="NS4" s="158">
         <f>IF(NS5="","",IF(OR(NS5=$M$3,DAY(NS5)=1),MONTH(NS5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NT4" s="156">
+      <c r="NT4" s="158">
         <f>IF(NT5="","",IF(OR(NT5=$M$3,DAY(NT5)=1),MONTH(NT5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NU4" s="156">
+      <c r="NU4" s="158">
         <f>IF(NU5="","",IF(OR(NU5=$M$3,DAY(NU5)=1),MONTH(NU5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NV4" s="156">
+      <c r="NV4" s="158">
         <f>IF(NV5="","",IF(OR(NV5=$M$3,DAY(NV5)=1),MONTH(NV5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NW4" s="156">
+      <c r="NW4" s="158">
         <f>IF(NW5="","",IF(OR(NW5=$M$3,DAY(NW5)=1),MONTH(NW5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NX4" s="156">
+      <c r="NX4" s="158">
         <f>IF(NX5="","",IF(OR(NX5=$M$3,DAY(NX5)=1),MONTH(NX5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NY4" s="156">
+      <c r="NY4" s="158">
         <f>IF(NY5="","",IF(OR(NY5=$M$3,DAY(NY5)=1),MONTH(NY5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="NZ4" s="156">
+      <c r="NZ4" s="158">
         <f>IF(NZ5="","",IF(OR(NZ5=$M$3,DAY(NZ5)=1),MONTH(NZ5)&amp;"월",""))</f>
         <v/>
       </c>
-      <c r="OA4" s="156">
+      <c r="OA4" s="158">
         <f>IF(OA5="","",IF(OR(OA5=$M$3,DAY(OA5)=1),MONTH(OA5)&amp;"월",""))</f>
         <v/>
       </c>
@@ -32350,1505 +32407,1505 @@
       <c r="I5" s="26" t="n"/>
       <c r="J5" s="26" t="n"/>
       <c r="K5" s="26" t="n"/>
-      <c r="L5" s="157" t="n"/>
-      <c r="M5" s="158" t="n"/>
+      <c r="L5" s="159" t="n"/>
+      <c r="M5" s="160" t="n"/>
       <c r="N5" s="26" t="n"/>
       <c r="O5" s="26" t="n"/>
-      <c r="P5" s="159" t="n"/>
+      <c r="P5" s="161" t="n"/>
       <c r="Q5" s="26" t="n"/>
       <c r="R5" s="26" t="n"/>
       <c r="S5" s="26" t="n"/>
       <c r="T5" s="26" t="n"/>
       <c r="U5" s="30" t="n"/>
-      <c r="V5" s="160">
+      <c r="V5" s="162">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="W5" s="160">
+      <c r="W5" s="162">
         <f>IF(OR(V5="",V5&gt;=$R$3),"",V5+1)</f>
         <v/>
       </c>
-      <c r="X5" s="160">
+      <c r="X5" s="162">
         <f>IF(OR(W5="",W5&gt;=$R$3),"",W5+1)</f>
         <v/>
       </c>
-      <c r="Y5" s="160">
+      <c r="Y5" s="162">
         <f>IF(OR(X5="",X5&gt;=$R$3),"",X5+1)</f>
         <v/>
       </c>
-      <c r="Z5" s="160">
+      <c r="Z5" s="162">
         <f>IF(OR(Y5="",Y5&gt;=$R$3),"",Y5+1)</f>
         <v/>
       </c>
-      <c r="AA5" s="160">
+      <c r="AA5" s="162">
         <f>IF(OR(Z5="",Z5&gt;=$R$3),"",Z5+1)</f>
         <v/>
       </c>
-      <c r="AB5" s="160">
+      <c r="AB5" s="162">
         <f>IF(OR(AA5="",AA5&gt;=$R$3),"",AA5+1)</f>
         <v/>
       </c>
-      <c r="AC5" s="160">
+      <c r="AC5" s="162">
         <f>IF(OR(AB5="",AB5&gt;=$R$3),"",AB5+1)</f>
         <v/>
       </c>
-      <c r="AD5" s="160">
+      <c r="AD5" s="162">
         <f>IF(OR(AC5="",AC5&gt;=$R$3),"",AC5+1)</f>
         <v/>
       </c>
-      <c r="AE5" s="160">
+      <c r="AE5" s="162">
         <f>IF(OR(AD5="",AD5&gt;=$R$3),"",AD5+1)</f>
         <v/>
       </c>
-      <c r="AF5" s="160">
+      <c r="AF5" s="162">
         <f>IF(OR(AE5="",AE5&gt;=$R$3),"",AE5+1)</f>
         <v/>
       </c>
-      <c r="AG5" s="160">
+      <c r="AG5" s="162">
         <f>IF(OR(AF5="",AF5&gt;=$R$3),"",AF5+1)</f>
         <v/>
       </c>
-      <c r="AH5" s="160">
+      <c r="AH5" s="162">
         <f>IF(OR(AG5="",AG5&gt;=$R$3),"",AG5+1)</f>
         <v/>
       </c>
-      <c r="AI5" s="160">
+      <c r="AI5" s="162">
         <f>IF(OR(AH5="",AH5&gt;=$R$3),"",AH5+1)</f>
         <v/>
       </c>
-      <c r="AJ5" s="160">
+      <c r="AJ5" s="162">
         <f>IF(OR(AI5="",AI5&gt;=$R$3),"",AI5+1)</f>
         <v/>
       </c>
-      <c r="AK5" s="160">
+      <c r="AK5" s="162">
         <f>IF(OR(AJ5="",AJ5&gt;=$R$3),"",AJ5+1)</f>
         <v/>
       </c>
-      <c r="AL5" s="160">
+      <c r="AL5" s="162">
         <f>IF(OR(AK5="",AK5&gt;=$R$3),"",AK5+1)</f>
         <v/>
       </c>
-      <c r="AM5" s="160">
+      <c r="AM5" s="162">
         <f>IF(OR(AL5="",AL5&gt;=$R$3),"",AL5+1)</f>
         <v/>
       </c>
-      <c r="AN5" s="160">
+      <c r="AN5" s="162">
         <f>IF(OR(AM5="",AM5&gt;=$R$3),"",AM5+1)</f>
         <v/>
       </c>
-      <c r="AO5" s="160">
+      <c r="AO5" s="162">
         <f>IF(OR(AN5="",AN5&gt;=$R$3),"",AN5+1)</f>
         <v/>
       </c>
-      <c r="AP5" s="160">
+      <c r="AP5" s="162">
         <f>IF(OR(AO5="",AO5&gt;=$R$3),"",AO5+1)</f>
         <v/>
       </c>
-      <c r="AQ5" s="160">
+      <c r="AQ5" s="162">
         <f>IF(OR(AP5="",AP5&gt;=$R$3),"",AP5+1)</f>
         <v/>
       </c>
-      <c r="AR5" s="160">
+      <c r="AR5" s="162">
         <f>IF(OR(AQ5="",AQ5&gt;=$R$3),"",AQ5+1)</f>
         <v/>
       </c>
-      <c r="AS5" s="160">
+      <c r="AS5" s="162">
         <f>IF(OR(AR5="",AR5&gt;=$R$3),"",AR5+1)</f>
         <v/>
       </c>
-      <c r="AT5" s="160">
+      <c r="AT5" s="162">
         <f>IF(OR(AS5="",AS5&gt;=$R$3),"",AS5+1)</f>
         <v/>
       </c>
-      <c r="AU5" s="160">
+      <c r="AU5" s="162">
         <f>IF(OR(AT5="",AT5&gt;=$R$3),"",AT5+1)</f>
         <v/>
       </c>
-      <c r="AV5" s="160">
+      <c r="AV5" s="162">
         <f>IF(OR(AU5="",AU5&gt;=$R$3),"",AU5+1)</f>
         <v/>
       </c>
-      <c r="AW5" s="160">
+      <c r="AW5" s="162">
         <f>IF(OR(AV5="",AV5&gt;=$R$3),"",AV5+1)</f>
         <v/>
       </c>
-      <c r="AX5" s="160">
+      <c r="AX5" s="162">
         <f>IF(OR(AW5="",AW5&gt;=$R$3),"",AW5+1)</f>
         <v/>
       </c>
-      <c r="AY5" s="160">
+      <c r="AY5" s="162">
         <f>IF(OR(AX5="",AX5&gt;=$R$3),"",AX5+1)</f>
         <v/>
       </c>
-      <c r="AZ5" s="160">
+      <c r="AZ5" s="162">
         <f>IF(OR(AY5="",AY5&gt;=$R$3),"",AY5+1)</f>
         <v/>
       </c>
-      <c r="BA5" s="160">
+      <c r="BA5" s="162">
         <f>IF(OR(AZ5="",AZ5&gt;=$R$3),"",AZ5+1)</f>
         <v/>
       </c>
-      <c r="BB5" s="160">
+      <c r="BB5" s="162">
         <f>IF(OR(BA5="",BA5&gt;=$R$3),"",BA5+1)</f>
         <v/>
       </c>
-      <c r="BC5" s="160">
+      <c r="BC5" s="162">
         <f>IF(OR(BB5="",BB5&gt;=$R$3),"",BB5+1)</f>
         <v/>
       </c>
-      <c r="BD5" s="160">
+      <c r="BD5" s="162">
         <f>IF(OR(BC5="",BC5&gt;=$R$3),"",BC5+1)</f>
         <v/>
       </c>
-      <c r="BE5" s="160">
+      <c r="BE5" s="162">
         <f>IF(OR(BD5="",BD5&gt;=$R$3),"",BD5+1)</f>
         <v/>
       </c>
-      <c r="BF5" s="160">
+      <c r="BF5" s="162">
         <f>IF(OR(BE5="",BE5&gt;=$R$3),"",BE5+1)</f>
         <v/>
       </c>
-      <c r="BG5" s="160">
+      <c r="BG5" s="162">
         <f>IF(OR(BF5="",BF5&gt;=$R$3),"",BF5+1)</f>
         <v/>
       </c>
-      <c r="BH5" s="160">
+      <c r="BH5" s="162">
         <f>IF(OR(BG5="",BG5&gt;=$R$3),"",BG5+1)</f>
         <v/>
       </c>
-      <c r="BI5" s="160">
+      <c r="BI5" s="162">
         <f>IF(OR(BH5="",BH5&gt;=$R$3),"",BH5+1)</f>
         <v/>
       </c>
-      <c r="BJ5" s="160">
+      <c r="BJ5" s="162">
         <f>IF(OR(BI5="",BI5&gt;=$R$3),"",BI5+1)</f>
         <v/>
       </c>
-      <c r="BK5" s="160">
+      <c r="BK5" s="162">
         <f>IF(OR(BJ5="",BJ5&gt;=$R$3),"",BJ5+1)</f>
         <v/>
       </c>
-      <c r="BL5" s="160">
+      <c r="BL5" s="162">
         <f>IF(OR(BK5="",BK5&gt;=$R$3),"",BK5+1)</f>
         <v/>
       </c>
-      <c r="BM5" s="160">
+      <c r="BM5" s="162">
         <f>IF(OR(BL5="",BL5&gt;=$R$3),"",BL5+1)</f>
         <v/>
       </c>
-      <c r="BN5" s="160">
+      <c r="BN5" s="162">
         <f>IF(OR(BM5="",BM5&gt;=$R$3),"",BM5+1)</f>
         <v/>
       </c>
-      <c r="BO5" s="160">
+      <c r="BO5" s="162">
         <f>IF(OR(BN5="",BN5&gt;=$R$3),"",BN5+1)</f>
         <v/>
       </c>
-      <c r="BP5" s="160">
+      <c r="BP5" s="162">
         <f>IF(OR(BO5="",BO5&gt;=$R$3),"",BO5+1)</f>
         <v/>
       </c>
-      <c r="BQ5" s="160">
+      <c r="BQ5" s="162">
         <f>IF(OR(BP5="",BP5&gt;=$R$3),"",BP5+1)</f>
         <v/>
       </c>
-      <c r="BR5" s="160">
+      <c r="BR5" s="162">
         <f>IF(OR(BQ5="",BQ5&gt;=$R$3),"",BQ5+1)</f>
         <v/>
       </c>
-      <c r="BS5" s="160">
+      <c r="BS5" s="162">
         <f>IF(OR(BR5="",BR5&gt;=$R$3),"",BR5+1)</f>
         <v/>
       </c>
-      <c r="BT5" s="160">
+      <c r="BT5" s="162">
         <f>IF(OR(BS5="",BS5&gt;=$R$3),"",BS5+1)</f>
         <v/>
       </c>
-      <c r="BU5" s="160">
+      <c r="BU5" s="162">
         <f>IF(OR(BT5="",BT5&gt;=$R$3),"",BT5+1)</f>
         <v/>
       </c>
-      <c r="BV5" s="160">
+      <c r="BV5" s="162">
         <f>IF(OR(BU5="",BU5&gt;=$R$3),"",BU5+1)</f>
         <v/>
       </c>
-      <c r="BW5" s="160">
+      <c r="BW5" s="162">
         <f>IF(OR(BV5="",BV5&gt;=$R$3),"",BV5+1)</f>
         <v/>
       </c>
-      <c r="BX5" s="160">
+      <c r="BX5" s="162">
         <f>IF(OR(BW5="",BW5&gt;=$R$3),"",BW5+1)</f>
         <v/>
       </c>
-      <c r="BY5" s="160">
+      <c r="BY5" s="162">
         <f>IF(OR(BX5="",BX5&gt;=$R$3),"",BX5+1)</f>
         <v/>
       </c>
-      <c r="BZ5" s="160">
+      <c r="BZ5" s="162">
         <f>IF(OR(BY5="",BY5&gt;=$R$3),"",BY5+1)</f>
         <v/>
       </c>
-      <c r="CA5" s="160">
+      <c r="CA5" s="162">
         <f>IF(OR(BZ5="",BZ5&gt;=$R$3),"",BZ5+1)</f>
         <v/>
       </c>
-      <c r="CB5" s="160">
+      <c r="CB5" s="162">
         <f>IF(OR(CA5="",CA5&gt;=$R$3),"",CA5+1)</f>
         <v/>
       </c>
-      <c r="CC5" s="160">
+      <c r="CC5" s="162">
         <f>IF(OR(CB5="",CB5&gt;=$R$3),"",CB5+1)</f>
         <v/>
       </c>
-      <c r="CD5" s="160">
+      <c r="CD5" s="162">
         <f>IF(OR(CC5="",CC5&gt;=$R$3),"",CC5+1)</f>
         <v/>
       </c>
-      <c r="CE5" s="160">
+      <c r="CE5" s="162">
         <f>IF(OR(CD5="",CD5&gt;=$R$3),"",CD5+1)</f>
         <v/>
       </c>
-      <c r="CF5" s="160">
+      <c r="CF5" s="162">
         <f>IF(OR(CE5="",CE5&gt;=$R$3),"",CE5+1)</f>
         <v/>
       </c>
-      <c r="CG5" s="160">
+      <c r="CG5" s="162">
         <f>IF(OR(CF5="",CF5&gt;=$R$3),"",CF5+1)</f>
         <v/>
       </c>
-      <c r="CH5" s="160">
+      <c r="CH5" s="162">
         <f>IF(OR(CG5="",CG5&gt;=$R$3),"",CG5+1)</f>
         <v/>
       </c>
-      <c r="CI5" s="160">
+      <c r="CI5" s="162">
         <f>IF(OR(CH5="",CH5&gt;=$R$3),"",CH5+1)</f>
         <v/>
       </c>
-      <c r="CJ5" s="160">
+      <c r="CJ5" s="162">
         <f>IF(OR(CI5="",CI5&gt;=$R$3),"",CI5+1)</f>
         <v/>
       </c>
-      <c r="CK5" s="160">
+      <c r="CK5" s="162">
         <f>IF(OR(CJ5="",CJ5&gt;=$R$3),"",CJ5+1)</f>
         <v/>
       </c>
-      <c r="CL5" s="160">
+      <c r="CL5" s="162">
         <f>IF(OR(CK5="",CK5&gt;=$R$3),"",CK5+1)</f>
         <v/>
       </c>
-      <c r="CM5" s="160">
+      <c r="CM5" s="162">
         <f>IF(OR(CL5="",CL5&gt;=$R$3),"",CL5+1)</f>
         <v/>
       </c>
-      <c r="CN5" s="160">
+      <c r="CN5" s="162">
         <f>IF(OR(CM5="",CM5&gt;=$R$3),"",CM5+1)</f>
         <v/>
       </c>
-      <c r="CO5" s="160">
+      <c r="CO5" s="162">
         <f>IF(OR(CN5="",CN5&gt;=$R$3),"",CN5+1)</f>
         <v/>
       </c>
-      <c r="CP5" s="160">
+      <c r="CP5" s="162">
         <f>IF(OR(CO5="",CO5&gt;=$R$3),"",CO5+1)</f>
         <v/>
       </c>
-      <c r="CQ5" s="160">
+      <c r="CQ5" s="162">
         <f>IF(OR(CP5="",CP5&gt;=$R$3),"",CP5+1)</f>
         <v/>
       </c>
-      <c r="CR5" s="160">
+      <c r="CR5" s="162">
         <f>IF(OR(CQ5="",CQ5&gt;=$R$3),"",CQ5+1)</f>
         <v/>
       </c>
-      <c r="CS5" s="160">
+      <c r="CS5" s="162">
         <f>IF(OR(CR5="",CR5&gt;=$R$3),"",CR5+1)</f>
         <v/>
       </c>
-      <c r="CT5" s="160">
+      <c r="CT5" s="162">
         <f>IF(OR(CS5="",CS5&gt;=$R$3),"",CS5+1)</f>
         <v/>
       </c>
-      <c r="CU5" s="160">
+      <c r="CU5" s="162">
         <f>IF(OR(CT5="",CT5&gt;=$R$3),"",CT5+1)</f>
         <v/>
       </c>
-      <c r="CV5" s="160">
+      <c r="CV5" s="162">
         <f>IF(OR(CU5="",CU5&gt;=$R$3),"",CU5+1)</f>
         <v/>
       </c>
-      <c r="CW5" s="160">
+      <c r="CW5" s="162">
         <f>IF(OR(CV5="",CV5&gt;=$R$3),"",CV5+1)</f>
         <v/>
       </c>
-      <c r="CX5" s="160">
+      <c r="CX5" s="162">
         <f>IF(OR(CW5="",CW5&gt;=$R$3),"",CW5+1)</f>
         <v/>
       </c>
-      <c r="CY5" s="160">
+      <c r="CY5" s="162">
         <f>IF(OR(CX5="",CX5&gt;=$R$3),"",CX5+1)</f>
         <v/>
       </c>
-      <c r="CZ5" s="160">
+      <c r="CZ5" s="162">
         <f>IF(OR(CY5="",CY5&gt;=$R$3),"",CY5+1)</f>
         <v/>
       </c>
-      <c r="DA5" s="160">
+      <c r="DA5" s="162">
         <f>IF(OR(CZ5="",CZ5&gt;=$R$3),"",CZ5+1)</f>
         <v/>
       </c>
-      <c r="DB5" s="160">
+      <c r="DB5" s="162">
         <f>IF(OR(DA5="",DA5&gt;=$R$3),"",DA5+1)</f>
         <v/>
       </c>
-      <c r="DC5" s="160">
+      <c r="DC5" s="162">
         <f>IF(OR(DB5="",DB5&gt;=$R$3),"",DB5+1)</f>
         <v/>
       </c>
-      <c r="DD5" s="160">
+      <c r="DD5" s="162">
         <f>IF(OR(DC5="",DC5&gt;=$R$3),"",DC5+1)</f>
         <v/>
       </c>
-      <c r="DE5" s="160">
+      <c r="DE5" s="162">
         <f>IF(OR(DD5="",DD5&gt;=$R$3),"",DD5+1)</f>
         <v/>
       </c>
-      <c r="DF5" s="160">
+      <c r="DF5" s="162">
         <f>IF(OR(DE5="",DE5&gt;=$R$3),"",DE5+1)</f>
         <v/>
       </c>
-      <c r="DG5" s="160">
+      <c r="DG5" s="162">
         <f>IF(OR(DF5="",DF5&gt;=$R$3),"",DF5+1)</f>
         <v/>
       </c>
-      <c r="DH5" s="160">
+      <c r="DH5" s="162">
         <f>IF(OR(DG5="",DG5&gt;=$R$3),"",DG5+1)</f>
         <v/>
       </c>
-      <c r="DI5" s="160">
+      <c r="DI5" s="162">
         <f>IF(OR(DH5="",DH5&gt;=$R$3),"",DH5+1)</f>
         <v/>
       </c>
-      <c r="DJ5" s="160">
+      <c r="DJ5" s="162">
         <f>IF(OR(DI5="",DI5&gt;=$R$3),"",DI5+1)</f>
         <v/>
       </c>
-      <c r="DK5" s="160">
+      <c r="DK5" s="162">
         <f>IF(OR(DJ5="",DJ5&gt;=$R$3),"",DJ5+1)</f>
         <v/>
       </c>
-      <c r="DL5" s="160">
+      <c r="DL5" s="162">
         <f>IF(OR(DK5="",DK5&gt;=$R$3),"",DK5+1)</f>
         <v/>
       </c>
-      <c r="DM5" s="160">
+      <c r="DM5" s="162">
         <f>IF(OR(DL5="",DL5&gt;=$R$3),"",DL5+1)</f>
         <v/>
       </c>
-      <c r="DN5" s="160">
+      <c r="DN5" s="162">
         <f>IF(OR(DM5="",DM5&gt;=$R$3),"",DM5+1)</f>
         <v/>
       </c>
-      <c r="DO5" s="160">
+      <c r="DO5" s="162">
         <f>IF(OR(DN5="",DN5&gt;=$R$3),"",DN5+1)</f>
         <v/>
       </c>
-      <c r="DP5" s="160">
+      <c r="DP5" s="162">
         <f>IF(OR(DO5="",DO5&gt;=$R$3),"",DO5+1)</f>
         <v/>
       </c>
-      <c r="DQ5" s="160">
+      <c r="DQ5" s="162">
         <f>IF(OR(DP5="",DP5&gt;=$R$3),"",DP5+1)</f>
         <v/>
       </c>
-      <c r="DR5" s="160">
+      <c r="DR5" s="162">
         <f>IF(OR(DQ5="",DQ5&gt;=$R$3),"",DQ5+1)</f>
         <v/>
       </c>
-      <c r="DS5" s="160">
+      <c r="DS5" s="162">
         <f>IF(OR(DR5="",DR5&gt;=$R$3),"",DR5+1)</f>
         <v/>
       </c>
-      <c r="DT5" s="160">
+      <c r="DT5" s="162">
         <f>IF(OR(DS5="",DS5&gt;=$R$3),"",DS5+1)</f>
         <v/>
       </c>
-      <c r="DU5" s="160">
+      <c r="DU5" s="162">
         <f>IF(OR(DT5="",DT5&gt;=$R$3),"",DT5+1)</f>
         <v/>
       </c>
-      <c r="DV5" s="160">
+      <c r="DV5" s="162">
         <f>IF(OR(DU5="",DU5&gt;=$R$3),"",DU5+1)</f>
         <v/>
       </c>
-      <c r="DW5" s="160">
+      <c r="DW5" s="162">
         <f>IF(OR(DV5="",DV5&gt;=$R$3),"",DV5+1)</f>
         <v/>
       </c>
-      <c r="DX5" s="160">
+      <c r="DX5" s="162">
         <f>IF(OR(DW5="",DW5&gt;=$R$3),"",DW5+1)</f>
         <v/>
       </c>
-      <c r="DY5" s="160">
+      <c r="DY5" s="162">
         <f>IF(OR(DX5="",DX5&gt;=$R$3),"",DX5+1)</f>
         <v/>
       </c>
-      <c r="DZ5" s="160">
+      <c r="DZ5" s="162">
         <f>IF(OR(DY5="",DY5&gt;=$R$3),"",DY5+1)</f>
         <v/>
       </c>
-      <c r="EA5" s="160">
+      <c r="EA5" s="162">
         <f>IF(OR(DZ5="",DZ5&gt;=$R$3),"",DZ5+1)</f>
         <v/>
       </c>
-      <c r="EB5" s="160">
+      <c r="EB5" s="162">
         <f>IF(OR(EA5="",EA5&gt;=$R$3),"",EA5+1)</f>
         <v/>
       </c>
-      <c r="EC5" s="160">
+      <c r="EC5" s="162">
         <f>IF(OR(EB5="",EB5&gt;=$R$3),"",EB5+1)</f>
         <v/>
       </c>
-      <c r="ED5" s="160">
+      <c r="ED5" s="162">
         <f>IF(OR(EC5="",EC5&gt;=$R$3),"",EC5+1)</f>
         <v/>
       </c>
-      <c r="EE5" s="160">
+      <c r="EE5" s="162">
         <f>IF(OR(ED5="",ED5&gt;=$R$3),"",ED5+1)</f>
         <v/>
       </c>
-      <c r="EF5" s="160">
+      <c r="EF5" s="162">
         <f>IF(OR(EE5="",EE5&gt;=$R$3),"",EE5+1)</f>
         <v/>
       </c>
-      <c r="EG5" s="160">
+      <c r="EG5" s="162">
         <f>IF(OR(EF5="",EF5&gt;=$R$3),"",EF5+1)</f>
         <v/>
       </c>
-      <c r="EH5" s="160">
+      <c r="EH5" s="162">
         <f>IF(OR(EG5="",EG5&gt;=$R$3),"",EG5+1)</f>
         <v/>
       </c>
-      <c r="EI5" s="160">
+      <c r="EI5" s="162">
         <f>IF(OR(EH5="",EH5&gt;=$R$3),"",EH5+1)</f>
         <v/>
       </c>
-      <c r="EJ5" s="160">
+      <c r="EJ5" s="162">
         <f>IF(OR(EI5="",EI5&gt;=$R$3),"",EI5+1)</f>
         <v/>
       </c>
-      <c r="EK5" s="160">
+      <c r="EK5" s="162">
         <f>IF(OR(EJ5="",EJ5&gt;=$R$3),"",EJ5+1)</f>
         <v/>
       </c>
-      <c r="EL5" s="160">
+      <c r="EL5" s="162">
         <f>IF(OR(EK5="",EK5&gt;=$R$3),"",EK5+1)</f>
         <v/>
       </c>
-      <c r="EM5" s="160">
+      <c r="EM5" s="162">
         <f>IF(OR(EL5="",EL5&gt;=$R$3),"",EL5+1)</f>
         <v/>
       </c>
-      <c r="EN5" s="161">
+      <c r="EN5" s="163">
         <f>IF(OR(EM5="",EM5&gt;=$R$3),"",EM5+1)</f>
         <v/>
       </c>
-      <c r="EO5" s="161">
+      <c r="EO5" s="163">
         <f>IF(OR(EN5="",EN5&gt;=$R$3),"",EN5+1)</f>
         <v/>
       </c>
-      <c r="EP5" s="161">
+      <c r="EP5" s="163">
         <f>IF(OR(EO5="",EO5&gt;=$R$3),"",EO5+1)</f>
         <v/>
       </c>
-      <c r="EQ5" s="161">
+      <c r="EQ5" s="163">
         <f>IF(OR(EP5="",EP5&gt;=$R$3),"",EP5+1)</f>
         <v/>
       </c>
-      <c r="ER5" s="161">
+      <c r="ER5" s="163">
         <f>IF(OR(EQ5="",EQ5&gt;=$R$3),"",EQ5+1)</f>
         <v/>
       </c>
-      <c r="ES5" s="161">
+      <c r="ES5" s="163">
         <f>IF(OR(ER5="",ER5&gt;=$R$3),"",ER5+1)</f>
         <v/>
       </c>
-      <c r="ET5" s="161">
+      <c r="ET5" s="163">
         <f>IF(OR(ES5="",ES5&gt;=$R$3),"",ES5+1)</f>
         <v/>
       </c>
-      <c r="EU5" s="161">
+      <c r="EU5" s="163">
         <f>IF(OR(ET5="",ET5&gt;=$R$3),"",ET5+1)</f>
         <v/>
       </c>
-      <c r="EV5" s="161">
+      <c r="EV5" s="163">
         <f>IF(OR(EU5="",EU5&gt;=$R$3),"",EU5+1)</f>
         <v/>
       </c>
-      <c r="EW5" s="161">
+      <c r="EW5" s="163">
         <f>IF(OR(EV5="",EV5&gt;=$R$3),"",EV5+1)</f>
         <v/>
       </c>
-      <c r="EX5" s="161">
+      <c r="EX5" s="163">
         <f>IF(OR(EW5="",EW5&gt;=$R$3),"",EW5+1)</f>
         <v/>
       </c>
-      <c r="EY5" s="161">
+      <c r="EY5" s="163">
         <f>IF(OR(EX5="",EX5&gt;=$R$3),"",EX5+1)</f>
         <v/>
       </c>
-      <c r="EZ5" s="161">
+      <c r="EZ5" s="163">
         <f>IF(OR(EY5="",EY5&gt;=$R$3),"",EY5+1)</f>
         <v/>
       </c>
-      <c r="FA5" s="161">
+      <c r="FA5" s="163">
         <f>IF(OR(EZ5="",EZ5&gt;=$R$3),"",EZ5+1)</f>
         <v/>
       </c>
-      <c r="FB5" s="161">
+      <c r="FB5" s="163">
         <f>IF(OR(FA5="",FA5&gt;=$R$3),"",FA5+1)</f>
         <v/>
       </c>
-      <c r="FC5" s="161">
+      <c r="FC5" s="163">
         <f>IF(OR(FB5="",FB5&gt;=$R$3),"",FB5+1)</f>
         <v/>
       </c>
-      <c r="FD5" s="161">
+      <c r="FD5" s="163">
         <f>IF(OR(FC5="",FC5&gt;=$R$3),"",FC5+1)</f>
         <v/>
       </c>
-      <c r="FE5" s="161">
+      <c r="FE5" s="163">
         <f>IF(OR(FD5="",FD5&gt;=$R$3),"",FD5+1)</f>
         <v/>
       </c>
-      <c r="FF5" s="161">
+      <c r="FF5" s="163">
         <f>IF(OR(FE5="",FE5&gt;=$R$3),"",FE5+1)</f>
         <v/>
       </c>
-      <c r="FG5" s="161">
+      <c r="FG5" s="163">
         <f>IF(OR(FF5="",FF5&gt;=$R$3),"",FF5+1)</f>
         <v/>
       </c>
-      <c r="FH5" s="161">
+      <c r="FH5" s="163">
         <f>IF(OR(FG5="",FG5&gt;=$R$3),"",FG5+1)</f>
         <v/>
       </c>
-      <c r="FI5" s="161">
+      <c r="FI5" s="163">
         <f>IF(OR(FH5="",FH5&gt;=$R$3),"",FH5+1)</f>
         <v/>
       </c>
-      <c r="FJ5" s="161">
+      <c r="FJ5" s="163">
         <f>IF(OR(FI5="",FI5&gt;=$R$3),"",FI5+1)</f>
         <v/>
       </c>
-      <c r="FK5" s="161">
+      <c r="FK5" s="163">
         <f>IF(OR(FJ5="",FJ5&gt;=$R$3),"",FJ5+1)</f>
         <v/>
       </c>
-      <c r="FL5" s="161">
+      <c r="FL5" s="163">
         <f>IF(OR(FK5="",FK5&gt;=$R$3),"",FK5+1)</f>
         <v/>
       </c>
-      <c r="FM5" s="161">
+      <c r="FM5" s="163">
         <f>IF(OR(FL5="",FL5&gt;=$R$3),"",FL5+1)</f>
         <v/>
       </c>
-      <c r="FN5" s="161">
+      <c r="FN5" s="163">
         <f>IF(OR(FM5="",FM5&gt;=$R$3),"",FM5+1)</f>
         <v/>
       </c>
-      <c r="FO5" s="161">
+      <c r="FO5" s="163">
         <f>IF(OR(FN5="",FN5&gt;=$R$3),"",FN5+1)</f>
         <v/>
       </c>
-      <c r="FP5" s="161">
+      <c r="FP5" s="163">
         <f>IF(OR(FO5="",FO5&gt;=$R$3),"",FO5+1)</f>
         <v/>
       </c>
-      <c r="FQ5" s="161">
+      <c r="FQ5" s="163">
         <f>IF(OR(FP5="",FP5&gt;=$R$3),"",FP5+1)</f>
         <v/>
       </c>
-      <c r="FR5" s="161">
+      <c r="FR5" s="163">
         <f>IF(OR(FQ5="",FQ5&gt;=$R$3),"",FQ5+1)</f>
         <v/>
       </c>
-      <c r="FS5" s="161">
+      <c r="FS5" s="163">
         <f>IF(OR(FR5="",FR5&gt;=$R$3),"",FR5+1)</f>
         <v/>
       </c>
-      <c r="FT5" s="161">
+      <c r="FT5" s="163">
         <f>IF(OR(FS5="",FS5&gt;=$R$3),"",FS5+1)</f>
         <v/>
       </c>
-      <c r="FU5" s="161">
+      <c r="FU5" s="163">
         <f>IF(OR(FT5="",FT5&gt;=$R$3),"",FT5+1)</f>
         <v/>
       </c>
-      <c r="FV5" s="161">
+      <c r="FV5" s="163">
         <f>IF(OR(FU5="",FU5&gt;=$R$3),"",FU5+1)</f>
         <v/>
       </c>
-      <c r="FW5" s="161">
+      <c r="FW5" s="163">
         <f>IF(OR(FV5="",FV5&gt;=$R$3),"",FV5+1)</f>
         <v/>
       </c>
-      <c r="FX5" s="161">
+      <c r="FX5" s="163">
         <f>IF(OR(FW5="",FW5&gt;=$R$3),"",FW5+1)</f>
         <v/>
       </c>
-      <c r="FY5" s="161">
+      <c r="FY5" s="163">
         <f>IF(OR(FX5="",FX5&gt;=$R$3),"",FX5+1)</f>
         <v/>
       </c>
-      <c r="FZ5" s="161">
+      <c r="FZ5" s="163">
         <f>IF(OR(FY5="",FY5&gt;=$R$3),"",FY5+1)</f>
         <v/>
       </c>
-      <c r="GA5" s="161">
+      <c r="GA5" s="163">
         <f>IF(OR(FZ5="",FZ5&gt;=$R$3),"",FZ5+1)</f>
         <v/>
       </c>
-      <c r="GB5" s="161">
+      <c r="GB5" s="163">
         <f>IF(OR(GA5="",GA5&gt;=$R$3),"",GA5+1)</f>
         <v/>
       </c>
-      <c r="GC5" s="161">
+      <c r="GC5" s="163">
         <f>IF(OR(GB5="",GB5&gt;=$R$3),"",GB5+1)</f>
         <v/>
       </c>
-      <c r="GD5" s="161">
+      <c r="GD5" s="163">
         <f>IF(OR(GC5="",GC5&gt;=$R$3),"",GC5+1)</f>
         <v/>
       </c>
-      <c r="GE5" s="161">
+      <c r="GE5" s="163">
         <f>IF(OR(GD5="",GD5&gt;=$R$3),"",GD5+1)</f>
         <v/>
       </c>
-      <c r="GF5" s="161">
+      <c r="GF5" s="163">
         <f>IF(OR(GE5="",GE5&gt;=$R$3),"",GE5+1)</f>
         <v/>
       </c>
-      <c r="GG5" s="161">
+      <c r="GG5" s="163">
         <f>IF(OR(GF5="",GF5&gt;=$R$3),"",GF5+1)</f>
         <v/>
       </c>
-      <c r="GH5" s="161">
+      <c r="GH5" s="163">
         <f>IF(OR(GG5="",GG5&gt;=$R$3),"",GG5+1)</f>
         <v/>
       </c>
-      <c r="GI5" s="161">
+      <c r="GI5" s="163">
         <f>IF(OR(GH5="",GH5&gt;=$R$3),"",GH5+1)</f>
         <v/>
       </c>
-      <c r="GJ5" s="161">
+      <c r="GJ5" s="163">
         <f>IF(OR(GI5="",GI5&gt;=$R$3),"",GI5+1)</f>
         <v/>
       </c>
-      <c r="GK5" s="161">
+      <c r="GK5" s="163">
         <f>IF(OR(GJ5="",GJ5&gt;=$R$3),"",GJ5+1)</f>
         <v/>
       </c>
-      <c r="GL5" s="161">
+      <c r="GL5" s="163">
         <f>IF(OR(GK5="",GK5&gt;=$R$3),"",GK5+1)</f>
         <v/>
       </c>
-      <c r="GM5" s="161">
+      <c r="GM5" s="163">
         <f>IF(OR(GL5="",GL5&gt;=$R$3),"",GL5+1)</f>
         <v/>
       </c>
-      <c r="GN5" s="161">
+      <c r="GN5" s="163">
         <f>IF(OR(GM5="",GM5&gt;=$R$3),"",GM5+1)</f>
         <v/>
       </c>
-      <c r="GO5" s="161">
+      <c r="GO5" s="163">
         <f>IF(OR(GN5="",GN5&gt;=$R$3),"",GN5+1)</f>
         <v/>
       </c>
-      <c r="GP5" s="161">
+      <c r="GP5" s="163">
         <f>IF(OR(GO5="",GO5&gt;=$R$3),"",GO5+1)</f>
         <v/>
       </c>
-      <c r="GQ5" s="161">
+      <c r="GQ5" s="163">
         <f>IF(OR(GP5="",GP5&gt;=$R$3),"",GP5+1)</f>
         <v/>
       </c>
-      <c r="GR5" s="161">
+      <c r="GR5" s="163">
         <f>IF(OR(GQ5="",GQ5&gt;=$R$3),"",GQ5+1)</f>
         <v/>
       </c>
-      <c r="GS5" s="161">
+      <c r="GS5" s="163">
         <f>IF(OR(GR5="",GR5&gt;=$R$3),"",GR5+1)</f>
         <v/>
       </c>
-      <c r="GT5" s="161">
+      <c r="GT5" s="163">
         <f>IF(OR(GS5="",GS5&gt;=$R$3),"",GS5+1)</f>
         <v/>
       </c>
-      <c r="GU5" s="161">
+      <c r="GU5" s="163">
         <f>IF(OR(GT5="",GT5&gt;=$R$3),"",GT5+1)</f>
         <v/>
       </c>
-      <c r="GV5" s="161">
+      <c r="GV5" s="163">
         <f>IF(OR(GU5="",GU5&gt;=$R$3),"",GU5+1)</f>
         <v/>
       </c>
-      <c r="GW5" s="161">
+      <c r="GW5" s="163">
         <f>IF(OR(GV5="",GV5&gt;=$R$3),"",GV5+1)</f>
         <v/>
       </c>
-      <c r="GX5" s="161">
+      <c r="GX5" s="163">
         <f>IF(OR(GW5="",GW5&gt;=$R$3),"",GW5+1)</f>
         <v/>
       </c>
-      <c r="GY5" s="161">
+      <c r="GY5" s="163">
         <f>IF(OR(GX5="",GX5&gt;=$R$3),"",GX5+1)</f>
         <v/>
       </c>
-      <c r="GZ5" s="161">
+      <c r="GZ5" s="163">
         <f>IF(OR(GY5="",GY5&gt;=$R$3),"",GY5+1)</f>
         <v/>
       </c>
-      <c r="HA5" s="161">
+      <c r="HA5" s="163">
         <f>IF(OR(GZ5="",GZ5&gt;=$R$3),"",GZ5+1)</f>
         <v/>
       </c>
-      <c r="HB5" s="161">
+      <c r="HB5" s="163">
         <f>IF(OR(HA5="",HA5&gt;=$R$3),"",HA5+1)</f>
         <v/>
       </c>
-      <c r="HC5" s="161">
+      <c r="HC5" s="163">
         <f>IF(OR(HB5="",HB5&gt;=$R$3),"",HB5+1)</f>
         <v/>
       </c>
-      <c r="HD5" s="161">
+      <c r="HD5" s="163">
         <f>IF(OR(HC5="",HC5&gt;=$R$3),"",HC5+1)</f>
         <v/>
       </c>
-      <c r="HE5" s="161">
+      <c r="HE5" s="163">
         <f>IF(OR(HD5="",HD5&gt;=$R$3),"",HD5+1)</f>
         <v/>
       </c>
-      <c r="HF5" s="161">
+      <c r="HF5" s="163">
         <f>IF(OR(HE5="",HE5&gt;=$R$3),"",HE5+1)</f>
         <v/>
       </c>
-      <c r="HG5" s="161">
+      <c r="HG5" s="163">
         <f>IF(OR(HF5="",HF5&gt;=$R$3),"",HF5+1)</f>
         <v/>
       </c>
-      <c r="HH5" s="161">
+      <c r="HH5" s="163">
         <f>IF(OR(HG5="",HG5&gt;=$R$3),"",HG5+1)</f>
         <v/>
       </c>
-      <c r="HI5" s="161">
+      <c r="HI5" s="163">
         <f>IF(OR(HH5="",HH5&gt;=$R$3),"",HH5+1)</f>
         <v/>
       </c>
-      <c r="HJ5" s="161">
+      <c r="HJ5" s="163">
         <f>IF(OR(HI5="",HI5&gt;=$R$3),"",HI5+1)</f>
         <v/>
       </c>
-      <c r="HK5" s="161">
+      <c r="HK5" s="163">
         <f>IF(OR(HJ5="",HJ5&gt;=$R$3),"",HJ5+1)</f>
         <v/>
       </c>
-      <c r="HL5" s="161">
+      <c r="HL5" s="163">
         <f>IF(OR(HK5="",HK5&gt;=$R$3),"",HK5+1)</f>
         <v/>
       </c>
-      <c r="HM5" s="161">
+      <c r="HM5" s="163">
         <f>IF(OR(HL5="",HL5&gt;=$R$3),"",HL5+1)</f>
         <v/>
       </c>
-      <c r="HN5" s="161">
+      <c r="HN5" s="163">
         <f>IF(OR(HM5="",HM5&gt;=$R$3),"",HM5+1)</f>
         <v/>
       </c>
-      <c r="HO5" s="161">
+      <c r="HO5" s="163">
         <f>IF(OR(HN5="",HN5&gt;=$R$3),"",HN5+1)</f>
         <v/>
       </c>
-      <c r="HP5" s="161">
+      <c r="HP5" s="163">
         <f>IF(OR(HO5="",HO5&gt;=$R$3),"",HO5+1)</f>
         <v/>
       </c>
-      <c r="HQ5" s="161">
+      <c r="HQ5" s="163">
         <f>IF(OR(HP5="",HP5&gt;=$R$3),"",HP5+1)</f>
         <v/>
       </c>
-      <c r="HR5" s="161">
+      <c r="HR5" s="163">
         <f>IF(OR(HQ5="",HQ5&gt;=$R$3),"",HQ5+1)</f>
         <v/>
       </c>
-      <c r="HS5" s="161">
+      <c r="HS5" s="163">
         <f>IF(OR(HR5="",HR5&gt;=$R$3),"",HR5+1)</f>
         <v/>
       </c>
-      <c r="HT5" s="161">
+      <c r="HT5" s="163">
         <f>IF(OR(HS5="",HS5&gt;=$R$3),"",HS5+1)</f>
         <v/>
       </c>
-      <c r="HU5" s="161">
+      <c r="HU5" s="163">
         <f>IF(OR(HT5="",HT5&gt;=$R$3),"",HT5+1)</f>
         <v/>
       </c>
-      <c r="HV5" s="161">
+      <c r="HV5" s="163">
         <f>IF(OR(HU5="",HU5&gt;=$R$3),"",HU5+1)</f>
         <v/>
       </c>
-      <c r="HW5" s="161">
+      <c r="HW5" s="163">
         <f>IF(OR(HV5="",HV5&gt;=$R$3),"",HV5+1)</f>
         <v/>
       </c>
-      <c r="HX5" s="161">
+      <c r="HX5" s="163">
         <f>IF(OR(HW5="",HW5&gt;=$R$3),"",HW5+1)</f>
         <v/>
       </c>
-      <c r="HY5" s="161">
+      <c r="HY5" s="163">
         <f>IF(OR(HX5="",HX5&gt;=$R$3),"",HX5+1)</f>
         <v/>
       </c>
-      <c r="HZ5" s="161">
+      <c r="HZ5" s="163">
         <f>IF(OR(HY5="",HY5&gt;=$R$3),"",HY5+1)</f>
         <v/>
       </c>
-      <c r="IA5" s="161">
+      <c r="IA5" s="163">
         <f>IF(OR(HZ5="",HZ5&gt;=$R$3),"",HZ5+1)</f>
         <v/>
       </c>
-      <c r="IB5" s="161">
+      <c r="IB5" s="163">
         <f>IF(OR(IA5="",IA5&gt;=$R$3),"",IA5+1)</f>
         <v/>
       </c>
-      <c r="IC5" s="161">
+      <c r="IC5" s="163">
         <f>IF(OR(IB5="",IB5&gt;=$R$3),"",IB5+1)</f>
         <v/>
       </c>
-      <c r="ID5" s="161">
+      <c r="ID5" s="163">
         <f>IF(OR(IC5="",IC5&gt;=$R$3),"",IC5+1)</f>
         <v/>
       </c>
-      <c r="IE5" s="161">
+      <c r="IE5" s="163">
         <f>IF(OR(ID5="",ID5&gt;=$R$3),"",ID5+1)</f>
         <v/>
       </c>
-      <c r="IF5" s="161">
+      <c r="IF5" s="163">
         <f>IF(OR(IE5="",IE5&gt;=$R$3),"",IE5+1)</f>
         <v/>
       </c>
-      <c r="IG5" s="161">
+      <c r="IG5" s="163">
         <f>IF(OR(IF5="",IF5&gt;=$R$3),"",IF5+1)</f>
         <v/>
       </c>
-      <c r="IH5" s="161">
+      <c r="IH5" s="163">
         <f>IF(OR(IG5="",IG5&gt;=$R$3),"",IG5+1)</f>
         <v/>
       </c>
-      <c r="II5" s="161">
+      <c r="II5" s="163">
         <f>IF(OR(IH5="",IH5&gt;=$R$3),"",IH5+1)</f>
         <v/>
       </c>
-      <c r="IJ5" s="161">
+      <c r="IJ5" s="163">
         <f>IF(OR(II5="",II5&gt;=$R$3),"",II5+1)</f>
         <v/>
       </c>
-      <c r="IK5" s="161">
+      <c r="IK5" s="163">
         <f>IF(OR(IJ5="",IJ5&gt;=$R$3),"",IJ5+1)</f>
         <v/>
       </c>
-      <c r="IL5" s="161">
+      <c r="IL5" s="163">
         <f>IF(OR(IK5="",IK5&gt;=$R$3),"",IK5+1)</f>
         <v/>
       </c>
-      <c r="IM5" s="161">
+      <c r="IM5" s="163">
         <f>IF(OR(IL5="",IL5&gt;=$R$3),"",IL5+1)</f>
         <v/>
       </c>
-      <c r="IN5" s="161">
+      <c r="IN5" s="163">
         <f>IF(OR(IM5="",IM5&gt;=$R$3),"",IM5+1)</f>
         <v/>
       </c>
-      <c r="IO5" s="161">
+      <c r="IO5" s="163">
         <f>IF(OR(IN5="",IN5&gt;=$R$3),"",IN5+1)</f>
         <v/>
       </c>
-      <c r="IP5" s="161">
+      <c r="IP5" s="163">
         <f>IF(OR(IO5="",IO5&gt;=$R$3),"",IO5+1)</f>
         <v/>
       </c>
-      <c r="IQ5" s="161">
+      <c r="IQ5" s="163">
         <f>IF(OR(IP5="",IP5&gt;=$R$3),"",IP5+1)</f>
         <v/>
       </c>
-      <c r="IR5" s="161">
+      <c r="IR5" s="163">
         <f>IF(OR(IQ5="",IQ5&gt;=$R$3),"",IQ5+1)</f>
         <v/>
       </c>
-      <c r="IS5" s="161">
+      <c r="IS5" s="163">
         <f>IF(OR(IR5="",IR5&gt;=$R$3),"",IR5+1)</f>
         <v/>
       </c>
-      <c r="IT5" s="161">
+      <c r="IT5" s="163">
         <f>IF(OR(IS5="",IS5&gt;=$R$3),"",IS5+1)</f>
         <v/>
       </c>
-      <c r="IU5" s="161">
+      <c r="IU5" s="163">
         <f>IF(OR(IT5="",IT5&gt;=$R$3),"",IT5+1)</f>
         <v/>
       </c>
-      <c r="IV5" s="161">
+      <c r="IV5" s="163">
         <f>IF(OR(IU5="",IU5&gt;=$R$3),"",IU5+1)</f>
         <v/>
       </c>
-      <c r="IW5" s="161">
+      <c r="IW5" s="163">
         <f>IF(OR(IV5="",IV5&gt;=$R$3),"",IV5+1)</f>
         <v/>
       </c>
-      <c r="IX5" s="161">
+      <c r="IX5" s="163">
         <f>IF(OR(IW5="",IW5&gt;=$R$3),"",IW5+1)</f>
         <v/>
       </c>
-      <c r="IY5" s="161">
+      <c r="IY5" s="163">
         <f>IF(OR(IX5="",IX5&gt;=$R$3),"",IX5+1)</f>
         <v/>
       </c>
-      <c r="IZ5" s="161">
+      <c r="IZ5" s="163">
         <f>IF(OR(IY5="",IY5&gt;=$R$3),"",IY5+1)</f>
         <v/>
       </c>
-      <c r="JA5" s="161">
+      <c r="JA5" s="163">
         <f>IF(OR(IZ5="",IZ5&gt;=$R$3),"",IZ5+1)</f>
         <v/>
       </c>
-      <c r="JB5" s="161">
+      <c r="JB5" s="163">
         <f>IF(OR(JA5="",JA5&gt;=$R$3),"",JA5+1)</f>
         <v/>
       </c>
-      <c r="JC5" s="161">
+      <c r="JC5" s="163">
         <f>IF(OR(JB5="",JB5&gt;=$R$3),"",JB5+1)</f>
         <v/>
       </c>
-      <c r="JD5" s="161">
+      <c r="JD5" s="163">
         <f>IF(OR(JC5="",JC5&gt;=$R$3),"",JC5+1)</f>
         <v/>
       </c>
-      <c r="JE5" s="161">
+      <c r="JE5" s="163">
         <f>IF(OR(JD5="",JD5&gt;=$R$3),"",JD5+1)</f>
         <v/>
       </c>
-      <c r="JF5" s="161">
+      <c r="JF5" s="163">
         <f>IF(OR(JE5="",JE5&gt;=$R$3),"",JE5+1)</f>
         <v/>
       </c>
-      <c r="JG5" s="161">
+      <c r="JG5" s="163">
         <f>IF(OR(JF5="",JF5&gt;=$R$3),"",JF5+1)</f>
         <v/>
       </c>
-      <c r="JH5" s="161">
+      <c r="JH5" s="163">
         <f>IF(OR(JG5="",JG5&gt;=$R$3),"",JG5+1)</f>
         <v/>
       </c>
-      <c r="JI5" s="161">
+      <c r="JI5" s="163">
         <f>IF(OR(JH5="",JH5&gt;=$R$3),"",JH5+1)</f>
         <v/>
       </c>
-      <c r="JJ5" s="161">
+      <c r="JJ5" s="163">
         <f>IF(OR(JI5="",JI5&gt;=$R$3),"",JI5+1)</f>
         <v/>
       </c>
-      <c r="JK5" s="161">
+      <c r="JK5" s="163">
         <f>IF(OR(JJ5="",JJ5&gt;=$R$3),"",JJ5+1)</f>
         <v/>
       </c>
-      <c r="JL5" s="161">
+      <c r="JL5" s="163">
         <f>IF(OR(JK5="",JK5&gt;=$R$3),"",JK5+1)</f>
         <v/>
       </c>
-      <c r="JM5" s="161">
+      <c r="JM5" s="163">
         <f>IF(OR(JL5="",JL5&gt;=$R$3),"",JL5+1)</f>
         <v/>
       </c>
-      <c r="JN5" s="161">
+      <c r="JN5" s="163">
         <f>IF(OR(JM5="",JM5&gt;=$R$3),"",JM5+1)</f>
         <v/>
       </c>
-      <c r="JO5" s="161">
+      <c r="JO5" s="163">
         <f>IF(OR(JN5="",JN5&gt;=$R$3),"",JN5+1)</f>
         <v/>
       </c>
-      <c r="JP5" s="161">
+      <c r="JP5" s="163">
         <f>IF(OR(JO5="",JO5&gt;=$R$3),"",JO5+1)</f>
         <v/>
       </c>
-      <c r="JQ5" s="161">
+      <c r="JQ5" s="163">
         <f>IF(OR(JP5="",JP5&gt;=$R$3),"",JP5+1)</f>
         <v/>
       </c>
-      <c r="JR5" s="161">
+      <c r="JR5" s="163">
         <f>IF(OR(JQ5="",JQ5&gt;=$R$3),"",JQ5+1)</f>
         <v/>
       </c>
-      <c r="JS5" s="161">
+      <c r="JS5" s="163">
         <f>IF(OR(JR5="",JR5&gt;=$R$3),"",JR5+1)</f>
         <v/>
       </c>
-      <c r="JT5" s="161">
+      <c r="JT5" s="163">
         <f>IF(OR(JS5="",JS5&gt;=$R$3),"",JS5+1)</f>
         <v/>
       </c>
-      <c r="JU5" s="161">
+      <c r="JU5" s="163">
         <f>IF(OR(JT5="",JT5&gt;=$R$3),"",JT5+1)</f>
         <v/>
       </c>
-      <c r="JV5" s="161">
+      <c r="JV5" s="163">
         <f>IF(OR(JU5="",JU5&gt;=$R$3),"",JU5+1)</f>
         <v/>
       </c>
-      <c r="JW5" s="161">
+      <c r="JW5" s="163">
         <f>IF(OR(JV5="",JV5&gt;=$R$3),"",JV5+1)</f>
         <v/>
       </c>
-      <c r="JX5" s="161">
+      <c r="JX5" s="163">
         <f>IF(OR(JW5="",JW5&gt;=$R$3),"",JW5+1)</f>
         <v/>
       </c>
-      <c r="JY5" s="161">
+      <c r="JY5" s="163">
         <f>IF(OR(JX5="",JX5&gt;=$R$3),"",JX5+1)</f>
         <v/>
       </c>
-      <c r="JZ5" s="161">
+      <c r="JZ5" s="163">
         <f>IF(OR(JY5="",JY5&gt;=$R$3),"",JY5+1)</f>
         <v/>
       </c>
-      <c r="KA5" s="161">
+      <c r="KA5" s="163">
         <f>IF(OR(JZ5="",JZ5&gt;=$R$3),"",JZ5+1)</f>
         <v/>
       </c>
-      <c r="KB5" s="161">
+      <c r="KB5" s="163">
         <f>IF(OR(KA5="",KA5&gt;=$R$3),"",KA5+1)</f>
         <v/>
       </c>
-      <c r="KC5" s="161">
+      <c r="KC5" s="163">
         <f>IF(OR(KB5="",KB5&gt;=$R$3),"",KB5+1)</f>
         <v/>
       </c>
-      <c r="KD5" s="161">
+      <c r="KD5" s="163">
         <f>IF(OR(KC5="",KC5&gt;=$R$3),"",KC5+1)</f>
         <v/>
       </c>
-      <c r="KE5" s="161">
+      <c r="KE5" s="163">
         <f>IF(OR(KD5="",KD5&gt;=$R$3),"",KD5+1)</f>
         <v/>
       </c>
-      <c r="KF5" s="161">
+      <c r="KF5" s="163">
         <f>IF(OR(KE5="",KE5&gt;=$R$3),"",KE5+1)</f>
         <v/>
       </c>
-      <c r="KG5" s="161">
+      <c r="KG5" s="163">
         <f>IF(OR(KF5="",KF5&gt;=$R$3),"",KF5+1)</f>
         <v/>
       </c>
-      <c r="KH5" s="161">
+      <c r="KH5" s="163">
         <f>IF(OR(KG5="",KG5&gt;=$R$3),"",KG5+1)</f>
         <v/>
       </c>
-      <c r="KI5" s="161">
+      <c r="KI5" s="163">
         <f>IF(OR(KH5="",KH5&gt;=$R$3),"",KH5+1)</f>
         <v/>
       </c>
-      <c r="KJ5" s="161">
+      <c r="KJ5" s="163">
         <f>IF(OR(KI5="",KI5&gt;=$R$3),"",KI5+1)</f>
         <v/>
       </c>
-      <c r="KK5" s="161">
+      <c r="KK5" s="163">
         <f>IF(OR(KJ5="",KJ5&gt;=$R$3),"",KJ5+1)</f>
         <v/>
       </c>
-      <c r="KL5" s="161">
+      <c r="KL5" s="163">
         <f>IF(OR(KK5="",KK5&gt;=$R$3),"",KK5+1)</f>
         <v/>
       </c>
-      <c r="KM5" s="161">
+      <c r="KM5" s="163">
         <f>IF(OR(KL5="",KL5&gt;=$R$3),"",KL5+1)</f>
         <v/>
       </c>
-      <c r="KN5" s="161">
+      <c r="KN5" s="163">
         <f>IF(OR(KM5="",KM5&gt;=$R$3),"",KM5+1)</f>
         <v/>
       </c>
-      <c r="KO5" s="161">
+      <c r="KO5" s="163">
         <f>IF(OR(KN5="",KN5&gt;=$R$3),"",KN5+1)</f>
         <v/>
       </c>
-      <c r="KP5" s="161">
+      <c r="KP5" s="163">
         <f>IF(OR(KO5="",KO5&gt;=$R$3),"",KO5+1)</f>
         <v/>
       </c>
-      <c r="KQ5" s="161">
+      <c r="KQ5" s="163">
         <f>IF(OR(KP5="",KP5&gt;=$R$3),"",KP5+1)</f>
         <v/>
       </c>
-      <c r="KR5" s="161">
+      <c r="KR5" s="163">
         <f>IF(OR(KQ5="",KQ5&gt;=$R$3),"",KQ5+1)</f>
         <v/>
       </c>
-      <c r="KS5" s="161">
+      <c r="KS5" s="163">
         <f>IF(OR(KR5="",KR5&gt;=$R$3),"",KR5+1)</f>
         <v/>
       </c>
-      <c r="KT5" s="161">
+      <c r="KT5" s="163">
         <f>IF(OR(KS5="",KS5&gt;=$R$3),"",KS5+1)</f>
         <v/>
       </c>
-      <c r="KU5" s="161">
+      <c r="KU5" s="163">
         <f>IF(OR(KT5="",KT5&gt;=$R$3),"",KT5+1)</f>
         <v/>
       </c>
-      <c r="KV5" s="161">
+      <c r="KV5" s="163">
         <f>IF(OR(KU5="",KU5&gt;=$R$3),"",KU5+1)</f>
         <v/>
       </c>
-      <c r="KW5" s="161">
+      <c r="KW5" s="163">
         <f>IF(OR(KV5="",KV5&gt;=$R$3),"",KV5+1)</f>
         <v/>
       </c>
-      <c r="KX5" s="161">
+      <c r="KX5" s="163">
         <f>IF(OR(KW5="",KW5&gt;=$R$3),"",KW5+1)</f>
         <v/>
       </c>
-      <c r="KY5" s="161">
+      <c r="KY5" s="163">
         <f>IF(OR(KX5="",KX5&gt;=$R$3),"",KX5+1)</f>
         <v/>
       </c>
-      <c r="KZ5" s="161">
+      <c r="KZ5" s="163">
         <f>IF(OR(KY5="",KY5&gt;=$R$3),"",KY5+1)</f>
         <v/>
       </c>
-      <c r="LA5" s="161">
+      <c r="LA5" s="163">
         <f>IF(OR(KZ5="",KZ5&gt;=$R$3),"",KZ5+1)</f>
         <v/>
       </c>
-      <c r="LB5" s="161">
+      <c r="LB5" s="163">
         <f>IF(OR(LA5="",LA5&gt;=$R$3),"",LA5+1)</f>
         <v/>
       </c>
-      <c r="LC5" s="161">
+      <c r="LC5" s="163">
         <f>IF(OR(LB5="",LB5&gt;=$R$3),"",LB5+1)</f>
         <v/>
       </c>
-      <c r="LD5" s="161">
+      <c r="LD5" s="163">
         <f>IF(OR(LC5="",LC5&gt;=$R$3),"",LC5+1)</f>
         <v/>
       </c>
-      <c r="LE5" s="161">
+      <c r="LE5" s="163">
         <f>IF(OR(LD5="",LD5&gt;=$R$3),"",LD5+1)</f>
         <v/>
       </c>
-      <c r="LF5" s="161">
+      <c r="LF5" s="163">
         <f>IF(OR(LE5="",LE5&gt;=$R$3),"",LE5+1)</f>
         <v/>
       </c>
-      <c r="LG5" s="161">
+      <c r="LG5" s="163">
         <f>IF(OR(LF5="",LF5&gt;=$R$3),"",LF5+1)</f>
         <v/>
       </c>
-      <c r="LH5" s="161">
+      <c r="LH5" s="163">
         <f>IF(OR(LG5="",LG5&gt;=$R$3),"",LG5+1)</f>
         <v/>
       </c>
-      <c r="LI5" s="161">
+      <c r="LI5" s="163">
         <f>IF(OR(LH5="",LH5&gt;=$R$3),"",LH5+1)</f>
         <v/>
       </c>
-      <c r="LJ5" s="161">
+      <c r="LJ5" s="163">
         <f>IF(OR(LI5="",LI5&gt;=$R$3),"",LI5+1)</f>
         <v/>
       </c>
-      <c r="LK5" s="161">
+      <c r="LK5" s="163">
         <f>IF(OR(LJ5="",LJ5&gt;=$R$3),"",LJ5+1)</f>
         <v/>
       </c>
-      <c r="LL5" s="161">
+      <c r="LL5" s="163">
         <f>IF(OR(LK5="",LK5&gt;=$R$3),"",LK5+1)</f>
         <v/>
       </c>
-      <c r="LM5" s="161">
+      <c r="LM5" s="163">
         <f>IF(OR(LL5="",LL5&gt;=$R$3),"",LL5+1)</f>
         <v/>
       </c>
-      <c r="LN5" s="161">
+      <c r="LN5" s="163">
         <f>IF(OR(LM5="",LM5&gt;=$R$3),"",LM5+1)</f>
         <v/>
       </c>
-      <c r="LO5" s="161">
+      <c r="LO5" s="163">
         <f>IF(OR(LN5="",LN5&gt;=$R$3),"",LN5+1)</f>
         <v/>
       </c>
-      <c r="LP5" s="161">
+      <c r="LP5" s="163">
         <f>IF(OR(LO5="",LO5&gt;=$R$3),"",LO5+1)</f>
         <v/>
       </c>
-      <c r="LQ5" s="161">
+      <c r="LQ5" s="163">
         <f>IF(OR(LP5="",LP5&gt;=$R$3),"",LP5+1)</f>
         <v/>
       </c>
-      <c r="LR5" s="161">
+      <c r="LR5" s="163">
         <f>IF(OR(LQ5="",LQ5&gt;=$R$3),"",LQ5+1)</f>
         <v/>
       </c>
-      <c r="LS5" s="161">
+      <c r="LS5" s="163">
         <f>IF(OR(LR5="",LR5&gt;=$R$3),"",LR5+1)</f>
         <v/>
       </c>
-      <c r="LT5" s="161">
+      <c r="LT5" s="163">
         <f>IF(OR(LS5="",LS5&gt;=$R$3),"",LS5+1)</f>
         <v/>
       </c>
-      <c r="LU5" s="161">
+      <c r="LU5" s="163">
         <f>IF(OR(LT5="",LT5&gt;=$R$3),"",LT5+1)</f>
         <v/>
       </c>
-      <c r="LV5" s="161">
+      <c r="LV5" s="163">
         <f>IF(OR(LU5="",LU5&gt;=$R$3),"",LU5+1)</f>
         <v/>
       </c>
-      <c r="LW5" s="161">
+      <c r="LW5" s="163">
         <f>IF(OR(LV5="",LV5&gt;=$R$3),"",LV5+1)</f>
         <v/>
       </c>
-      <c r="LX5" s="161">
+      <c r="LX5" s="163">
         <f>IF(OR(LW5="",LW5&gt;=$R$3),"",LW5+1)</f>
         <v/>
       </c>
-      <c r="LY5" s="161">
+      <c r="LY5" s="163">
         <f>IF(OR(LX5="",LX5&gt;=$R$3),"",LX5+1)</f>
         <v/>
       </c>
-      <c r="LZ5" s="161">
+      <c r="LZ5" s="163">
         <f>IF(OR(LY5="",LY5&gt;=$R$3),"",LY5+1)</f>
         <v/>
       </c>
-      <c r="MA5" s="161">
+      <c r="MA5" s="163">
         <f>IF(OR(LZ5="",LZ5&gt;=$R$3),"",LZ5+1)</f>
         <v/>
       </c>
-      <c r="MB5" s="161">
+      <c r="MB5" s="163">
         <f>IF(OR(MA5="",MA5&gt;=$R$3),"",MA5+1)</f>
         <v/>
       </c>
-      <c r="MC5" s="161">
+      <c r="MC5" s="163">
         <f>IF(OR(MB5="",MB5&gt;=$R$3),"",MB5+1)</f>
         <v/>
       </c>
-      <c r="MD5" s="161">
+      <c r="MD5" s="163">
         <f>IF(OR(MC5="",MC5&gt;=$R$3),"",MC5+1)</f>
         <v/>
       </c>
-      <c r="ME5" s="161">
+      <c r="ME5" s="163">
         <f>IF(OR(MD5="",MD5&gt;=$R$3),"",MD5+1)</f>
         <v/>
       </c>
-      <c r="MF5" s="161">
+      <c r="MF5" s="163">
         <f>IF(OR(ME5="",ME5&gt;=$R$3),"",ME5+1)</f>
         <v/>
       </c>
-      <c r="MG5" s="161">
+      <c r="MG5" s="163">
         <f>IF(OR(MF5="",MF5&gt;=$R$3),"",MF5+1)</f>
         <v/>
       </c>
-      <c r="MH5" s="161">
+      <c r="MH5" s="163">
         <f>IF(OR(MG5="",MG5&gt;=$R$3),"",MG5+1)</f>
         <v/>
       </c>
-      <c r="MI5" s="161">
+      <c r="MI5" s="163">
         <f>IF(OR(MH5="",MH5&gt;=$R$3),"",MH5+1)</f>
         <v/>
       </c>
-      <c r="MJ5" s="161">
+      <c r="MJ5" s="163">
         <f>IF(OR(MI5="",MI5&gt;=$R$3),"",MI5+1)</f>
         <v/>
       </c>
-      <c r="MK5" s="161">
+      <c r="MK5" s="163">
         <f>IF(OR(MJ5="",MJ5&gt;=$R$3),"",MJ5+1)</f>
         <v/>
       </c>
-      <c r="ML5" s="161">
+      <c r="ML5" s="163">
         <f>IF(OR(MK5="",MK5&gt;=$R$3),"",MK5+1)</f>
         <v/>
       </c>
-      <c r="MM5" s="161">
+      <c r="MM5" s="163">
         <f>IF(OR(ML5="",ML5&gt;=$R$3),"",ML5+1)</f>
         <v/>
       </c>
-      <c r="MN5" s="161">
+      <c r="MN5" s="163">
         <f>IF(OR(MM5="",MM5&gt;=$R$3),"",MM5+1)</f>
         <v/>
       </c>
-      <c r="MO5" s="161">
+      <c r="MO5" s="163">
         <f>IF(OR(MN5="",MN5&gt;=$R$3),"",MN5+1)</f>
         <v/>
       </c>
-      <c r="MP5" s="161">
+      <c r="MP5" s="163">
         <f>IF(OR(MO5="",MO5&gt;=$R$3),"",MO5+1)</f>
         <v/>
       </c>
-      <c r="MQ5" s="161">
+      <c r="MQ5" s="163">
         <f>IF(OR(MP5="",MP5&gt;=$R$3),"",MP5+1)</f>
         <v/>
       </c>
-      <c r="MR5" s="161">
+      <c r="MR5" s="163">
         <f>IF(OR(MQ5="",MQ5&gt;=$R$3),"",MQ5+1)</f>
         <v/>
       </c>
-      <c r="MS5" s="161">
+      <c r="MS5" s="163">
         <f>IF(OR(MR5="",MR5&gt;=$R$3),"",MR5+1)</f>
         <v/>
       </c>
-      <c r="MT5" s="161">
+      <c r="MT5" s="163">
         <f>IF(OR(MS5="",MS5&gt;=$R$3),"",MS5+1)</f>
         <v/>
       </c>
-      <c r="MU5" s="161">
+      <c r="MU5" s="163">
         <f>IF(OR(MT5="",MT5&gt;=$R$3),"",MT5+1)</f>
         <v/>
       </c>
-      <c r="MV5" s="161">
+      <c r="MV5" s="163">
         <f>IF(OR(MU5="",MU5&gt;=$R$3),"",MU5+1)</f>
         <v/>
       </c>
-      <c r="MW5" s="161">
+      <c r="MW5" s="163">
         <f>IF(OR(MV5="",MV5&gt;=$R$3),"",MV5+1)</f>
         <v/>
       </c>
-      <c r="MX5" s="161">
+      <c r="MX5" s="163">
         <f>IF(OR(MW5="",MW5&gt;=$R$3),"",MW5+1)</f>
         <v/>
       </c>
-      <c r="MY5" s="161">
+      <c r="MY5" s="163">
         <f>IF(OR(MX5="",MX5&gt;=$R$3),"",MX5+1)</f>
         <v/>
       </c>
-      <c r="MZ5" s="161">
+      <c r="MZ5" s="163">
         <f>IF(OR(MY5="",MY5&gt;=$R$3),"",MY5+1)</f>
         <v/>
       </c>
-      <c r="NA5" s="161">
+      <c r="NA5" s="163">
         <f>IF(OR(MZ5="",MZ5&gt;=$R$3),"",MZ5+1)</f>
         <v/>
       </c>
-      <c r="NB5" s="161">
+      <c r="NB5" s="163">
         <f>IF(OR(NA5="",NA5&gt;=$R$3),"",NA5+1)</f>
         <v/>
       </c>
-      <c r="NC5" s="161">
+      <c r="NC5" s="163">
         <f>IF(OR(NB5="",NB5&gt;=$R$3),"",NB5+1)</f>
         <v/>
       </c>
-      <c r="ND5" s="161">
+      <c r="ND5" s="163">
         <f>IF(OR(NC5="",NC5&gt;=$R$3),"",NC5+1)</f>
         <v/>
       </c>
-      <c r="NE5" s="161">
+      <c r="NE5" s="163">
         <f>IF(OR(ND5="",ND5&gt;=$R$3),"",ND5+1)</f>
         <v/>
       </c>
-      <c r="NF5" s="161">
+      <c r="NF5" s="163">
         <f>IF(OR(NE5="",NE5&gt;=$R$3),"",NE5+1)</f>
         <v/>
       </c>
-      <c r="NG5" s="161">
+      <c r="NG5" s="163">
         <f>IF(OR(NF5="",NF5&gt;=$R$3),"",NF5+1)</f>
         <v/>
       </c>
-      <c r="NH5" s="161">
+      <c r="NH5" s="163">
         <f>IF(OR(NG5="",NG5&gt;=$R$3),"",NG5+1)</f>
         <v/>
       </c>
-      <c r="NI5" s="161">
+      <c r="NI5" s="163">
         <f>IF(OR(NH5="",NH5&gt;=$R$3),"",NH5+1)</f>
         <v/>
       </c>
-      <c r="NJ5" s="161">
+      <c r="NJ5" s="163">
         <f>IF(OR(NI5="",NI5&gt;=$R$3),"",NI5+1)</f>
         <v/>
       </c>
-      <c r="NK5" s="161">
+      <c r="NK5" s="163">
         <f>IF(OR(NJ5="",NJ5&gt;=$R$3),"",NJ5+1)</f>
         <v/>
       </c>
-      <c r="NL5" s="161">
+      <c r="NL5" s="163">
         <f>IF(OR(NK5="",NK5&gt;=$R$3),"",NK5+1)</f>
         <v/>
       </c>
-      <c r="NM5" s="161">
+      <c r="NM5" s="163">
         <f>IF(OR(NL5="",NL5&gt;=$R$3),"",NL5+1)</f>
         <v/>
       </c>
-      <c r="NN5" s="161">
+      <c r="NN5" s="163">
         <f>IF(OR(NM5="",NM5&gt;=$R$3),"",NM5+1)</f>
         <v/>
       </c>
-      <c r="NO5" s="161">
+      <c r="NO5" s="163">
         <f>IF(OR(NN5="",NN5&gt;=$R$3),"",NN5+1)</f>
         <v/>
       </c>
-      <c r="NP5" s="161">
+      <c r="NP5" s="163">
         <f>IF(OR(NO5="",NO5&gt;=$R$3),"",NO5+1)</f>
         <v/>
       </c>
-      <c r="NQ5" s="161">
+      <c r="NQ5" s="163">
         <f>IF(OR(NP5="",NP5&gt;=$R$3),"",NP5+1)</f>
         <v/>
       </c>
-      <c r="NR5" s="161">
+      <c r="NR5" s="163">
         <f>IF(OR(NQ5="",NQ5&gt;=$R$3),"",NQ5+1)</f>
         <v/>
       </c>
-      <c r="NS5" s="161">
+      <c r="NS5" s="163">
         <f>IF(OR(NR5="",NR5&gt;=$R$3),"",NR5+1)</f>
         <v/>
       </c>
-      <c r="NT5" s="161">
+      <c r="NT5" s="163">
         <f>IF(OR(NS5="",NS5&gt;=$R$3),"",NS5+1)</f>
         <v/>
       </c>
-      <c r="NU5" s="161">
+      <c r="NU5" s="163">
         <f>IF(OR(NT5="",NT5&gt;=$R$3),"",NT5+1)</f>
         <v/>
       </c>
-      <c r="NV5" s="161">
+      <c r="NV5" s="163">
         <f>IF(OR(NU5="",NU5&gt;=$R$3),"",NU5+1)</f>
         <v/>
       </c>
-      <c r="NW5" s="161">
+      <c r="NW5" s="163">
         <f>IF(OR(NV5="",NV5&gt;=$R$3),"",NV5+1)</f>
         <v/>
       </c>
-      <c r="NX5" s="161">
+      <c r="NX5" s="163">
         <f>IF(OR(NW5="",NW5&gt;=$R$3),"",NW5+1)</f>
         <v/>
       </c>
-      <c r="NY5" s="161">
+      <c r="NY5" s="163">
         <f>IF(OR(NX5="",NX5&gt;=$R$3),"",NX5+1)</f>
         <v/>
       </c>
-      <c r="NZ5" s="161">
+      <c r="NZ5" s="163">
         <f>IF(OR(NY5="",NY5&gt;=$R$3),"",NY5+1)</f>
         <v/>
       </c>
-      <c r="OA5" s="161">
+      <c r="OA5" s="163">
         <f>IF(OR(NZ5="",NZ5&gt;=$R$3),"",NZ5+1)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" s="104">
-      <c r="A6" s="162" t="inlineStr">
+      <c r="A6" s="164" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B6" s="163" t="n"/>
-      <c r="C6" s="164" t="n"/>
+      <c r="B6" s="165" t="n"/>
+      <c r="C6" s="166" t="n"/>
       <c r="D6" s="32" t="inlineStr">
         <is>
           <t>L1</t>
@@ -33909,7 +33966,7 @@
           <t>총 작업량</t>
         </is>
       </c>
-      <c r="P6" s="165" t="inlineStr">
+      <c r="P6" s="167" t="inlineStr">
         <is>
           <t>목표 작업량</t>
         </is>
@@ -33939,1509 +33996,1509 @@
           <t>비고</t>
         </is>
       </c>
-      <c r="V6" s="166">
+      <c r="V6" s="168">
         <f>IF(V5="","",CHOOSE(WEEKDAY(V5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="W6" s="166">
+      <c r="W6" s="168">
         <f>IF(W5="","",CHOOSE(WEEKDAY(W5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="X6" s="166">
+      <c r="X6" s="168">
         <f>IF(X5="","",CHOOSE(WEEKDAY(X5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="Y6" s="166">
+      <c r="Y6" s="168">
         <f>IF(Y5="","",CHOOSE(WEEKDAY(Y5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="Z6" s="166">
+      <c r="Z6" s="168">
         <f>IF(Z5="","",CHOOSE(WEEKDAY(Z5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AA6" s="166">
+      <c r="AA6" s="168">
         <f>IF(AA5="","",CHOOSE(WEEKDAY(AA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AB6" s="166">
+      <c r="AB6" s="168">
         <f>IF(AB5="","",CHOOSE(WEEKDAY(AB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AC6" s="166">
+      <c r="AC6" s="168">
         <f>IF(AC5="","",CHOOSE(WEEKDAY(AC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AD6" s="166">
+      <c r="AD6" s="168">
         <f>IF(AD5="","",CHOOSE(WEEKDAY(AD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AE6" s="166">
+      <c r="AE6" s="168">
         <f>IF(AE5="","",CHOOSE(WEEKDAY(AE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AF6" s="166">
+      <c r="AF6" s="168">
         <f>IF(AF5="","",CHOOSE(WEEKDAY(AF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AG6" s="166">
+      <c r="AG6" s="168">
         <f>IF(AG5="","",CHOOSE(WEEKDAY(AG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AH6" s="166">
+      <c r="AH6" s="168">
         <f>IF(AH5="","",CHOOSE(WEEKDAY(AH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AI6" s="166">
+      <c r="AI6" s="168">
         <f>IF(AI5="","",CHOOSE(WEEKDAY(AI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AJ6" s="166">
+      <c r="AJ6" s="168">
         <f>IF(AJ5="","",CHOOSE(WEEKDAY(AJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AK6" s="166">
+      <c r="AK6" s="168">
         <f>IF(AK5="","",CHOOSE(WEEKDAY(AK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AL6" s="166">
+      <c r="AL6" s="168">
         <f>IF(AL5="","",CHOOSE(WEEKDAY(AL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AM6" s="166">
+      <c r="AM6" s="168">
         <f>IF(AM5="","",CHOOSE(WEEKDAY(AM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AN6" s="166">
+      <c r="AN6" s="168">
         <f>IF(AN5="","",CHOOSE(WEEKDAY(AN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AO6" s="166">
+      <c r="AO6" s="168">
         <f>IF(AO5="","",CHOOSE(WEEKDAY(AO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AP6" s="166">
+      <c r="AP6" s="168">
         <f>IF(AP5="","",CHOOSE(WEEKDAY(AP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AQ6" s="166">
+      <c r="AQ6" s="168">
         <f>IF(AQ5="","",CHOOSE(WEEKDAY(AQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AR6" s="166">
+      <c r="AR6" s="168">
         <f>IF(AR5="","",CHOOSE(WEEKDAY(AR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AS6" s="166">
+      <c r="AS6" s="168">
         <f>IF(AS5="","",CHOOSE(WEEKDAY(AS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AT6" s="166">
+      <c r="AT6" s="168">
         <f>IF(AT5="","",CHOOSE(WEEKDAY(AT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AU6" s="166">
+      <c r="AU6" s="168">
         <f>IF(AU5="","",CHOOSE(WEEKDAY(AU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AV6" s="166">
+      <c r="AV6" s="168">
         <f>IF(AV5="","",CHOOSE(WEEKDAY(AV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AW6" s="166">
+      <c r="AW6" s="168">
         <f>IF(AW5="","",CHOOSE(WEEKDAY(AW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AX6" s="166">
+      <c r="AX6" s="168">
         <f>IF(AX5="","",CHOOSE(WEEKDAY(AX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AY6" s="166">
+      <c r="AY6" s="168">
         <f>IF(AY5="","",CHOOSE(WEEKDAY(AY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="AZ6" s="166">
+      <c r="AZ6" s="168">
         <f>IF(AZ5="","",CHOOSE(WEEKDAY(AZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BA6" s="166">
+      <c r="BA6" s="168">
         <f>IF(BA5="","",CHOOSE(WEEKDAY(BA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BB6" s="166">
+      <c r="BB6" s="168">
         <f>IF(BB5="","",CHOOSE(WEEKDAY(BB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BC6" s="166">
+      <c r="BC6" s="168">
         <f>IF(BC5="","",CHOOSE(WEEKDAY(BC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BD6" s="166">
+      <c r="BD6" s="168">
         <f>IF(BD5="","",CHOOSE(WEEKDAY(BD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BE6" s="166">
+      <c r="BE6" s="168">
         <f>IF(BE5="","",CHOOSE(WEEKDAY(BE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BF6" s="166">
+      <c r="BF6" s="168">
         <f>IF(BF5="","",CHOOSE(WEEKDAY(BF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BG6" s="166">
+      <c r="BG6" s="168">
         <f>IF(BG5="","",CHOOSE(WEEKDAY(BG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BH6" s="166">
+      <c r="BH6" s="168">
         <f>IF(BH5="","",CHOOSE(WEEKDAY(BH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BI6" s="166">
+      <c r="BI6" s="168">
         <f>IF(BI5="","",CHOOSE(WEEKDAY(BI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BJ6" s="166">
+      <c r="BJ6" s="168">
         <f>IF(BJ5="","",CHOOSE(WEEKDAY(BJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BK6" s="166">
+      <c r="BK6" s="168">
         <f>IF(BK5="","",CHOOSE(WEEKDAY(BK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BL6" s="166">
+      <c r="BL6" s="168">
         <f>IF(BL5="","",CHOOSE(WEEKDAY(BL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BM6" s="166">
+      <c r="BM6" s="168">
         <f>IF(BM5="","",CHOOSE(WEEKDAY(BM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BN6" s="166">
+      <c r="BN6" s="168">
         <f>IF(BN5="","",CHOOSE(WEEKDAY(BN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BO6" s="166">
+      <c r="BO6" s="168">
         <f>IF(BO5="","",CHOOSE(WEEKDAY(BO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BP6" s="166">
+      <c r="BP6" s="168">
         <f>IF(BP5="","",CHOOSE(WEEKDAY(BP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BQ6" s="166">
+      <c r="BQ6" s="168">
         <f>IF(BQ5="","",CHOOSE(WEEKDAY(BQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BR6" s="166">
+      <c r="BR6" s="168">
         <f>IF(BR5="","",CHOOSE(WEEKDAY(BR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BS6" s="166">
+      <c r="BS6" s="168">
         <f>IF(BS5="","",CHOOSE(WEEKDAY(BS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BT6" s="166">
+      <c r="BT6" s="168">
         <f>IF(BT5="","",CHOOSE(WEEKDAY(BT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BU6" s="166">
+      <c r="BU6" s="168">
         <f>IF(BU5="","",CHOOSE(WEEKDAY(BU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BV6" s="166">
+      <c r="BV6" s="168">
         <f>IF(BV5="","",CHOOSE(WEEKDAY(BV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BW6" s="166">
+      <c r="BW6" s="168">
         <f>IF(BW5="","",CHOOSE(WEEKDAY(BW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BX6" s="166">
+      <c r="BX6" s="168">
         <f>IF(BX5="","",CHOOSE(WEEKDAY(BX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BY6" s="166">
+      <c r="BY6" s="168">
         <f>IF(BY5="","",CHOOSE(WEEKDAY(BY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="BZ6" s="166">
+      <c r="BZ6" s="168">
         <f>IF(BZ5="","",CHOOSE(WEEKDAY(BZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CA6" s="166">
+      <c r="CA6" s="168">
         <f>IF(CA5="","",CHOOSE(WEEKDAY(CA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CB6" s="166">
+      <c r="CB6" s="168">
         <f>IF(CB5="","",CHOOSE(WEEKDAY(CB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CC6" s="166">
+      <c r="CC6" s="168">
         <f>IF(CC5="","",CHOOSE(WEEKDAY(CC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CD6" s="166">
+      <c r="CD6" s="168">
         <f>IF(CD5="","",CHOOSE(WEEKDAY(CD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CE6" s="166">
+      <c r="CE6" s="168">
         <f>IF(CE5="","",CHOOSE(WEEKDAY(CE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CF6" s="166">
+      <c r="CF6" s="168">
         <f>IF(CF5="","",CHOOSE(WEEKDAY(CF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CG6" s="166">
+      <c r="CG6" s="168">
         <f>IF(CG5="","",CHOOSE(WEEKDAY(CG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CH6" s="166">
+      <c r="CH6" s="168">
         <f>IF(CH5="","",CHOOSE(WEEKDAY(CH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CI6" s="166">
+      <c r="CI6" s="168">
         <f>IF(CI5="","",CHOOSE(WEEKDAY(CI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CJ6" s="166">
+      <c r="CJ6" s="168">
         <f>IF(CJ5="","",CHOOSE(WEEKDAY(CJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CK6" s="166">
+      <c r="CK6" s="168">
         <f>IF(CK5="","",CHOOSE(WEEKDAY(CK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CL6" s="166">
+      <c r="CL6" s="168">
         <f>IF(CL5="","",CHOOSE(WEEKDAY(CL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CM6" s="166">
+      <c r="CM6" s="168">
         <f>IF(CM5="","",CHOOSE(WEEKDAY(CM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CN6" s="166">
+      <c r="CN6" s="168">
         <f>IF(CN5="","",CHOOSE(WEEKDAY(CN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CO6" s="166">
+      <c r="CO6" s="168">
         <f>IF(CO5="","",CHOOSE(WEEKDAY(CO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CP6" s="166">
+      <c r="CP6" s="168">
         <f>IF(CP5="","",CHOOSE(WEEKDAY(CP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CQ6" s="166">
+      <c r="CQ6" s="168">
         <f>IF(CQ5="","",CHOOSE(WEEKDAY(CQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CR6" s="166">
+      <c r="CR6" s="168">
         <f>IF(CR5="","",CHOOSE(WEEKDAY(CR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CS6" s="166">
+      <c r="CS6" s="168">
         <f>IF(CS5="","",CHOOSE(WEEKDAY(CS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CT6" s="166">
+      <c r="CT6" s="168">
         <f>IF(CT5="","",CHOOSE(WEEKDAY(CT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CU6" s="166">
+      <c r="CU6" s="168">
         <f>IF(CU5="","",CHOOSE(WEEKDAY(CU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CV6" s="166">
+      <c r="CV6" s="168">
         <f>IF(CV5="","",CHOOSE(WEEKDAY(CV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CW6" s="166">
+      <c r="CW6" s="168">
         <f>IF(CW5="","",CHOOSE(WEEKDAY(CW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CX6" s="166">
+      <c r="CX6" s="168">
         <f>IF(CX5="","",CHOOSE(WEEKDAY(CX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CY6" s="166">
+      <c r="CY6" s="168">
         <f>IF(CY5="","",CHOOSE(WEEKDAY(CY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="CZ6" s="166">
+      <c r="CZ6" s="168">
         <f>IF(CZ5="","",CHOOSE(WEEKDAY(CZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DA6" s="166">
+      <c r="DA6" s="168">
         <f>IF(DA5="","",CHOOSE(WEEKDAY(DA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DB6" s="166">
+      <c r="DB6" s="168">
         <f>IF(DB5="","",CHOOSE(WEEKDAY(DB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DC6" s="166">
+      <c r="DC6" s="168">
         <f>IF(DC5="","",CHOOSE(WEEKDAY(DC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DD6" s="166">
+      <c r="DD6" s="168">
         <f>IF(DD5="","",CHOOSE(WEEKDAY(DD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DE6" s="166">
+      <c r="DE6" s="168">
         <f>IF(DE5="","",CHOOSE(WEEKDAY(DE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DF6" s="166">
+      <c r="DF6" s="168">
         <f>IF(DF5="","",CHOOSE(WEEKDAY(DF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DG6" s="166">
+      <c r="DG6" s="168">
         <f>IF(DG5="","",CHOOSE(WEEKDAY(DG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DH6" s="166">
+      <c r="DH6" s="168">
         <f>IF(DH5="","",CHOOSE(WEEKDAY(DH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DI6" s="166">
+      <c r="DI6" s="168">
         <f>IF(DI5="","",CHOOSE(WEEKDAY(DI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DJ6" s="166">
+      <c r="DJ6" s="168">
         <f>IF(DJ5="","",CHOOSE(WEEKDAY(DJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DK6" s="166">
+      <c r="DK6" s="168">
         <f>IF(DK5="","",CHOOSE(WEEKDAY(DK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DL6" s="166">
+      <c r="DL6" s="168">
         <f>IF(DL5="","",CHOOSE(WEEKDAY(DL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DM6" s="166">
+      <c r="DM6" s="168">
         <f>IF(DM5="","",CHOOSE(WEEKDAY(DM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DN6" s="166">
+      <c r="DN6" s="168">
         <f>IF(DN5="","",CHOOSE(WEEKDAY(DN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DO6" s="166">
+      <c r="DO6" s="168">
         <f>IF(DO5="","",CHOOSE(WEEKDAY(DO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DP6" s="166">
+      <c r="DP6" s="168">
         <f>IF(DP5="","",CHOOSE(WEEKDAY(DP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DQ6" s="166">
+      <c r="DQ6" s="168">
         <f>IF(DQ5="","",CHOOSE(WEEKDAY(DQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DR6" s="166">
+      <c r="DR6" s="168">
         <f>IF(DR5="","",CHOOSE(WEEKDAY(DR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DS6" s="166">
+      <c r="DS6" s="168">
         <f>IF(DS5="","",CHOOSE(WEEKDAY(DS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DT6" s="166">
+      <c r="DT6" s="168">
         <f>IF(DT5="","",CHOOSE(WEEKDAY(DT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DU6" s="166">
+      <c r="DU6" s="168">
         <f>IF(DU5="","",CHOOSE(WEEKDAY(DU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DV6" s="166">
+      <c r="DV6" s="168">
         <f>IF(DV5="","",CHOOSE(WEEKDAY(DV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DW6" s="166">
+      <c r="DW6" s="168">
         <f>IF(DW5="","",CHOOSE(WEEKDAY(DW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DX6" s="166">
+      <c r="DX6" s="168">
         <f>IF(DX5="","",CHOOSE(WEEKDAY(DX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DY6" s="166">
+      <c r="DY6" s="168">
         <f>IF(DY5="","",CHOOSE(WEEKDAY(DY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="DZ6" s="166">
+      <c r="DZ6" s="168">
         <f>IF(DZ5="","",CHOOSE(WEEKDAY(DZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EA6" s="166">
+      <c r="EA6" s="168">
         <f>IF(EA5="","",CHOOSE(WEEKDAY(EA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EB6" s="166">
+      <c r="EB6" s="168">
         <f>IF(EB5="","",CHOOSE(WEEKDAY(EB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EC6" s="166">
+      <c r="EC6" s="168">
         <f>IF(EC5="","",CHOOSE(WEEKDAY(EC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ED6" s="166">
+      <c r="ED6" s="168">
         <f>IF(ED5="","",CHOOSE(WEEKDAY(ED5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EE6" s="166">
+      <c r="EE6" s="168">
         <f>IF(EE5="","",CHOOSE(WEEKDAY(EE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EF6" s="166">
+      <c r="EF6" s="168">
         <f>IF(EF5="","",CHOOSE(WEEKDAY(EF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EG6" s="166">
+      <c r="EG6" s="168">
         <f>IF(EG5="","",CHOOSE(WEEKDAY(EG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EH6" s="166">
+      <c r="EH6" s="168">
         <f>IF(EH5="","",CHOOSE(WEEKDAY(EH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EI6" s="166">
+      <c r="EI6" s="168">
         <f>IF(EI5="","",CHOOSE(WEEKDAY(EI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EJ6" s="166">
+      <c r="EJ6" s="168">
         <f>IF(EJ5="","",CHOOSE(WEEKDAY(EJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EK6" s="166">
+      <c r="EK6" s="168">
         <f>IF(EK5="","",CHOOSE(WEEKDAY(EK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EL6" s="166">
+      <c r="EL6" s="168">
         <f>IF(EL5="","",CHOOSE(WEEKDAY(EL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EM6" s="166">
+      <c r="EM6" s="168">
         <f>IF(EM5="","",CHOOSE(WEEKDAY(EM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EN6" s="167">
+      <c r="EN6" s="169">
         <f>IF(EN5="","",CHOOSE(WEEKDAY(EN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EO6" s="167">
+      <c r="EO6" s="169">
         <f>IF(EO5="","",CHOOSE(WEEKDAY(EO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EP6" s="167">
+      <c r="EP6" s="169">
         <f>IF(EP5="","",CHOOSE(WEEKDAY(EP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EQ6" s="167">
+      <c r="EQ6" s="169">
         <f>IF(EQ5="","",CHOOSE(WEEKDAY(EQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ER6" s="167">
+      <c r="ER6" s="169">
         <f>IF(ER5="","",CHOOSE(WEEKDAY(ER5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ES6" s="167">
+      <c r="ES6" s="169">
         <f>IF(ES5="","",CHOOSE(WEEKDAY(ES5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ET6" s="167">
+      <c r="ET6" s="169">
         <f>IF(ET5="","",CHOOSE(WEEKDAY(ET5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EU6" s="167">
+      <c r="EU6" s="169">
         <f>IF(EU5="","",CHOOSE(WEEKDAY(EU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EV6" s="167">
+      <c r="EV6" s="169">
         <f>IF(EV5="","",CHOOSE(WEEKDAY(EV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EW6" s="167">
+      <c r="EW6" s="169">
         <f>IF(EW5="","",CHOOSE(WEEKDAY(EW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EX6" s="167">
+      <c r="EX6" s="169">
         <f>IF(EX5="","",CHOOSE(WEEKDAY(EX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EY6" s="167">
+      <c r="EY6" s="169">
         <f>IF(EY5="","",CHOOSE(WEEKDAY(EY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="EZ6" s="167">
+      <c r="EZ6" s="169">
         <f>IF(EZ5="","",CHOOSE(WEEKDAY(EZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FA6" s="167">
+      <c r="FA6" s="169">
         <f>IF(FA5="","",CHOOSE(WEEKDAY(FA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FB6" s="167">
+      <c r="FB6" s="169">
         <f>IF(FB5="","",CHOOSE(WEEKDAY(FB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FC6" s="167">
+      <c r="FC6" s="169">
         <f>IF(FC5="","",CHOOSE(WEEKDAY(FC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FD6" s="167">
+      <c r="FD6" s="169">
         <f>IF(FD5="","",CHOOSE(WEEKDAY(FD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FE6" s="167">
+      <c r="FE6" s="169">
         <f>IF(FE5="","",CHOOSE(WEEKDAY(FE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FF6" s="167">
+      <c r="FF6" s="169">
         <f>IF(FF5="","",CHOOSE(WEEKDAY(FF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FG6" s="167">
+      <c r="FG6" s="169">
         <f>IF(FG5="","",CHOOSE(WEEKDAY(FG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FH6" s="167">
+      <c r="FH6" s="169">
         <f>IF(FH5="","",CHOOSE(WEEKDAY(FH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FI6" s="167">
+      <c r="FI6" s="169">
         <f>IF(FI5="","",CHOOSE(WEEKDAY(FI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FJ6" s="167">
+      <c r="FJ6" s="169">
         <f>IF(FJ5="","",CHOOSE(WEEKDAY(FJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FK6" s="167">
+      <c r="FK6" s="169">
         <f>IF(FK5="","",CHOOSE(WEEKDAY(FK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FL6" s="167">
+      <c r="FL6" s="169">
         <f>IF(FL5="","",CHOOSE(WEEKDAY(FL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FM6" s="167">
+      <c r="FM6" s="169">
         <f>IF(FM5="","",CHOOSE(WEEKDAY(FM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FN6" s="167">
+      <c r="FN6" s="169">
         <f>IF(FN5="","",CHOOSE(WEEKDAY(FN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FO6" s="167">
+      <c r="FO6" s="169">
         <f>IF(FO5="","",CHOOSE(WEEKDAY(FO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FP6" s="167">
+      <c r="FP6" s="169">
         <f>IF(FP5="","",CHOOSE(WEEKDAY(FP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FQ6" s="167">
+      <c r="FQ6" s="169">
         <f>IF(FQ5="","",CHOOSE(WEEKDAY(FQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FR6" s="167">
+      <c r="FR6" s="169">
         <f>IF(FR5="","",CHOOSE(WEEKDAY(FR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FS6" s="167">
+      <c r="FS6" s="169">
         <f>IF(FS5="","",CHOOSE(WEEKDAY(FS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FT6" s="167">
+      <c r="FT6" s="169">
         <f>IF(FT5="","",CHOOSE(WEEKDAY(FT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FU6" s="167">
+      <c r="FU6" s="169">
         <f>IF(FU5="","",CHOOSE(WEEKDAY(FU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FV6" s="167">
+      <c r="FV6" s="169">
         <f>IF(FV5="","",CHOOSE(WEEKDAY(FV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FW6" s="167">
+      <c r="FW6" s="169">
         <f>IF(FW5="","",CHOOSE(WEEKDAY(FW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FX6" s="167">
+      <c r="FX6" s="169">
         <f>IF(FX5="","",CHOOSE(WEEKDAY(FX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FY6" s="167">
+      <c r="FY6" s="169">
         <f>IF(FY5="","",CHOOSE(WEEKDAY(FY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="FZ6" s="167">
+      <c r="FZ6" s="169">
         <f>IF(FZ5="","",CHOOSE(WEEKDAY(FZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GA6" s="167">
+      <c r="GA6" s="169">
         <f>IF(GA5="","",CHOOSE(WEEKDAY(GA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GB6" s="167">
+      <c r="GB6" s="169">
         <f>IF(GB5="","",CHOOSE(WEEKDAY(GB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GC6" s="167">
+      <c r="GC6" s="169">
         <f>IF(GC5="","",CHOOSE(WEEKDAY(GC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GD6" s="167">
+      <c r="GD6" s="169">
         <f>IF(GD5="","",CHOOSE(WEEKDAY(GD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GE6" s="167">
+      <c r="GE6" s="169">
         <f>IF(GE5="","",CHOOSE(WEEKDAY(GE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GF6" s="167">
+      <c r="GF6" s="169">
         <f>IF(GF5="","",CHOOSE(WEEKDAY(GF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GG6" s="167">
+      <c r="GG6" s="169">
         <f>IF(GG5="","",CHOOSE(WEEKDAY(GG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GH6" s="167">
+      <c r="GH6" s="169">
         <f>IF(GH5="","",CHOOSE(WEEKDAY(GH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GI6" s="167">
+      <c r="GI6" s="169">
         <f>IF(GI5="","",CHOOSE(WEEKDAY(GI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GJ6" s="167">
+      <c r="GJ6" s="169">
         <f>IF(GJ5="","",CHOOSE(WEEKDAY(GJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GK6" s="167">
+      <c r="GK6" s="169">
         <f>IF(GK5="","",CHOOSE(WEEKDAY(GK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GL6" s="167">
+      <c r="GL6" s="169">
         <f>IF(GL5="","",CHOOSE(WEEKDAY(GL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GM6" s="167">
+      <c r="GM6" s="169">
         <f>IF(GM5="","",CHOOSE(WEEKDAY(GM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GN6" s="167">
+      <c r="GN6" s="169">
         <f>IF(GN5="","",CHOOSE(WEEKDAY(GN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GO6" s="167">
+      <c r="GO6" s="169">
         <f>IF(GO5="","",CHOOSE(WEEKDAY(GO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GP6" s="167">
+      <c r="GP6" s="169">
         <f>IF(GP5="","",CHOOSE(WEEKDAY(GP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GQ6" s="167">
+      <c r="GQ6" s="169">
         <f>IF(GQ5="","",CHOOSE(WEEKDAY(GQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GR6" s="167">
+      <c r="GR6" s="169">
         <f>IF(GR5="","",CHOOSE(WEEKDAY(GR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GS6" s="167">
+      <c r="GS6" s="169">
         <f>IF(GS5="","",CHOOSE(WEEKDAY(GS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GT6" s="167">
+      <c r="GT6" s="169">
         <f>IF(GT5="","",CHOOSE(WEEKDAY(GT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GU6" s="167">
+      <c r="GU6" s="169">
         <f>IF(GU5="","",CHOOSE(WEEKDAY(GU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GV6" s="167">
+      <c r="GV6" s="169">
         <f>IF(GV5="","",CHOOSE(WEEKDAY(GV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GW6" s="167">
+      <c r="GW6" s="169">
         <f>IF(GW5="","",CHOOSE(WEEKDAY(GW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GX6" s="167">
+      <c r="GX6" s="169">
         <f>IF(GX5="","",CHOOSE(WEEKDAY(GX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GY6" s="167">
+      <c r="GY6" s="169">
         <f>IF(GY5="","",CHOOSE(WEEKDAY(GY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="GZ6" s="167">
+      <c r="GZ6" s="169">
         <f>IF(GZ5="","",CHOOSE(WEEKDAY(GZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HA6" s="167">
+      <c r="HA6" s="169">
         <f>IF(HA5="","",CHOOSE(WEEKDAY(HA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HB6" s="167">
+      <c r="HB6" s="169">
         <f>IF(HB5="","",CHOOSE(WEEKDAY(HB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HC6" s="167">
+      <c r="HC6" s="169">
         <f>IF(HC5="","",CHOOSE(WEEKDAY(HC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HD6" s="167">
+      <c r="HD6" s="169">
         <f>IF(HD5="","",CHOOSE(WEEKDAY(HD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HE6" s="167">
+      <c r="HE6" s="169">
         <f>IF(HE5="","",CHOOSE(WEEKDAY(HE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HF6" s="167">
+      <c r="HF6" s="169">
         <f>IF(HF5="","",CHOOSE(WEEKDAY(HF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HG6" s="167">
+      <c r="HG6" s="169">
         <f>IF(HG5="","",CHOOSE(WEEKDAY(HG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HH6" s="167">
+      <c r="HH6" s="169">
         <f>IF(HH5="","",CHOOSE(WEEKDAY(HH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HI6" s="167">
+      <c r="HI6" s="169">
         <f>IF(HI5="","",CHOOSE(WEEKDAY(HI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HJ6" s="167">
+      <c r="HJ6" s="169">
         <f>IF(HJ5="","",CHOOSE(WEEKDAY(HJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HK6" s="167">
+      <c r="HK6" s="169">
         <f>IF(HK5="","",CHOOSE(WEEKDAY(HK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HL6" s="167">
+      <c r="HL6" s="169">
         <f>IF(HL5="","",CHOOSE(WEEKDAY(HL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HM6" s="167">
+      <c r="HM6" s="169">
         <f>IF(HM5="","",CHOOSE(WEEKDAY(HM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HN6" s="167">
+      <c r="HN6" s="169">
         <f>IF(HN5="","",CHOOSE(WEEKDAY(HN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HO6" s="167">
+      <c r="HO6" s="169">
         <f>IF(HO5="","",CHOOSE(WEEKDAY(HO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HP6" s="167">
+      <c r="HP6" s="169">
         <f>IF(HP5="","",CHOOSE(WEEKDAY(HP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HQ6" s="167">
+      <c r="HQ6" s="169">
         <f>IF(HQ5="","",CHOOSE(WEEKDAY(HQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HR6" s="167">
+      <c r="HR6" s="169">
         <f>IF(HR5="","",CHOOSE(WEEKDAY(HR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HS6" s="167">
+      <c r="HS6" s="169">
         <f>IF(HS5="","",CHOOSE(WEEKDAY(HS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HT6" s="167">
+      <c r="HT6" s="169">
         <f>IF(HT5="","",CHOOSE(WEEKDAY(HT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HU6" s="167">
+      <c r="HU6" s="169">
         <f>IF(HU5="","",CHOOSE(WEEKDAY(HU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HV6" s="167">
+      <c r="HV6" s="169">
         <f>IF(HV5="","",CHOOSE(WEEKDAY(HV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HW6" s="167">
+      <c r="HW6" s="169">
         <f>IF(HW5="","",CHOOSE(WEEKDAY(HW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HX6" s="167">
+      <c r="HX6" s="169">
         <f>IF(HX5="","",CHOOSE(WEEKDAY(HX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HY6" s="167">
+      <c r="HY6" s="169">
         <f>IF(HY5="","",CHOOSE(WEEKDAY(HY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="HZ6" s="167">
+      <c r="HZ6" s="169">
         <f>IF(HZ5="","",CHOOSE(WEEKDAY(HZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IA6" s="167">
+      <c r="IA6" s="169">
         <f>IF(IA5="","",CHOOSE(WEEKDAY(IA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IB6" s="167">
+      <c r="IB6" s="169">
         <f>IF(IB5="","",CHOOSE(WEEKDAY(IB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IC6" s="167">
+      <c r="IC6" s="169">
         <f>IF(IC5="","",CHOOSE(WEEKDAY(IC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ID6" s="167">
+      <c r="ID6" s="169">
         <f>IF(ID5="","",CHOOSE(WEEKDAY(ID5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IE6" s="167">
+      <c r="IE6" s="169">
         <f>IF(IE5="","",CHOOSE(WEEKDAY(IE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IF6" s="167">
+      <c r="IF6" s="169">
         <f>IF(IF5="","",CHOOSE(WEEKDAY(IF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IG6" s="167">
+      <c r="IG6" s="169">
         <f>IF(IG5="","",CHOOSE(WEEKDAY(IG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IH6" s="167">
+      <c r="IH6" s="169">
         <f>IF(IH5="","",CHOOSE(WEEKDAY(IH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="II6" s="167">
+      <c r="II6" s="169">
         <f>IF(II5="","",CHOOSE(WEEKDAY(II5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IJ6" s="167">
+      <c r="IJ6" s="169">
         <f>IF(IJ5="","",CHOOSE(WEEKDAY(IJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IK6" s="167">
+      <c r="IK6" s="169">
         <f>IF(IK5="","",CHOOSE(WEEKDAY(IK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IL6" s="167">
+      <c r="IL6" s="169">
         <f>IF(IL5="","",CHOOSE(WEEKDAY(IL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IM6" s="167">
+      <c r="IM6" s="169">
         <f>IF(IM5="","",CHOOSE(WEEKDAY(IM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IN6" s="167">
+      <c r="IN6" s="169">
         <f>IF(IN5="","",CHOOSE(WEEKDAY(IN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IO6" s="167">
+      <c r="IO6" s="169">
         <f>IF(IO5="","",CHOOSE(WEEKDAY(IO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IP6" s="167">
+      <c r="IP6" s="169">
         <f>IF(IP5="","",CHOOSE(WEEKDAY(IP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IQ6" s="167">
+      <c r="IQ6" s="169">
         <f>IF(IQ5="","",CHOOSE(WEEKDAY(IQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IR6" s="167">
+      <c r="IR6" s="169">
         <f>IF(IR5="","",CHOOSE(WEEKDAY(IR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IS6" s="167">
+      <c r="IS6" s="169">
         <f>IF(IS5="","",CHOOSE(WEEKDAY(IS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IT6" s="167">
+      <c r="IT6" s="169">
         <f>IF(IT5="","",CHOOSE(WEEKDAY(IT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IU6" s="167">
+      <c r="IU6" s="169">
         <f>IF(IU5="","",CHOOSE(WEEKDAY(IU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IV6" s="167">
+      <c r="IV6" s="169">
         <f>IF(IV5="","",CHOOSE(WEEKDAY(IV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IW6" s="167">
+      <c r="IW6" s="169">
         <f>IF(IW5="","",CHOOSE(WEEKDAY(IW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IX6" s="167">
+      <c r="IX6" s="169">
         <f>IF(IX5="","",CHOOSE(WEEKDAY(IX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IY6" s="167">
+      <c r="IY6" s="169">
         <f>IF(IY5="","",CHOOSE(WEEKDAY(IY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="IZ6" s="167">
+      <c r="IZ6" s="169">
         <f>IF(IZ5="","",CHOOSE(WEEKDAY(IZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JA6" s="167">
+      <c r="JA6" s="169">
         <f>IF(JA5="","",CHOOSE(WEEKDAY(JA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JB6" s="167">
+      <c r="JB6" s="169">
         <f>IF(JB5="","",CHOOSE(WEEKDAY(JB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JC6" s="167">
+      <c r="JC6" s="169">
         <f>IF(JC5="","",CHOOSE(WEEKDAY(JC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JD6" s="167">
+      <c r="JD6" s="169">
         <f>IF(JD5="","",CHOOSE(WEEKDAY(JD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JE6" s="167">
+      <c r="JE6" s="169">
         <f>IF(JE5="","",CHOOSE(WEEKDAY(JE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JF6" s="167">
+      <c r="JF6" s="169">
         <f>IF(JF5="","",CHOOSE(WEEKDAY(JF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JG6" s="167">
+      <c r="JG6" s="169">
         <f>IF(JG5="","",CHOOSE(WEEKDAY(JG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JH6" s="167">
+      <c r="JH6" s="169">
         <f>IF(JH5="","",CHOOSE(WEEKDAY(JH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JI6" s="167">
+      <c r="JI6" s="169">
         <f>IF(JI5="","",CHOOSE(WEEKDAY(JI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JJ6" s="167">
+      <c r="JJ6" s="169">
         <f>IF(JJ5="","",CHOOSE(WEEKDAY(JJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JK6" s="167">
+      <c r="JK6" s="169">
         <f>IF(JK5="","",CHOOSE(WEEKDAY(JK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JL6" s="167">
+      <c r="JL6" s="169">
         <f>IF(JL5="","",CHOOSE(WEEKDAY(JL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JM6" s="167">
+      <c r="JM6" s="169">
         <f>IF(JM5="","",CHOOSE(WEEKDAY(JM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JN6" s="167">
+      <c r="JN6" s="169">
         <f>IF(JN5="","",CHOOSE(WEEKDAY(JN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JO6" s="167">
+      <c r="JO6" s="169">
         <f>IF(JO5="","",CHOOSE(WEEKDAY(JO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JP6" s="167">
+      <c r="JP6" s="169">
         <f>IF(JP5="","",CHOOSE(WEEKDAY(JP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JQ6" s="167">
+      <c r="JQ6" s="169">
         <f>IF(JQ5="","",CHOOSE(WEEKDAY(JQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JR6" s="167">
+      <c r="JR6" s="169">
         <f>IF(JR5="","",CHOOSE(WEEKDAY(JR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JS6" s="167">
+      <c r="JS6" s="169">
         <f>IF(JS5="","",CHOOSE(WEEKDAY(JS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JT6" s="167">
+      <c r="JT6" s="169">
         <f>IF(JT5="","",CHOOSE(WEEKDAY(JT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JU6" s="167">
+      <c r="JU6" s="169">
         <f>IF(JU5="","",CHOOSE(WEEKDAY(JU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JV6" s="167">
+      <c r="JV6" s="169">
         <f>IF(JV5="","",CHOOSE(WEEKDAY(JV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JW6" s="167">
+      <c r="JW6" s="169">
         <f>IF(JW5="","",CHOOSE(WEEKDAY(JW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JX6" s="167">
+      <c r="JX6" s="169">
         <f>IF(JX5="","",CHOOSE(WEEKDAY(JX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JY6" s="167">
+      <c r="JY6" s="169">
         <f>IF(JY5="","",CHOOSE(WEEKDAY(JY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="JZ6" s="167">
+      <c r="JZ6" s="169">
         <f>IF(JZ5="","",CHOOSE(WEEKDAY(JZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KA6" s="167">
+      <c r="KA6" s="169">
         <f>IF(KA5="","",CHOOSE(WEEKDAY(KA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KB6" s="167">
+      <c r="KB6" s="169">
         <f>IF(KB5="","",CHOOSE(WEEKDAY(KB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KC6" s="167">
+      <c r="KC6" s="169">
         <f>IF(KC5="","",CHOOSE(WEEKDAY(KC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KD6" s="167">
+      <c r="KD6" s="169">
         <f>IF(KD5="","",CHOOSE(WEEKDAY(KD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KE6" s="167">
+      <c r="KE6" s="169">
         <f>IF(KE5="","",CHOOSE(WEEKDAY(KE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KF6" s="167">
+      <c r="KF6" s="169">
         <f>IF(KF5="","",CHOOSE(WEEKDAY(KF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KG6" s="167">
+      <c r="KG6" s="169">
         <f>IF(KG5="","",CHOOSE(WEEKDAY(KG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KH6" s="167">
+      <c r="KH6" s="169">
         <f>IF(KH5="","",CHOOSE(WEEKDAY(KH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KI6" s="167">
+      <c r="KI6" s="169">
         <f>IF(KI5="","",CHOOSE(WEEKDAY(KI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KJ6" s="167">
+      <c r="KJ6" s="169">
         <f>IF(KJ5="","",CHOOSE(WEEKDAY(KJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KK6" s="167">
+      <c r="KK6" s="169">
         <f>IF(KK5="","",CHOOSE(WEEKDAY(KK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KL6" s="167">
+      <c r="KL6" s="169">
         <f>IF(KL5="","",CHOOSE(WEEKDAY(KL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KM6" s="167">
+      <c r="KM6" s="169">
         <f>IF(KM5="","",CHOOSE(WEEKDAY(KM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KN6" s="167">
+      <c r="KN6" s="169">
         <f>IF(KN5="","",CHOOSE(WEEKDAY(KN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KO6" s="167">
+      <c r="KO6" s="169">
         <f>IF(KO5="","",CHOOSE(WEEKDAY(KO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KP6" s="167">
+      <c r="KP6" s="169">
         <f>IF(KP5="","",CHOOSE(WEEKDAY(KP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KQ6" s="167">
+      <c r="KQ6" s="169">
         <f>IF(KQ5="","",CHOOSE(WEEKDAY(KQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KR6" s="167">
+      <c r="KR6" s="169">
         <f>IF(KR5="","",CHOOSE(WEEKDAY(KR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KS6" s="167">
+      <c r="KS6" s="169">
         <f>IF(KS5="","",CHOOSE(WEEKDAY(KS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KT6" s="167">
+      <c r="KT6" s="169">
         <f>IF(KT5="","",CHOOSE(WEEKDAY(KT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KU6" s="167">
+      <c r="KU6" s="169">
         <f>IF(KU5="","",CHOOSE(WEEKDAY(KU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KV6" s="167">
+      <c r="KV6" s="169">
         <f>IF(KV5="","",CHOOSE(WEEKDAY(KV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KW6" s="167">
+      <c r="KW6" s="169">
         <f>IF(KW5="","",CHOOSE(WEEKDAY(KW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KX6" s="167">
+      <c r="KX6" s="169">
         <f>IF(KX5="","",CHOOSE(WEEKDAY(KX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KY6" s="167">
+      <c r="KY6" s="169">
         <f>IF(KY5="","",CHOOSE(WEEKDAY(KY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="KZ6" s="167">
+      <c r="KZ6" s="169">
         <f>IF(KZ5="","",CHOOSE(WEEKDAY(KZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LA6" s="167">
+      <c r="LA6" s="169">
         <f>IF(LA5="","",CHOOSE(WEEKDAY(LA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LB6" s="167">
+      <c r="LB6" s="169">
         <f>IF(LB5="","",CHOOSE(WEEKDAY(LB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LC6" s="167">
+      <c r="LC6" s="169">
         <f>IF(LC5="","",CHOOSE(WEEKDAY(LC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LD6" s="167">
+      <c r="LD6" s="169">
         <f>IF(LD5="","",CHOOSE(WEEKDAY(LD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LE6" s="167">
+      <c r="LE6" s="169">
         <f>IF(LE5="","",CHOOSE(WEEKDAY(LE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LF6" s="167">
+      <c r="LF6" s="169">
         <f>IF(LF5="","",CHOOSE(WEEKDAY(LF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LG6" s="167">
+      <c r="LG6" s="169">
         <f>IF(LG5="","",CHOOSE(WEEKDAY(LG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LH6" s="167">
+      <c r="LH6" s="169">
         <f>IF(LH5="","",CHOOSE(WEEKDAY(LH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LI6" s="167">
+      <c r="LI6" s="169">
         <f>IF(LI5="","",CHOOSE(WEEKDAY(LI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LJ6" s="167">
+      <c r="LJ6" s="169">
         <f>IF(LJ5="","",CHOOSE(WEEKDAY(LJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LK6" s="167">
+      <c r="LK6" s="169">
         <f>IF(LK5="","",CHOOSE(WEEKDAY(LK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LL6" s="167">
+      <c r="LL6" s="169">
         <f>IF(LL5="","",CHOOSE(WEEKDAY(LL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LM6" s="167">
+      <c r="LM6" s="169">
         <f>IF(LM5="","",CHOOSE(WEEKDAY(LM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LN6" s="167">
+      <c r="LN6" s="169">
         <f>IF(LN5="","",CHOOSE(WEEKDAY(LN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LO6" s="167">
+      <c r="LO6" s="169">
         <f>IF(LO5="","",CHOOSE(WEEKDAY(LO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LP6" s="167">
+      <c r="LP6" s="169">
         <f>IF(LP5="","",CHOOSE(WEEKDAY(LP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LQ6" s="167">
+      <c r="LQ6" s="169">
         <f>IF(LQ5="","",CHOOSE(WEEKDAY(LQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LR6" s="167">
+      <c r="LR6" s="169">
         <f>IF(LR5="","",CHOOSE(WEEKDAY(LR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LS6" s="167">
+      <c r="LS6" s="169">
         <f>IF(LS5="","",CHOOSE(WEEKDAY(LS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LT6" s="167">
+      <c r="LT6" s="169">
         <f>IF(LT5="","",CHOOSE(WEEKDAY(LT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LU6" s="167">
+      <c r="LU6" s="169">
         <f>IF(LU5="","",CHOOSE(WEEKDAY(LU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LV6" s="167">
+      <c r="LV6" s="169">
         <f>IF(LV5="","",CHOOSE(WEEKDAY(LV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LW6" s="167">
+      <c r="LW6" s="169">
         <f>IF(LW5="","",CHOOSE(WEEKDAY(LW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LX6" s="167">
+      <c r="LX6" s="169">
         <f>IF(LX5="","",CHOOSE(WEEKDAY(LX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LY6" s="167">
+      <c r="LY6" s="169">
         <f>IF(LY5="","",CHOOSE(WEEKDAY(LY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="LZ6" s="167">
+      <c r="LZ6" s="169">
         <f>IF(LZ5="","",CHOOSE(WEEKDAY(LZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MA6" s="167">
+      <c r="MA6" s="169">
         <f>IF(MA5="","",CHOOSE(WEEKDAY(MA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MB6" s="167">
+      <c r="MB6" s="169">
         <f>IF(MB5="","",CHOOSE(WEEKDAY(MB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MC6" s="167">
+      <c r="MC6" s="169">
         <f>IF(MC5="","",CHOOSE(WEEKDAY(MC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MD6" s="167">
+      <c r="MD6" s="169">
         <f>IF(MD5="","",CHOOSE(WEEKDAY(MD5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ME6" s="167">
+      <c r="ME6" s="169">
         <f>IF(ME5="","",CHOOSE(WEEKDAY(ME5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MF6" s="167">
+      <c r="MF6" s="169">
         <f>IF(MF5="","",CHOOSE(WEEKDAY(MF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MG6" s="167">
+      <c r="MG6" s="169">
         <f>IF(MG5="","",CHOOSE(WEEKDAY(MG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MH6" s="167">
+      <c r="MH6" s="169">
         <f>IF(MH5="","",CHOOSE(WEEKDAY(MH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MI6" s="167">
+      <c r="MI6" s="169">
         <f>IF(MI5="","",CHOOSE(WEEKDAY(MI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MJ6" s="167">
+      <c r="MJ6" s="169">
         <f>IF(MJ5="","",CHOOSE(WEEKDAY(MJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MK6" s="167">
+      <c r="MK6" s="169">
         <f>IF(MK5="","",CHOOSE(WEEKDAY(MK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ML6" s="167">
+      <c r="ML6" s="169">
         <f>IF(ML5="","",CHOOSE(WEEKDAY(ML5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MM6" s="167">
+      <c r="MM6" s="169">
         <f>IF(MM5="","",CHOOSE(WEEKDAY(MM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MN6" s="167">
+      <c r="MN6" s="169">
         <f>IF(MN5="","",CHOOSE(WEEKDAY(MN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MO6" s="167">
+      <c r="MO6" s="169">
         <f>IF(MO5="","",CHOOSE(WEEKDAY(MO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MP6" s="167">
+      <c r="MP6" s="169">
         <f>IF(MP5="","",CHOOSE(WEEKDAY(MP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MQ6" s="167">
+      <c r="MQ6" s="169">
         <f>IF(MQ5="","",CHOOSE(WEEKDAY(MQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MR6" s="167">
+      <c r="MR6" s="169">
         <f>IF(MR5="","",CHOOSE(WEEKDAY(MR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MS6" s="167">
+      <c r="MS6" s="169">
         <f>IF(MS5="","",CHOOSE(WEEKDAY(MS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MT6" s="167">
+      <c r="MT6" s="169">
         <f>IF(MT5="","",CHOOSE(WEEKDAY(MT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MU6" s="167">
+      <c r="MU6" s="169">
         <f>IF(MU5="","",CHOOSE(WEEKDAY(MU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MV6" s="167">
+      <c r="MV6" s="169">
         <f>IF(MV5="","",CHOOSE(WEEKDAY(MV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MW6" s="167">
+      <c r="MW6" s="169">
         <f>IF(MW5="","",CHOOSE(WEEKDAY(MW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MX6" s="167">
+      <c r="MX6" s="169">
         <f>IF(MX5="","",CHOOSE(WEEKDAY(MX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MY6" s="167">
+      <c r="MY6" s="169">
         <f>IF(MY5="","",CHOOSE(WEEKDAY(MY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="MZ6" s="167">
+      <c r="MZ6" s="169">
         <f>IF(MZ5="","",CHOOSE(WEEKDAY(MZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NA6" s="167">
+      <c r="NA6" s="169">
         <f>IF(NA5="","",CHOOSE(WEEKDAY(NA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NB6" s="167">
+      <c r="NB6" s="169">
         <f>IF(NB5="","",CHOOSE(WEEKDAY(NB5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NC6" s="167">
+      <c r="NC6" s="169">
         <f>IF(NC5="","",CHOOSE(WEEKDAY(NC5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="ND6" s="167">
+      <c r="ND6" s="169">
         <f>IF(ND5="","",CHOOSE(WEEKDAY(ND5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NE6" s="167">
+      <c r="NE6" s="169">
         <f>IF(NE5="","",CHOOSE(WEEKDAY(NE5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NF6" s="167">
+      <c r="NF6" s="169">
         <f>IF(NF5="","",CHOOSE(WEEKDAY(NF5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NG6" s="167">
+      <c r="NG6" s="169">
         <f>IF(NG5="","",CHOOSE(WEEKDAY(NG5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NH6" s="167">
+      <c r="NH6" s="169">
         <f>IF(NH5="","",CHOOSE(WEEKDAY(NH5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NI6" s="167">
+      <c r="NI6" s="169">
         <f>IF(NI5="","",CHOOSE(WEEKDAY(NI5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NJ6" s="167">
+      <c r="NJ6" s="169">
         <f>IF(NJ5="","",CHOOSE(WEEKDAY(NJ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NK6" s="167">
+      <c r="NK6" s="169">
         <f>IF(NK5="","",CHOOSE(WEEKDAY(NK5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NL6" s="167">
+      <c r="NL6" s="169">
         <f>IF(NL5="","",CHOOSE(WEEKDAY(NL5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NM6" s="167">
+      <c r="NM6" s="169">
         <f>IF(NM5="","",CHOOSE(WEEKDAY(NM5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NN6" s="167">
+      <c r="NN6" s="169">
         <f>IF(NN5="","",CHOOSE(WEEKDAY(NN5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NO6" s="167">
+      <c r="NO6" s="169">
         <f>IF(NO5="","",CHOOSE(WEEKDAY(NO5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NP6" s="167">
+      <c r="NP6" s="169">
         <f>IF(NP5="","",CHOOSE(WEEKDAY(NP5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NQ6" s="167">
+      <c r="NQ6" s="169">
         <f>IF(NQ5="","",CHOOSE(WEEKDAY(NQ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NR6" s="167">
+      <c r="NR6" s="169">
         <f>IF(NR5="","",CHOOSE(WEEKDAY(NR5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NS6" s="167">
+      <c r="NS6" s="169">
         <f>IF(NS5="","",CHOOSE(WEEKDAY(NS5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NT6" s="167">
+      <c r="NT6" s="169">
         <f>IF(NT5="","",CHOOSE(WEEKDAY(NT5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NU6" s="167">
+      <c r="NU6" s="169">
         <f>IF(NU5="","",CHOOSE(WEEKDAY(NU5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NV6" s="167">
+      <c r="NV6" s="169">
         <f>IF(NV5="","",CHOOSE(WEEKDAY(NV5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NW6" s="167">
+      <c r="NW6" s="169">
         <f>IF(NW5="","",CHOOSE(WEEKDAY(NW5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NX6" s="167">
+      <c r="NX6" s="169">
         <f>IF(NX5="","",CHOOSE(WEEKDAY(NX5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NY6" s="167">
+      <c r="NY6" s="169">
         <f>IF(NY5="","",CHOOSE(WEEKDAY(NY5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="NZ6" s="167">
+      <c r="NZ6" s="169">
         <f>IF(NZ5="","",CHOOSE(WEEKDAY(NZ5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
-      <c r="OA6" s="167">
+      <c r="OA6" s="169">
         <f>IF(OA5="","",CHOOSE(WEEKDAY(OA5,2),"월","화","수","목","금","토","일"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="104">
-      <c r="A7" s="168" t="n"/>
-      <c r="B7" s="168" t="n"/>
-      <c r="C7" s="168" t="n"/>
-      <c r="D7" s="169" t="n"/>
-      <c r="E7" s="169" t="n"/>
-      <c r="F7" s="169" t="n"/>
-      <c r="G7" s="170" t="n"/>
-      <c r="H7" s="170" t="n"/>
-      <c r="I7" s="170" t="n"/>
-      <c r="J7" s="170" t="n"/>
-      <c r="K7" s="170" t="n"/>
-      <c r="L7" s="171" t="n"/>
-      <c r="M7" s="171" t="n"/>
-      <c r="N7" s="172" t="n"/>
-      <c r="O7" s="173" t="n"/>
-      <c r="P7" s="173" t="n"/>
-      <c r="Q7" s="173" t="n"/>
-      <c r="R7" s="174" t="n"/>
-      <c r="S7" s="174" t="n"/>
-      <c r="T7" s="172" t="n"/>
-      <c r="U7" s="175" t="n"/>
+      <c r="A7" s="170" t="n"/>
+      <c r="B7" s="170" t="n"/>
+      <c r="C7" s="170" t="n"/>
+      <c r="D7" s="171" t="n"/>
+      <c r="E7" s="171" t="n"/>
+      <c r="F7" s="171" t="n"/>
+      <c r="G7" s="172" t="n"/>
+      <c r="H7" s="172" t="n"/>
+      <c r="I7" s="172" t="n"/>
+      <c r="J7" s="172" t="n"/>
+      <c r="K7" s="172" t="n"/>
+      <c r="L7" s="173" t="n"/>
+      <c r="M7" s="173" t="n"/>
+      <c r="N7" s="174" t="n"/>
+      <c r="O7" s="175" t="n"/>
+      <c r="P7" s="175" t="n"/>
+      <c r="Q7" s="175" t="n"/>
+      <c r="R7" s="176" t="n"/>
+      <c r="S7" s="176" t="n"/>
+      <c r="T7" s="174" t="n"/>
+      <c r="U7" s="177" t="n"/>
       <c r="V7" s="44" t="n"/>
       <c r="W7" s="45" t="n"/>
       <c r="X7" s="45" t="n"/>
@@ -35566,27 +35623,27 @@
       <c r="EM7" s="45" t="n"/>
     </row>
     <row r="8" collapsed="1" ht="14.25" customHeight="1" s="104">
-      <c r="A8" s="168" t="n"/>
-      <c r="B8" s="168" t="n"/>
-      <c r="C8" s="168" t="n"/>
-      <c r="D8" s="169" t="n"/>
-      <c r="E8" s="169" t="n"/>
-      <c r="F8" s="169" t="n"/>
-      <c r="G8" s="170" t="n"/>
-      <c r="H8" s="170" t="n"/>
-      <c r="I8" s="170" t="n"/>
-      <c r="J8" s="170" t="n"/>
-      <c r="K8" s="170" t="n"/>
-      <c r="L8" s="171" t="n"/>
-      <c r="M8" s="171" t="n"/>
-      <c r="N8" s="172" t="n"/>
-      <c r="O8" s="173" t="n"/>
-      <c r="P8" s="173" t="n"/>
-      <c r="Q8" s="173" t="n"/>
-      <c r="R8" s="174" t="n"/>
-      <c r="S8" s="174" t="n"/>
-      <c r="T8" s="172" t="n"/>
-      <c r="U8" s="175" t="n"/>
+      <c r="A8" s="170" t="n"/>
+      <c r="B8" s="170" t="n"/>
+      <c r="C8" s="170" t="n"/>
+      <c r="D8" s="171" t="n"/>
+      <c r="E8" s="171" t="n"/>
+      <c r="F8" s="171" t="n"/>
+      <c r="G8" s="172" t="n"/>
+      <c r="H8" s="172" t="n"/>
+      <c r="I8" s="172" t="n"/>
+      <c r="J8" s="172" t="n"/>
+      <c r="K8" s="172" t="n"/>
+      <c r="L8" s="173" t="n"/>
+      <c r="M8" s="173" t="n"/>
+      <c r="N8" s="174" t="n"/>
+      <c r="O8" s="175" t="n"/>
+      <c r="P8" s="175" t="n"/>
+      <c r="Q8" s="175" t="n"/>
+      <c r="R8" s="176" t="n"/>
+      <c r="S8" s="176" t="n"/>
+      <c r="T8" s="174" t="n"/>
+      <c r="U8" s="177" t="n"/>
       <c r="V8" s="44" t="n"/>
       <c r="W8" s="45" t="n"/>
       <c r="X8" s="45" t="n"/>
@@ -35711,27 +35768,27 @@
       <c r="EM8" s="45" t="n"/>
     </row>
     <row r="9" ht="14.25" customHeight="1" s="104">
-      <c r="A9" s="176" t="n"/>
-      <c r="B9" s="176" t="n"/>
-      <c r="C9" s="176" t="n"/>
-      <c r="D9" s="177" t="n"/>
-      <c r="E9" s="177" t="n"/>
-      <c r="F9" s="177" t="n"/>
-      <c r="G9" s="178" t="n"/>
-      <c r="H9" s="178" t="n"/>
-      <c r="I9" s="178" t="n"/>
-      <c r="J9" s="178" t="n"/>
-      <c r="K9" s="178" t="n"/>
-      <c r="L9" s="179" t="n"/>
-      <c r="M9" s="179" t="n"/>
-      <c r="N9" s="180" t="n"/>
-      <c r="O9" s="181" t="n"/>
-      <c r="P9" s="181" t="n"/>
-      <c r="Q9" s="181" t="n"/>
-      <c r="R9" s="182" t="n"/>
-      <c r="S9" s="182" t="n"/>
-      <c r="T9" s="180" t="n"/>
-      <c r="U9" s="183" t="n"/>
+      <c r="A9" s="178" t="n"/>
+      <c r="B9" s="178" t="n"/>
+      <c r="C9" s="178" t="n"/>
+      <c r="D9" s="179" t="n"/>
+      <c r="E9" s="179" t="n"/>
+      <c r="F9" s="179" t="n"/>
+      <c r="G9" s="180" t="n"/>
+      <c r="H9" s="180" t="n"/>
+      <c r="I9" s="180" t="n"/>
+      <c r="J9" s="180" t="n"/>
+      <c r="K9" s="180" t="n"/>
+      <c r="L9" s="181" t="n"/>
+      <c r="M9" s="181" t="n"/>
+      <c r="N9" s="182" t="n"/>
+      <c r="O9" s="183" t="n"/>
+      <c r="P9" s="183" t="n"/>
+      <c r="Q9" s="183" t="n"/>
+      <c r="R9" s="184" t="n"/>
+      <c r="S9" s="184" t="n"/>
+      <c r="T9" s="182" t="n"/>
+      <c r="U9" s="185" t="n"/>
       <c r="V9" s="44" t="n"/>
       <c r="W9" s="45" t="n"/>
       <c r="X9" s="45" t="n"/>
@@ -35856,27 +35913,27 @@
       <c r="EM9" s="45" t="n"/>
     </row>
     <row r="10" collapsed="1" ht="14.25" customHeight="1" s="104">
-      <c r="A10" s="176" t="n"/>
-      <c r="B10" s="176" t="n"/>
-      <c r="C10" s="176" t="n"/>
-      <c r="D10" s="177" t="n"/>
-      <c r="E10" s="177" t="n"/>
-      <c r="F10" s="177" t="n"/>
-      <c r="G10" s="178" t="n"/>
-      <c r="H10" s="178" t="n"/>
-      <c r="I10" s="178" t="n"/>
-      <c r="J10" s="178" t="n"/>
-      <c r="K10" s="178" t="n"/>
-      <c r="L10" s="179" t="n"/>
-      <c r="M10" s="179" t="n"/>
-      <c r="N10" s="180" t="n"/>
-      <c r="O10" s="181" t="n"/>
-      <c r="P10" s="181" t="n"/>
-      <c r="Q10" s="181" t="n"/>
-      <c r="R10" s="182" t="n"/>
-      <c r="S10" s="182" t="n"/>
-      <c r="T10" s="180" t="n"/>
-      <c r="U10" s="183" t="n"/>
+      <c r="A10" s="178" t="n"/>
+      <c r="B10" s="178" t="n"/>
+      <c r="C10" s="178" t="n"/>
+      <c r="D10" s="179" t="n"/>
+      <c r="E10" s="179" t="n"/>
+      <c r="F10" s="179" t="n"/>
+      <c r="G10" s="180" t="n"/>
+      <c r="H10" s="180" t="n"/>
+      <c r="I10" s="180" t="n"/>
+      <c r="J10" s="180" t="n"/>
+      <c r="K10" s="180" t="n"/>
+      <c r="L10" s="181" t="n"/>
+      <c r="M10" s="181" t="n"/>
+      <c r="N10" s="182" t="n"/>
+      <c r="O10" s="183" t="n"/>
+      <c r="P10" s="183" t="n"/>
+      <c r="Q10" s="183" t="n"/>
+      <c r="R10" s="184" t="n"/>
+      <c r="S10" s="184" t="n"/>
+      <c r="T10" s="182" t="n"/>
+      <c r="U10" s="185" t="n"/>
       <c r="V10" s="54" t="n"/>
       <c r="W10" s="55" t="n"/>
       <c r="X10" s="55" t="n"/>
@@ -36001,27 +36058,27 @@
       <c r="EM10" s="55" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="104">
-      <c r="A11" s="184" t="n"/>
-      <c r="B11" s="184" t="n"/>
-      <c r="C11" s="184" t="n"/>
-      <c r="D11" s="185" t="n"/>
-      <c r="E11" s="185" t="n"/>
-      <c r="F11" s="185" t="n"/>
-      <c r="G11" s="186" t="n"/>
-      <c r="H11" s="186" t="n"/>
-      <c r="I11" s="186" t="n"/>
-      <c r="J11" s="186" t="n"/>
-      <c r="K11" s="186" t="n"/>
-      <c r="L11" s="187" t="n"/>
-      <c r="M11" s="187" t="n"/>
-      <c r="N11" s="186" t="n"/>
-      <c r="O11" s="188" t="n"/>
-      <c r="P11" s="188" t="n"/>
-      <c r="Q11" s="188" t="n"/>
-      <c r="R11" s="189" t="n"/>
-      <c r="S11" s="189" t="n"/>
-      <c r="T11" s="186" t="n"/>
-      <c r="U11" s="190" t="n"/>
+      <c r="A11" s="186" t="n"/>
+      <c r="B11" s="186" t="n"/>
+      <c r="C11" s="186" t="n"/>
+      <c r="D11" s="187" t="n"/>
+      <c r="E11" s="187" t="n"/>
+      <c r="F11" s="187" t="n"/>
+      <c r="G11" s="188" t="n"/>
+      <c r="H11" s="188" t="n"/>
+      <c r="I11" s="188" t="n"/>
+      <c r="J11" s="188" t="n"/>
+      <c r="K11" s="188" t="n"/>
+      <c r="L11" s="189" t="n"/>
+      <c r="M11" s="189" t="n"/>
+      <c r="N11" s="188" t="n"/>
+      <c r="O11" s="190" t="n"/>
+      <c r="P11" s="190" t="n"/>
+      <c r="Q11" s="190" t="n"/>
+      <c r="R11" s="191" t="n"/>
+      <c r="S11" s="191" t="n"/>
+      <c r="T11" s="188" t="n"/>
+      <c r="U11" s="192" t="n"/>
       <c r="V11" s="54" t="n"/>
       <c r="W11" s="55" t="n"/>
       <c r="X11" s="55" t="n"/>
@@ -36146,27 +36203,27 @@
       <c r="EM11" s="55" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="104">
-      <c r="A12" s="184" t="n"/>
-      <c r="B12" s="184" t="n"/>
-      <c r="C12" s="184" t="n"/>
-      <c r="D12" s="185" t="n"/>
-      <c r="E12" s="185" t="n"/>
-      <c r="F12" s="185" t="n"/>
-      <c r="G12" s="186" t="n"/>
-      <c r="H12" s="186" t="n"/>
-      <c r="I12" s="186" t="n"/>
-      <c r="J12" s="186" t="n"/>
-      <c r="K12" s="186" t="n"/>
-      <c r="L12" s="187" t="n"/>
-      <c r="M12" s="187" t="n"/>
-      <c r="N12" s="186" t="n"/>
-      <c r="O12" s="188" t="n"/>
-      <c r="P12" s="188" t="n"/>
-      <c r="Q12" s="188" t="n"/>
-      <c r="R12" s="189" t="n"/>
-      <c r="S12" s="189" t="n"/>
-      <c r="T12" s="186" t="n"/>
-      <c r="U12" s="190" t="n"/>
+      <c r="A12" s="186" t="n"/>
+      <c r="B12" s="186" t="n"/>
+      <c r="C12" s="186" t="n"/>
+      <c r="D12" s="187" t="n"/>
+      <c r="E12" s="187" t="n"/>
+      <c r="F12" s="187" t="n"/>
+      <c r="G12" s="188" t="n"/>
+      <c r="H12" s="188" t="n"/>
+      <c r="I12" s="188" t="n"/>
+      <c r="J12" s="188" t="n"/>
+      <c r="K12" s="188" t="n"/>
+      <c r="L12" s="189" t="n"/>
+      <c r="M12" s="189" t="n"/>
+      <c r="N12" s="188" t="n"/>
+      <c r="O12" s="190" t="n"/>
+      <c r="P12" s="190" t="n"/>
+      <c r="Q12" s="190" t="n"/>
+      <c r="R12" s="191" t="n"/>
+      <c r="S12" s="191" t="n"/>
+      <c r="T12" s="188" t="n"/>
+      <c r="U12" s="192" t="n"/>
       <c r="V12" s="54" t="n"/>
       <c r="W12" s="55" t="n"/>
       <c r="X12" s="55" t="n"/>
@@ -36291,27 +36348,27 @@
       <c r="EM12" s="55" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="104">
-      <c r="A13" s="184" t="n"/>
-      <c r="B13" s="184" t="n"/>
-      <c r="C13" s="184" t="n"/>
-      <c r="D13" s="185" t="n"/>
-      <c r="E13" s="185" t="n"/>
-      <c r="F13" s="185" t="n"/>
-      <c r="G13" s="186" t="n"/>
-      <c r="H13" s="187" t="n"/>
-      <c r="I13" s="186" t="n"/>
-      <c r="J13" s="186" t="n"/>
-      <c r="K13" s="186" t="n"/>
-      <c r="L13" s="187" t="n"/>
-      <c r="M13" s="187" t="n"/>
-      <c r="N13" s="186" t="n"/>
-      <c r="O13" s="188" t="n"/>
-      <c r="P13" s="188" t="n"/>
-      <c r="Q13" s="188" t="n"/>
-      <c r="R13" s="189" t="n"/>
-      <c r="S13" s="189" t="n"/>
-      <c r="T13" s="186" t="n"/>
-      <c r="U13" s="190" t="n"/>
+      <c r="A13" s="186" t="n"/>
+      <c r="B13" s="186" t="n"/>
+      <c r="C13" s="186" t="n"/>
+      <c r="D13" s="187" t="n"/>
+      <c r="E13" s="187" t="n"/>
+      <c r="F13" s="187" t="n"/>
+      <c r="G13" s="188" t="n"/>
+      <c r="H13" s="189" t="n"/>
+      <c r="I13" s="188" t="n"/>
+      <c r="J13" s="188" t="n"/>
+      <c r="K13" s="188" t="n"/>
+      <c r="L13" s="189" t="n"/>
+      <c r="M13" s="189" t="n"/>
+      <c r="N13" s="188" t="n"/>
+      <c r="O13" s="190" t="n"/>
+      <c r="P13" s="190" t="n"/>
+      <c r="Q13" s="190" t="n"/>
+      <c r="R13" s="191" t="n"/>
+      <c r="S13" s="191" t="n"/>
+      <c r="T13" s="188" t="n"/>
+      <c r="U13" s="192" t="n"/>
       <c r="V13" s="54" t="n"/>
       <c r="W13" s="55" t="n"/>
       <c r="X13" s="55" t="n"/>
@@ -36436,27 +36493,27 @@
       <c r="EM13" s="55" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1" s="104">
-      <c r="A14" s="184" t="n"/>
-      <c r="B14" s="184" t="n"/>
-      <c r="C14" s="184" t="n"/>
-      <c r="D14" s="185" t="n"/>
-      <c r="E14" s="185" t="n"/>
-      <c r="F14" s="185" t="n"/>
-      <c r="G14" s="186" t="n"/>
-      <c r="H14" s="186" t="n"/>
-      <c r="I14" s="186" t="n"/>
-      <c r="J14" s="186" t="n"/>
-      <c r="K14" s="186" t="n"/>
-      <c r="L14" s="187" t="n"/>
-      <c r="M14" s="187" t="n"/>
-      <c r="N14" s="186" t="n"/>
-      <c r="O14" s="188" t="n"/>
-      <c r="P14" s="188" t="n"/>
-      <c r="Q14" s="188" t="n"/>
-      <c r="R14" s="189" t="n"/>
-      <c r="S14" s="189" t="n"/>
-      <c r="T14" s="186" t="n"/>
-      <c r="U14" s="190" t="n"/>
+      <c r="A14" s="186" t="n"/>
+      <c r="B14" s="186" t="n"/>
+      <c r="C14" s="186" t="n"/>
+      <c r="D14" s="187" t="n"/>
+      <c r="E14" s="187" t="n"/>
+      <c r="F14" s="187" t="n"/>
+      <c r="G14" s="188" t="n"/>
+      <c r="H14" s="188" t="n"/>
+      <c r="I14" s="188" t="n"/>
+      <c r="J14" s="188" t="n"/>
+      <c r="K14" s="188" t="n"/>
+      <c r="L14" s="189" t="n"/>
+      <c r="M14" s="189" t="n"/>
+      <c r="N14" s="188" t="n"/>
+      <c r="O14" s="190" t="n"/>
+      <c r="P14" s="190" t="n"/>
+      <c r="Q14" s="190" t="n"/>
+      <c r="R14" s="191" t="n"/>
+      <c r="S14" s="191" t="n"/>
+      <c r="T14" s="188" t="n"/>
+      <c r="U14" s="192" t="n"/>
       <c r="V14" s="54" t="n"/>
       <c r="W14" s="55" t="n"/>
       <c r="X14" s="55" t="n"/>
@@ -36581,27 +36638,27 @@
       <c r="EM14" s="55" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="104">
-      <c r="A15" s="184" t="n"/>
-      <c r="B15" s="184" t="n"/>
-      <c r="C15" s="184" t="n"/>
-      <c r="D15" s="185" t="n"/>
-      <c r="E15" s="185" t="n"/>
-      <c r="F15" s="185" t="n"/>
-      <c r="G15" s="186" t="n"/>
-      <c r="H15" s="186" t="n"/>
-      <c r="I15" s="186" t="n"/>
-      <c r="J15" s="186" t="n"/>
-      <c r="K15" s="187" t="n"/>
-      <c r="L15" s="187" t="n"/>
-      <c r="M15" s="187" t="n"/>
-      <c r="N15" s="186" t="n"/>
-      <c r="O15" s="188" t="n"/>
-      <c r="P15" s="188" t="n"/>
-      <c r="Q15" s="188" t="n"/>
-      <c r="R15" s="189" t="n"/>
-      <c r="S15" s="189" t="n"/>
-      <c r="T15" s="186" t="n"/>
-      <c r="U15" s="190" t="n"/>
+      <c r="A15" s="186" t="n"/>
+      <c r="B15" s="186" t="n"/>
+      <c r="C15" s="186" t="n"/>
+      <c r="D15" s="187" t="n"/>
+      <c r="E15" s="187" t="n"/>
+      <c r="F15" s="187" t="n"/>
+      <c r="G15" s="188" t="n"/>
+      <c r="H15" s="188" t="n"/>
+      <c r="I15" s="188" t="n"/>
+      <c r="J15" s="188" t="n"/>
+      <c r="K15" s="189" t="n"/>
+      <c r="L15" s="189" t="n"/>
+      <c r="M15" s="189" t="n"/>
+      <c r="N15" s="188" t="n"/>
+      <c r="O15" s="190" t="n"/>
+      <c r="P15" s="190" t="n"/>
+      <c r="Q15" s="190" t="n"/>
+      <c r="R15" s="191" t="n"/>
+      <c r="S15" s="191" t="n"/>
+      <c r="T15" s="188" t="n"/>
+      <c r="U15" s="192" t="n"/>
       <c r="V15" s="54" t="n"/>
       <c r="W15" s="55" t="n"/>
       <c r="X15" s="55" t="n"/>
@@ -36726,27 +36783,27 @@
       <c r="EM15" s="55" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="104">
-      <c r="A16" s="184" t="n"/>
-      <c r="B16" s="184" t="n"/>
-      <c r="C16" s="184" t="n"/>
-      <c r="D16" s="185" t="n"/>
-      <c r="E16" s="185" t="n"/>
-      <c r="F16" s="185" t="n"/>
-      <c r="G16" s="186" t="n"/>
-      <c r="H16" s="187" t="n"/>
-      <c r="I16" s="186" t="n"/>
-      <c r="J16" s="186" t="n"/>
-      <c r="K16" s="187" t="n"/>
-      <c r="L16" s="187" t="n"/>
-      <c r="M16" s="187" t="n"/>
-      <c r="N16" s="186" t="n"/>
-      <c r="O16" s="188" t="n"/>
-      <c r="P16" s="188" t="n"/>
-      <c r="Q16" s="188" t="n"/>
-      <c r="R16" s="189" t="n"/>
-      <c r="S16" s="189" t="n"/>
-      <c r="T16" s="186" t="n"/>
-      <c r="U16" s="190" t="n"/>
+      <c r="A16" s="186" t="n"/>
+      <c r="B16" s="186" t="n"/>
+      <c r="C16" s="186" t="n"/>
+      <c r="D16" s="187" t="n"/>
+      <c r="E16" s="187" t="n"/>
+      <c r="F16" s="187" t="n"/>
+      <c r="G16" s="188" t="n"/>
+      <c r="H16" s="189" t="n"/>
+      <c r="I16" s="188" t="n"/>
+      <c r="J16" s="188" t="n"/>
+      <c r="K16" s="189" t="n"/>
+      <c r="L16" s="189" t="n"/>
+      <c r="M16" s="189" t="n"/>
+      <c r="N16" s="188" t="n"/>
+      <c r="O16" s="190" t="n"/>
+      <c r="P16" s="190" t="n"/>
+      <c r="Q16" s="190" t="n"/>
+      <c r="R16" s="191" t="n"/>
+      <c r="S16" s="191" t="n"/>
+      <c r="T16" s="188" t="n"/>
+      <c r="U16" s="192" t="n"/>
       <c r="V16" s="54" t="n"/>
       <c r="W16" s="55" t="n"/>
       <c r="X16" s="55" t="n"/>
@@ -36871,27 +36928,27 @@
       <c r="EM16" s="55" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" s="104">
-      <c r="A17" s="184" t="n"/>
-      <c r="B17" s="184" t="n"/>
-      <c r="C17" s="184" t="n"/>
-      <c r="D17" s="185" t="n"/>
-      <c r="E17" s="185" t="n"/>
-      <c r="F17" s="185" t="n"/>
-      <c r="G17" s="186" t="n"/>
-      <c r="H17" s="187" t="n"/>
-      <c r="I17" s="186" t="n"/>
-      <c r="J17" s="186" t="n"/>
-      <c r="K17" s="187" t="n"/>
-      <c r="L17" s="187" t="n"/>
-      <c r="M17" s="187" t="n"/>
-      <c r="N17" s="186" t="n"/>
-      <c r="O17" s="188" t="n"/>
-      <c r="P17" s="188" t="n"/>
-      <c r="Q17" s="188" t="n"/>
-      <c r="R17" s="189" t="n"/>
-      <c r="S17" s="189" t="n"/>
-      <c r="T17" s="186" t="n"/>
-      <c r="U17" s="190" t="n"/>
+      <c r="A17" s="186" t="n"/>
+      <c r="B17" s="186" t="n"/>
+      <c r="C17" s="186" t="n"/>
+      <c r="D17" s="187" t="n"/>
+      <c r="E17" s="187" t="n"/>
+      <c r="F17" s="187" t="n"/>
+      <c r="G17" s="188" t="n"/>
+      <c r="H17" s="189" t="n"/>
+      <c r="I17" s="188" t="n"/>
+      <c r="J17" s="188" t="n"/>
+      <c r="K17" s="189" t="n"/>
+      <c r="L17" s="189" t="n"/>
+      <c r="M17" s="189" t="n"/>
+      <c r="N17" s="188" t="n"/>
+      <c r="O17" s="190" t="n"/>
+      <c r="P17" s="190" t="n"/>
+      <c r="Q17" s="190" t="n"/>
+      <c r="R17" s="191" t="n"/>
+      <c r="S17" s="191" t="n"/>
+      <c r="T17" s="188" t="n"/>
+      <c r="U17" s="192" t="n"/>
       <c r="V17" s="54" t="n"/>
       <c r="W17" s="55" t="n"/>
       <c r="X17" s="55" t="n"/>
@@ -37016,27 +37073,27 @@
       <c r="EM17" s="55" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" s="104">
-      <c r="A18" s="184" t="n"/>
-      <c r="B18" s="184" t="n"/>
-      <c r="C18" s="184" t="n"/>
-      <c r="D18" s="185" t="n"/>
-      <c r="E18" s="185" t="n"/>
-      <c r="F18" s="185" t="n"/>
-      <c r="G18" s="186" t="n"/>
-      <c r="H18" s="187" t="n"/>
-      <c r="I18" s="186" t="n"/>
-      <c r="J18" s="186" t="n"/>
-      <c r="K18" s="186" t="n"/>
-      <c r="L18" s="187" t="n"/>
-      <c r="M18" s="187" t="n"/>
-      <c r="N18" s="186" t="n"/>
-      <c r="O18" s="188" t="n"/>
-      <c r="P18" s="188" t="n"/>
-      <c r="Q18" s="188" t="n"/>
-      <c r="R18" s="189" t="n"/>
-      <c r="S18" s="189" t="n"/>
-      <c r="T18" s="186" t="n"/>
-      <c r="U18" s="190" t="n"/>
+      <c r="A18" s="186" t="n"/>
+      <c r="B18" s="186" t="n"/>
+      <c r="C18" s="186" t="n"/>
+      <c r="D18" s="187" t="n"/>
+      <c r="E18" s="187" t="n"/>
+      <c r="F18" s="187" t="n"/>
+      <c r="G18" s="188" t="n"/>
+      <c r="H18" s="189" t="n"/>
+      <c r="I18" s="188" t="n"/>
+      <c r="J18" s="188" t="n"/>
+      <c r="K18" s="188" t="n"/>
+      <c r="L18" s="189" t="n"/>
+      <c r="M18" s="189" t="n"/>
+      <c r="N18" s="188" t="n"/>
+      <c r="O18" s="190" t="n"/>
+      <c r="P18" s="190" t="n"/>
+      <c r="Q18" s="190" t="n"/>
+      <c r="R18" s="191" t="n"/>
+      <c r="S18" s="191" t="n"/>
+      <c r="T18" s="188" t="n"/>
+      <c r="U18" s="192" t="n"/>
       <c r="V18" s="54" t="n"/>
       <c r="W18" s="55" t="n"/>
       <c r="X18" s="55" t="n"/>
@@ -37161,27 +37218,27 @@
       <c r="EM18" s="55" t="n"/>
     </row>
     <row r="19" ht="14.25" customHeight="1" s="104">
-      <c r="A19" s="184" t="n"/>
-      <c r="B19" s="184" t="n"/>
-      <c r="C19" s="184" t="n"/>
-      <c r="D19" s="185" t="n"/>
-      <c r="E19" s="185" t="n"/>
-      <c r="F19" s="185" t="n"/>
-      <c r="G19" s="186" t="n"/>
-      <c r="H19" s="187" t="n"/>
-      <c r="I19" s="186" t="n"/>
-      <c r="J19" s="186" t="n"/>
-      <c r="K19" s="187" t="n"/>
-      <c r="L19" s="187" t="n"/>
-      <c r="M19" s="187" t="n"/>
-      <c r="N19" s="186" t="n"/>
-      <c r="O19" s="188" t="n"/>
-      <c r="P19" s="188" t="n"/>
-      <c r="Q19" s="188" t="n"/>
-      <c r="R19" s="189" t="n"/>
-      <c r="S19" s="189" t="n"/>
-      <c r="T19" s="186" t="n"/>
-      <c r="U19" s="190" t="n"/>
+      <c r="A19" s="186" t="n"/>
+      <c r="B19" s="186" t="n"/>
+      <c r="C19" s="186" t="n"/>
+      <c r="D19" s="187" t="n"/>
+      <c r="E19" s="187" t="n"/>
+      <c r="F19" s="187" t="n"/>
+      <c r="G19" s="188" t="n"/>
+      <c r="H19" s="189" t="n"/>
+      <c r="I19" s="188" t="n"/>
+      <c r="J19" s="188" t="n"/>
+      <c r="K19" s="189" t="n"/>
+      <c r="L19" s="189" t="n"/>
+      <c r="M19" s="189" t="n"/>
+      <c r="N19" s="188" t="n"/>
+      <c r="O19" s="190" t="n"/>
+      <c r="P19" s="190" t="n"/>
+      <c r="Q19" s="190" t="n"/>
+      <c r="R19" s="191" t="n"/>
+      <c r="S19" s="191" t="n"/>
+      <c r="T19" s="188" t="n"/>
+      <c r="U19" s="192" t="n"/>
       <c r="V19" s="54" t="n"/>
       <c r="W19" s="55" t="n"/>
       <c r="X19" s="55" t="n"/>
@@ -37306,27 +37363,27 @@
       <c r="EM19" s="55" t="n"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" s="104">
-      <c r="A20" s="184" t="n"/>
-      <c r="B20" s="184" t="n"/>
-      <c r="C20" s="184" t="n"/>
-      <c r="D20" s="185" t="n"/>
-      <c r="E20" s="185" t="n"/>
-      <c r="F20" s="185" t="n"/>
-      <c r="G20" s="186" t="n"/>
-      <c r="H20" s="187" t="n"/>
-      <c r="I20" s="186" t="n"/>
-      <c r="J20" s="186" t="n"/>
-      <c r="K20" s="186" t="n"/>
-      <c r="L20" s="187" t="n"/>
-      <c r="M20" s="187" t="n"/>
-      <c r="N20" s="186" t="n"/>
-      <c r="O20" s="188" t="n"/>
-      <c r="P20" s="188" t="n"/>
-      <c r="Q20" s="188" t="n"/>
-      <c r="R20" s="189" t="n"/>
-      <c r="S20" s="189" t="n"/>
-      <c r="T20" s="186" t="n"/>
-      <c r="U20" s="190" t="n"/>
+      <c r="A20" s="186" t="n"/>
+      <c r="B20" s="186" t="n"/>
+      <c r="C20" s="186" t="n"/>
+      <c r="D20" s="187" t="n"/>
+      <c r="E20" s="187" t="n"/>
+      <c r="F20" s="187" t="n"/>
+      <c r="G20" s="188" t="n"/>
+      <c r="H20" s="189" t="n"/>
+      <c r="I20" s="188" t="n"/>
+      <c r="J20" s="188" t="n"/>
+      <c r="K20" s="188" t="n"/>
+      <c r="L20" s="189" t="n"/>
+      <c r="M20" s="189" t="n"/>
+      <c r="N20" s="188" t="n"/>
+      <c r="O20" s="190" t="n"/>
+      <c r="P20" s="190" t="n"/>
+      <c r="Q20" s="190" t="n"/>
+      <c r="R20" s="191" t="n"/>
+      <c r="S20" s="191" t="n"/>
+      <c r="T20" s="188" t="n"/>
+      <c r="U20" s="192" t="n"/>
       <c r="V20" s="54" t="n"/>
       <c r="W20" s="55" t="n"/>
       <c r="X20" s="55" t="n"/>
@@ -37451,27 +37508,27 @@
       <c r="EM20" s="55" t="n"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" s="104">
-      <c r="A21" s="184" t="n"/>
-      <c r="B21" s="184" t="n"/>
-      <c r="C21" s="184" t="n"/>
-      <c r="D21" s="191" t="n"/>
-      <c r="E21" s="191" t="n"/>
-      <c r="F21" s="191" t="n"/>
-      <c r="G21" s="192" t="n"/>
-      <c r="H21" s="192" t="n"/>
-      <c r="I21" s="192" t="n"/>
-      <c r="J21" s="192" t="n"/>
-      <c r="K21" s="192" t="n"/>
-      <c r="L21" s="193" t="n"/>
-      <c r="M21" s="193" t="n"/>
-      <c r="N21" s="186" t="n"/>
-      <c r="O21" s="188" t="n"/>
-      <c r="P21" s="188" t="n"/>
-      <c r="Q21" s="188" t="n"/>
-      <c r="R21" s="189" t="n"/>
-      <c r="S21" s="189" t="n"/>
-      <c r="T21" s="186" t="n"/>
-      <c r="U21" s="190" t="n"/>
+      <c r="A21" s="186" t="n"/>
+      <c r="B21" s="186" t="n"/>
+      <c r="C21" s="186" t="n"/>
+      <c r="D21" s="193" t="n"/>
+      <c r="E21" s="193" t="n"/>
+      <c r="F21" s="193" t="n"/>
+      <c r="G21" s="194" t="n"/>
+      <c r="H21" s="194" t="n"/>
+      <c r="I21" s="194" t="n"/>
+      <c r="J21" s="194" t="n"/>
+      <c r="K21" s="194" t="n"/>
+      <c r="L21" s="195" t="n"/>
+      <c r="M21" s="195" t="n"/>
+      <c r="N21" s="188" t="n"/>
+      <c r="O21" s="190" t="n"/>
+      <c r="P21" s="190" t="n"/>
+      <c r="Q21" s="190" t="n"/>
+      <c r="R21" s="191" t="n"/>
+      <c r="S21" s="191" t="n"/>
+      <c r="T21" s="188" t="n"/>
+      <c r="U21" s="192" t="n"/>
       <c r="V21" s="54" t="n"/>
       <c r="W21" s="55" t="n"/>
       <c r="X21" s="55" t="n"/>
@@ -37596,27 +37653,27 @@
       <c r="EM21" s="55" t="n"/>
     </row>
     <row r="22" ht="14.25" customHeight="1" s="104">
-      <c r="A22" s="184" t="n"/>
-      <c r="B22" s="184" t="n"/>
-      <c r="C22" s="184" t="n"/>
-      <c r="D22" s="191" t="n"/>
-      <c r="E22" s="191" t="n"/>
-      <c r="F22" s="191" t="n"/>
-      <c r="G22" s="192" t="n"/>
-      <c r="H22" s="193" t="n"/>
-      <c r="I22" s="192" t="n"/>
-      <c r="J22" s="192" t="n"/>
-      <c r="K22" s="192" t="n"/>
-      <c r="L22" s="193" t="n"/>
-      <c r="M22" s="193" t="n"/>
-      <c r="N22" s="186" t="n"/>
-      <c r="O22" s="188" t="n"/>
-      <c r="P22" s="188" t="n"/>
-      <c r="Q22" s="188" t="n"/>
-      <c r="R22" s="189" t="n"/>
-      <c r="S22" s="189" t="n"/>
-      <c r="T22" s="186" t="n"/>
-      <c r="U22" s="190" t="n"/>
+      <c r="A22" s="186" t="n"/>
+      <c r="B22" s="186" t="n"/>
+      <c r="C22" s="186" t="n"/>
+      <c r="D22" s="193" t="n"/>
+      <c r="E22" s="193" t="n"/>
+      <c r="F22" s="193" t="n"/>
+      <c r="G22" s="194" t="n"/>
+      <c r="H22" s="195" t="n"/>
+      <c r="I22" s="194" t="n"/>
+      <c r="J22" s="194" t="n"/>
+      <c r="K22" s="194" t="n"/>
+      <c r="L22" s="195" t="n"/>
+      <c r="M22" s="195" t="n"/>
+      <c r="N22" s="188" t="n"/>
+      <c r="O22" s="190" t="n"/>
+      <c r="P22" s="190" t="n"/>
+      <c r="Q22" s="190" t="n"/>
+      <c r="R22" s="191" t="n"/>
+      <c r="S22" s="191" t="n"/>
+      <c r="T22" s="188" t="n"/>
+      <c r="U22" s="192" t="n"/>
       <c r="V22" s="54" t="n"/>
       <c r="W22" s="55" t="n"/>
       <c r="X22" s="55" t="n"/>
@@ -37741,27 +37798,27 @@
       <c r="EM22" s="55" t="n"/>
     </row>
     <row r="23" ht="14.25" customHeight="1" s="104">
-      <c r="A23" s="184" t="n"/>
-      <c r="B23" s="184" t="n"/>
-      <c r="C23" s="184" t="n"/>
-      <c r="D23" s="191" t="n"/>
-      <c r="E23" s="191" t="n"/>
-      <c r="F23" s="191" t="n"/>
-      <c r="G23" s="192" t="n"/>
-      <c r="H23" s="192" t="n"/>
-      <c r="I23" s="192" t="n"/>
-      <c r="J23" s="192" t="n"/>
-      <c r="K23" s="192" t="n"/>
-      <c r="L23" s="193" t="n"/>
-      <c r="M23" s="193" t="n"/>
-      <c r="N23" s="186" t="n"/>
-      <c r="O23" s="188" t="n"/>
-      <c r="P23" s="188" t="n"/>
-      <c r="Q23" s="188" t="n"/>
-      <c r="R23" s="189" t="n"/>
-      <c r="S23" s="189" t="n"/>
-      <c r="T23" s="186" t="n"/>
-      <c r="U23" s="190" t="n"/>
+      <c r="A23" s="186" t="n"/>
+      <c r="B23" s="186" t="n"/>
+      <c r="C23" s="186" t="n"/>
+      <c r="D23" s="193" t="n"/>
+      <c r="E23" s="193" t="n"/>
+      <c r="F23" s="193" t="n"/>
+      <c r="G23" s="194" t="n"/>
+      <c r="H23" s="194" t="n"/>
+      <c r="I23" s="194" t="n"/>
+      <c r="J23" s="194" t="n"/>
+      <c r="K23" s="194" t="n"/>
+      <c r="L23" s="195" t="n"/>
+      <c r="M23" s="195" t="n"/>
+      <c r="N23" s="188" t="n"/>
+      <c r="O23" s="190" t="n"/>
+      <c r="P23" s="190" t="n"/>
+      <c r="Q23" s="190" t="n"/>
+      <c r="R23" s="191" t="n"/>
+      <c r="S23" s="191" t="n"/>
+      <c r="T23" s="188" t="n"/>
+      <c r="U23" s="192" t="n"/>
       <c r="V23" s="54" t="n"/>
       <c r="W23" s="55" t="n"/>
       <c r="X23" s="55" t="n"/>
@@ -37886,27 +37943,27 @@
       <c r="EM23" s="55" t="n"/>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="104">
-      <c r="A24" s="184" t="n"/>
-      <c r="B24" s="184" t="n"/>
-      <c r="C24" s="184" t="n"/>
-      <c r="D24" s="191" t="n"/>
-      <c r="E24" s="191" t="n"/>
-      <c r="F24" s="191" t="n"/>
-      <c r="G24" s="192" t="n"/>
-      <c r="H24" s="192" t="n"/>
-      <c r="I24" s="192" t="n"/>
-      <c r="J24" s="192" t="n"/>
-      <c r="K24" s="192" t="n"/>
-      <c r="L24" s="193" t="n"/>
-      <c r="M24" s="193" t="n"/>
-      <c r="N24" s="186" t="n"/>
-      <c r="O24" s="188" t="n"/>
-      <c r="P24" s="188" t="n"/>
-      <c r="Q24" s="188" t="n"/>
-      <c r="R24" s="189" t="n"/>
-      <c r="S24" s="189" t="n"/>
-      <c r="T24" s="186" t="n"/>
-      <c r="U24" s="190" t="n"/>
+      <c r="A24" s="186" t="n"/>
+      <c r="B24" s="186" t="n"/>
+      <c r="C24" s="186" t="n"/>
+      <c r="D24" s="193" t="n"/>
+      <c r="E24" s="193" t="n"/>
+      <c r="F24" s="193" t="n"/>
+      <c r="G24" s="194" t="n"/>
+      <c r="H24" s="194" t="n"/>
+      <c r="I24" s="194" t="n"/>
+      <c r="J24" s="194" t="n"/>
+      <c r="K24" s="194" t="n"/>
+      <c r="L24" s="195" t="n"/>
+      <c r="M24" s="195" t="n"/>
+      <c r="N24" s="188" t="n"/>
+      <c r="O24" s="190" t="n"/>
+      <c r="P24" s="190" t="n"/>
+      <c r="Q24" s="190" t="n"/>
+      <c r="R24" s="191" t="n"/>
+      <c r="S24" s="191" t="n"/>
+      <c r="T24" s="188" t="n"/>
+      <c r="U24" s="192" t="n"/>
       <c r="V24" s="54" t="n"/>
       <c r="W24" s="55" t="n"/>
       <c r="X24" s="55" t="n"/>
@@ -38031,27 +38088,27 @@
       <c r="EM24" s="55" t="n"/>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="104">
-      <c r="A25" s="184" t="n"/>
-      <c r="B25" s="184" t="n"/>
-      <c r="C25" s="184" t="n"/>
-      <c r="D25" s="191" t="n"/>
-      <c r="E25" s="191" t="n"/>
-      <c r="F25" s="191" t="n"/>
-      <c r="G25" s="192" t="n"/>
-      <c r="H25" s="192" t="n"/>
-      <c r="I25" s="192" t="n"/>
-      <c r="J25" s="192" t="n"/>
-      <c r="K25" s="192" t="n"/>
-      <c r="L25" s="193" t="n"/>
-      <c r="M25" s="193" t="n"/>
-      <c r="N25" s="186" t="n"/>
-      <c r="O25" s="188" t="n"/>
-      <c r="P25" s="188" t="n"/>
-      <c r="Q25" s="188" t="n"/>
-      <c r="R25" s="189" t="n"/>
-      <c r="S25" s="189" t="n"/>
-      <c r="T25" s="186" t="n"/>
-      <c r="U25" s="190" t="n"/>
+      <c r="A25" s="186" t="n"/>
+      <c r="B25" s="186" t="n"/>
+      <c r="C25" s="186" t="n"/>
+      <c r="D25" s="193" t="n"/>
+      <c r="E25" s="193" t="n"/>
+      <c r="F25" s="193" t="n"/>
+      <c r="G25" s="194" t="n"/>
+      <c r="H25" s="194" t="n"/>
+      <c r="I25" s="194" t="n"/>
+      <c r="J25" s="194" t="n"/>
+      <c r="K25" s="194" t="n"/>
+      <c r="L25" s="195" t="n"/>
+      <c r="M25" s="195" t="n"/>
+      <c r="N25" s="188" t="n"/>
+      <c r="O25" s="190" t="n"/>
+      <c r="P25" s="190" t="n"/>
+      <c r="Q25" s="190" t="n"/>
+      <c r="R25" s="191" t="n"/>
+      <c r="S25" s="191" t="n"/>
+      <c r="T25" s="188" t="n"/>
+      <c r="U25" s="192" t="n"/>
       <c r="V25" s="54" t="n"/>
       <c r="W25" s="55" t="n"/>
       <c r="X25" s="55" t="n"/>
@@ -38176,27 +38233,27 @@
       <c r="EM25" s="55" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1" s="104">
-      <c r="A26" s="184" t="n"/>
-      <c r="B26" s="184" t="n"/>
-      <c r="C26" s="184" t="n"/>
-      <c r="D26" s="191" t="n"/>
-      <c r="E26" s="191" t="n"/>
-      <c r="F26" s="191" t="n"/>
-      <c r="G26" s="192" t="n"/>
-      <c r="H26" s="192" t="n"/>
-      <c r="I26" s="192" t="n"/>
-      <c r="J26" s="192" t="n"/>
-      <c r="K26" s="192" t="n"/>
-      <c r="L26" s="193" t="n"/>
-      <c r="M26" s="193" t="n"/>
-      <c r="N26" s="186" t="n"/>
-      <c r="O26" s="188" t="n"/>
-      <c r="P26" s="188" t="n"/>
-      <c r="Q26" s="188" t="n"/>
-      <c r="R26" s="189" t="n"/>
-      <c r="S26" s="189" t="n"/>
-      <c r="T26" s="186" t="n"/>
-      <c r="U26" s="190" t="n"/>
+      <c r="A26" s="186" t="n"/>
+      <c r="B26" s="186" t="n"/>
+      <c r="C26" s="186" t="n"/>
+      <c r="D26" s="193" t="n"/>
+      <c r="E26" s="193" t="n"/>
+      <c r="F26" s="193" t="n"/>
+      <c r="G26" s="194" t="n"/>
+      <c r="H26" s="194" t="n"/>
+      <c r="I26" s="194" t="n"/>
+      <c r="J26" s="194" t="n"/>
+      <c r="K26" s="194" t="n"/>
+      <c r="L26" s="195" t="n"/>
+      <c r="M26" s="195" t="n"/>
+      <c r="N26" s="188" t="n"/>
+      <c r="O26" s="190" t="n"/>
+      <c r="P26" s="190" t="n"/>
+      <c r="Q26" s="190" t="n"/>
+      <c r="R26" s="191" t="n"/>
+      <c r="S26" s="191" t="n"/>
+      <c r="T26" s="188" t="n"/>
+      <c r="U26" s="192" t="n"/>
       <c r="V26" s="54" t="n"/>
       <c r="W26" s="55" t="n"/>
       <c r="X26" s="55" t="n"/>
@@ -38321,27 +38378,27 @@
       <c r="EM26" s="55" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1" s="104">
-      <c r="A27" s="184" t="n"/>
-      <c r="B27" s="184" t="n"/>
-      <c r="C27" s="184" t="n"/>
-      <c r="D27" s="191" t="n"/>
-      <c r="E27" s="191" t="n"/>
-      <c r="F27" s="191" t="n"/>
-      <c r="G27" s="192" t="n"/>
-      <c r="H27" s="192" t="n"/>
-      <c r="I27" s="192" t="n"/>
-      <c r="J27" s="192" t="n"/>
-      <c r="K27" s="192" t="n"/>
-      <c r="L27" s="193" t="n"/>
-      <c r="M27" s="193" t="n"/>
-      <c r="N27" s="186" t="n"/>
-      <c r="O27" s="188" t="n"/>
-      <c r="P27" s="188" t="n"/>
-      <c r="Q27" s="188" t="n"/>
-      <c r="R27" s="189" t="n"/>
-      <c r="S27" s="189" t="n"/>
-      <c r="T27" s="186" t="n"/>
-      <c r="U27" s="190" t="n"/>
+      <c r="A27" s="186" t="n"/>
+      <c r="B27" s="186" t="n"/>
+      <c r="C27" s="186" t="n"/>
+      <c r="D27" s="193" t="n"/>
+      <c r="E27" s="193" t="n"/>
+      <c r="F27" s="193" t="n"/>
+      <c r="G27" s="194" t="n"/>
+      <c r="H27" s="194" t="n"/>
+      <c r="I27" s="194" t="n"/>
+      <c r="J27" s="194" t="n"/>
+      <c r="K27" s="194" t="n"/>
+      <c r="L27" s="195" t="n"/>
+      <c r="M27" s="195" t="n"/>
+      <c r="N27" s="188" t="n"/>
+      <c r="O27" s="190" t="n"/>
+      <c r="P27" s="190" t="n"/>
+      <c r="Q27" s="190" t="n"/>
+      <c r="R27" s="191" t="n"/>
+      <c r="S27" s="191" t="n"/>
+      <c r="T27" s="188" t="n"/>
+      <c r="U27" s="192" t="n"/>
       <c r="V27" s="54" t="n"/>
       <c r="W27" s="55" t="n"/>
       <c r="X27" s="55" t="n"/>
@@ -38466,27 +38523,27 @@
       <c r="EM27" s="55" t="n"/>
     </row>
     <row r="28" ht="14.25" customHeight="1" s="104">
-      <c r="A28" s="184" t="n"/>
-      <c r="B28" s="184" t="n"/>
-      <c r="C28" s="184" t="n"/>
-      <c r="D28" s="191" t="n"/>
-      <c r="E28" s="191" t="n"/>
-      <c r="F28" s="191" t="n"/>
-      <c r="G28" s="192" t="n"/>
-      <c r="H28" s="192" t="n"/>
-      <c r="I28" s="192" t="n"/>
-      <c r="J28" s="192" t="n"/>
-      <c r="K28" s="192" t="n"/>
-      <c r="L28" s="193" t="n"/>
-      <c r="M28" s="193" t="n"/>
-      <c r="N28" s="186" t="n"/>
-      <c r="O28" s="188" t="n"/>
-      <c r="P28" s="188" t="n"/>
-      <c r="Q28" s="188" t="n"/>
-      <c r="R28" s="189" t="n"/>
-      <c r="S28" s="189" t="n"/>
-      <c r="T28" s="186" t="n"/>
-      <c r="U28" s="190" t="n"/>
+      <c r="A28" s="186" t="n"/>
+      <c r="B28" s="186" t="n"/>
+      <c r="C28" s="186" t="n"/>
+      <c r="D28" s="193" t="n"/>
+      <c r="E28" s="193" t="n"/>
+      <c r="F28" s="193" t="n"/>
+      <c r="G28" s="194" t="n"/>
+      <c r="H28" s="194" t="n"/>
+      <c r="I28" s="194" t="n"/>
+      <c r="J28" s="194" t="n"/>
+      <c r="K28" s="194" t="n"/>
+      <c r="L28" s="195" t="n"/>
+      <c r="M28" s="195" t="n"/>
+      <c r="N28" s="188" t="n"/>
+      <c r="O28" s="190" t="n"/>
+      <c r="P28" s="190" t="n"/>
+      <c r="Q28" s="190" t="n"/>
+      <c r="R28" s="191" t="n"/>
+      <c r="S28" s="191" t="n"/>
+      <c r="T28" s="188" t="n"/>
+      <c r="U28" s="192" t="n"/>
       <c r="V28" s="54" t="n"/>
       <c r="W28" s="55" t="n"/>
       <c r="X28" s="55" t="n"/>
@@ -38611,27 +38668,27 @@
       <c r="EM28" s="55" t="n"/>
     </row>
     <row r="29" ht="14.25" customHeight="1" s="104">
-      <c r="A29" s="184" t="n"/>
-      <c r="B29" s="184" t="n"/>
-      <c r="C29" s="184" t="n"/>
-      <c r="D29" s="191" t="n"/>
-      <c r="E29" s="191" t="n"/>
-      <c r="F29" s="191" t="n"/>
-      <c r="G29" s="192" t="n"/>
-      <c r="H29" s="192" t="n"/>
-      <c r="I29" s="192" t="n"/>
-      <c r="J29" s="192" t="n"/>
-      <c r="K29" s="192" t="n"/>
-      <c r="L29" s="193" t="n"/>
-      <c r="M29" s="193" t="n"/>
-      <c r="N29" s="186" t="n"/>
-      <c r="O29" s="188" t="n"/>
-      <c r="P29" s="188" t="n"/>
-      <c r="Q29" s="188" t="n"/>
-      <c r="R29" s="189" t="n"/>
-      <c r="S29" s="189" t="n"/>
-      <c r="T29" s="186" t="n"/>
-      <c r="U29" s="190" t="n"/>
+      <c r="A29" s="186" t="n"/>
+      <c r="B29" s="186" t="n"/>
+      <c r="C29" s="186" t="n"/>
+      <c r="D29" s="193" t="n"/>
+      <c r="E29" s="193" t="n"/>
+      <c r="F29" s="193" t="n"/>
+      <c r="G29" s="194" t="n"/>
+      <c r="H29" s="194" t="n"/>
+      <c r="I29" s="194" t="n"/>
+      <c r="J29" s="194" t="n"/>
+      <c r="K29" s="194" t="n"/>
+      <c r="L29" s="195" t="n"/>
+      <c r="M29" s="195" t="n"/>
+      <c r="N29" s="188" t="n"/>
+      <c r="O29" s="190" t="n"/>
+      <c r="P29" s="190" t="n"/>
+      <c r="Q29" s="190" t="n"/>
+      <c r="R29" s="191" t="n"/>
+      <c r="S29" s="191" t="n"/>
+      <c r="T29" s="188" t="n"/>
+      <c r="U29" s="192" t="n"/>
       <c r="V29" s="54" t="n"/>
       <c r="W29" s="55" t="n"/>
       <c r="X29" s="55" t="n"/>
@@ -38756,27 +38813,27 @@
       <c r="EM29" s="55" t="n"/>
     </row>
     <row r="30" ht="14.25" customHeight="1" s="104">
-      <c r="A30" s="184" t="n"/>
-      <c r="B30" s="184" t="n"/>
-      <c r="C30" s="184" t="n"/>
-      <c r="D30" s="191" t="n"/>
-      <c r="E30" s="191" t="n"/>
-      <c r="F30" s="191" t="n"/>
-      <c r="G30" s="192" t="n"/>
-      <c r="H30" s="192" t="n"/>
-      <c r="I30" s="192" t="n"/>
-      <c r="J30" s="192" t="n"/>
-      <c r="K30" s="192" t="n"/>
-      <c r="L30" s="193" t="n"/>
-      <c r="M30" s="193" t="n"/>
-      <c r="N30" s="186" t="n"/>
-      <c r="O30" s="188" t="n"/>
-      <c r="P30" s="188" t="n"/>
-      <c r="Q30" s="188" t="n"/>
-      <c r="R30" s="189" t="n"/>
-      <c r="S30" s="189" t="n"/>
-      <c r="T30" s="186" t="n"/>
-      <c r="U30" s="190" t="n"/>
+      <c r="A30" s="186" t="n"/>
+      <c r="B30" s="186" t="n"/>
+      <c r="C30" s="186" t="n"/>
+      <c r="D30" s="193" t="n"/>
+      <c r="E30" s="193" t="n"/>
+      <c r="F30" s="193" t="n"/>
+      <c r="G30" s="194" t="n"/>
+      <c r="H30" s="194" t="n"/>
+      <c r="I30" s="194" t="n"/>
+      <c r="J30" s="194" t="n"/>
+      <c r="K30" s="194" t="n"/>
+      <c r="L30" s="195" t="n"/>
+      <c r="M30" s="195" t="n"/>
+      <c r="N30" s="188" t="n"/>
+      <c r="O30" s="190" t="n"/>
+      <c r="P30" s="190" t="n"/>
+      <c r="Q30" s="190" t="n"/>
+      <c r="R30" s="191" t="n"/>
+      <c r="S30" s="191" t="n"/>
+      <c r="T30" s="188" t="n"/>
+      <c r="U30" s="192" t="n"/>
       <c r="V30" s="54" t="n"/>
       <c r="W30" s="55" t="n"/>
       <c r="X30" s="55" t="n"/>
@@ -38901,27 +38958,27 @@
       <c r="EM30" s="55" t="n"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" s="104">
-      <c r="A31" s="184" t="n"/>
-      <c r="B31" s="184" t="n"/>
-      <c r="C31" s="184" t="n"/>
-      <c r="D31" s="191" t="n"/>
-      <c r="E31" s="191" t="n"/>
-      <c r="F31" s="191" t="n"/>
-      <c r="G31" s="192" t="n"/>
-      <c r="H31" s="192" t="n"/>
-      <c r="I31" s="192" t="n"/>
-      <c r="J31" s="192" t="n"/>
-      <c r="K31" s="192" t="n"/>
-      <c r="L31" s="193" t="n"/>
-      <c r="M31" s="193" t="n"/>
-      <c r="N31" s="186" t="n"/>
-      <c r="O31" s="188" t="n"/>
-      <c r="P31" s="188" t="n"/>
-      <c r="Q31" s="188" t="n"/>
-      <c r="R31" s="189" t="n"/>
-      <c r="S31" s="189" t="n"/>
-      <c r="T31" s="186" t="n"/>
-      <c r="U31" s="190" t="n"/>
+      <c r="A31" s="186" t="n"/>
+      <c r="B31" s="186" t="n"/>
+      <c r="C31" s="186" t="n"/>
+      <c r="D31" s="193" t="n"/>
+      <c r="E31" s="193" t="n"/>
+      <c r="F31" s="193" t="n"/>
+      <c r="G31" s="194" t="n"/>
+      <c r="H31" s="194" t="n"/>
+      <c r="I31" s="194" t="n"/>
+      <c r="J31" s="194" t="n"/>
+      <c r="K31" s="194" t="n"/>
+      <c r="L31" s="195" t="n"/>
+      <c r="M31" s="195" t="n"/>
+      <c r="N31" s="188" t="n"/>
+      <c r="O31" s="190" t="n"/>
+      <c r="P31" s="190" t="n"/>
+      <c r="Q31" s="190" t="n"/>
+      <c r="R31" s="191" t="n"/>
+      <c r="S31" s="191" t="n"/>
+      <c r="T31" s="188" t="n"/>
+      <c r="U31" s="192" t="n"/>
       <c r="V31" s="54" t="n"/>
       <c r="W31" s="55" t="n"/>
       <c r="X31" s="55" t="n"/>
@@ -39046,27 +39103,27 @@
       <c r="EM31" s="55" t="n"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" s="104">
-      <c r="A32" s="184" t="n"/>
-      <c r="B32" s="184" t="n"/>
-      <c r="C32" s="184" t="n"/>
-      <c r="D32" s="191" t="n"/>
-      <c r="E32" s="191" t="n"/>
-      <c r="F32" s="191" t="n"/>
-      <c r="G32" s="192" t="n"/>
-      <c r="H32" s="192" t="n"/>
-      <c r="I32" s="192" t="n"/>
-      <c r="J32" s="192" t="n"/>
-      <c r="K32" s="192" t="n"/>
-      <c r="L32" s="193" t="n"/>
-      <c r="M32" s="193" t="n"/>
-      <c r="N32" s="186" t="n"/>
-      <c r="O32" s="188" t="n"/>
-      <c r="P32" s="188" t="n"/>
-      <c r="Q32" s="188" t="n"/>
-      <c r="R32" s="189" t="n"/>
-      <c r="S32" s="189" t="n"/>
-      <c r="T32" s="186" t="n"/>
-      <c r="U32" s="190" t="n"/>
+      <c r="A32" s="186" t="n"/>
+      <c r="B32" s="186" t="n"/>
+      <c r="C32" s="186" t="n"/>
+      <c r="D32" s="193" t="n"/>
+      <c r="E32" s="193" t="n"/>
+      <c r="F32" s="193" t="n"/>
+      <c r="G32" s="194" t="n"/>
+      <c r="H32" s="194" t="n"/>
+      <c r="I32" s="194" t="n"/>
+      <c r="J32" s="194" t="n"/>
+      <c r="K32" s="194" t="n"/>
+      <c r="L32" s="195" t="n"/>
+      <c r="M32" s="195" t="n"/>
+      <c r="N32" s="188" t="n"/>
+      <c r="O32" s="190" t="n"/>
+      <c r="P32" s="190" t="n"/>
+      <c r="Q32" s="190" t="n"/>
+      <c r="R32" s="191" t="n"/>
+      <c r="S32" s="191" t="n"/>
+      <c r="T32" s="188" t="n"/>
+      <c r="U32" s="192" t="n"/>
       <c r="V32" s="54" t="n"/>
       <c r="W32" s="55" t="n"/>
       <c r="X32" s="55" t="n"/>
@@ -39191,27 +39248,27 @@
       <c r="EM32" s="55" t="n"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" s="104">
-      <c r="A33" s="184" t="n"/>
-      <c r="B33" s="184" t="n"/>
-      <c r="C33" s="184" t="n"/>
-      <c r="D33" s="191" t="n"/>
-      <c r="E33" s="191" t="n"/>
-      <c r="F33" s="191" t="n"/>
-      <c r="G33" s="192" t="n"/>
-      <c r="H33" s="192" t="n"/>
-      <c r="I33" s="192" t="n"/>
-      <c r="J33" s="192" t="n"/>
-      <c r="K33" s="192" t="n"/>
-      <c r="L33" s="193" t="n"/>
-      <c r="M33" s="193" t="n"/>
-      <c r="N33" s="186" t="n"/>
-      <c r="O33" s="188" t="n"/>
-      <c r="P33" s="188" t="n"/>
-      <c r="Q33" s="188" t="n"/>
-      <c r="R33" s="189" t="n"/>
-      <c r="S33" s="189" t="n"/>
-      <c r="T33" s="186" t="n"/>
-      <c r="U33" s="190" t="n"/>
+      <c r="A33" s="186" t="n"/>
+      <c r="B33" s="186" t="n"/>
+      <c r="C33" s="186" t="n"/>
+      <c r="D33" s="193" t="n"/>
+      <c r="E33" s="193" t="n"/>
+      <c r="F33" s="193" t="n"/>
+      <c r="G33" s="194" t="n"/>
+      <c r="H33" s="194" t="n"/>
+      <c r="I33" s="194" t="n"/>
+      <c r="J33" s="194" t="n"/>
+      <c r="K33" s="194" t="n"/>
+      <c r="L33" s="195" t="n"/>
+      <c r="M33" s="195" t="n"/>
+      <c r="N33" s="188" t="n"/>
+      <c r="O33" s="190" t="n"/>
+      <c r="P33" s="190" t="n"/>
+      <c r="Q33" s="190" t="n"/>
+      <c r="R33" s="191" t="n"/>
+      <c r="S33" s="191" t="n"/>
+      <c r="T33" s="188" t="n"/>
+      <c r="U33" s="192" t="n"/>
       <c r="V33" s="54" t="n"/>
       <c r="W33" s="55" t="n"/>
       <c r="X33" s="55" t="n"/>
@@ -39336,27 +39393,27 @@
       <c r="EM33" s="55" t="n"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" s="104">
-      <c r="A34" s="184" t="n"/>
-      <c r="B34" s="184" t="n"/>
-      <c r="C34" s="184" t="n"/>
-      <c r="D34" s="191" t="n"/>
-      <c r="E34" s="191" t="n"/>
-      <c r="F34" s="191" t="n"/>
-      <c r="G34" s="192" t="n"/>
-      <c r="H34" s="192" t="n"/>
-      <c r="I34" s="192" t="n"/>
-      <c r="J34" s="192" t="n"/>
-      <c r="K34" s="192" t="n"/>
-      <c r="L34" s="193" t="n"/>
-      <c r="M34" s="193" t="n"/>
-      <c r="N34" s="186" t="n"/>
-      <c r="O34" s="188" t="n"/>
-      <c r="P34" s="188" t="n"/>
-      <c r="Q34" s="188" t="n"/>
-      <c r="R34" s="189" t="n"/>
-      <c r="S34" s="189" t="n"/>
-      <c r="T34" s="186" t="n"/>
-      <c r="U34" s="190" t="n"/>
+      <c r="A34" s="186" t="n"/>
+      <c r="B34" s="186" t="n"/>
+      <c r="C34" s="186" t="n"/>
+      <c r="D34" s="193" t="n"/>
+      <c r="E34" s="193" t="n"/>
+      <c r="F34" s="193" t="n"/>
+      <c r="G34" s="194" t="n"/>
+      <c r="H34" s="194" t="n"/>
+      <c r="I34" s="194" t="n"/>
+      <c r="J34" s="194" t="n"/>
+      <c r="K34" s="194" t="n"/>
+      <c r="L34" s="195" t="n"/>
+      <c r="M34" s="195" t="n"/>
+      <c r="N34" s="188" t="n"/>
+      <c r="O34" s="190" t="n"/>
+      <c r="P34" s="190" t="n"/>
+      <c r="Q34" s="190" t="n"/>
+      <c r="R34" s="191" t="n"/>
+      <c r="S34" s="191" t="n"/>
+      <c r="T34" s="188" t="n"/>
+      <c r="U34" s="192" t="n"/>
       <c r="V34" s="54" t="n"/>
       <c r="W34" s="55" t="n"/>
       <c r="X34" s="55" t="n"/>
@@ -39481,27 +39538,27 @@
       <c r="EM34" s="55" t="n"/>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="104">
-      <c r="A35" s="184" t="n"/>
-      <c r="B35" s="184" t="n"/>
-      <c r="C35" s="184" t="n"/>
-      <c r="D35" s="191" t="n"/>
-      <c r="E35" s="191" t="n"/>
-      <c r="F35" s="191" t="n"/>
-      <c r="G35" s="192" t="n"/>
-      <c r="H35" s="192" t="n"/>
-      <c r="I35" s="192" t="n"/>
-      <c r="J35" s="192" t="n"/>
-      <c r="K35" s="192" t="n"/>
-      <c r="L35" s="193" t="n"/>
-      <c r="M35" s="193" t="n"/>
-      <c r="N35" s="186" t="n"/>
-      <c r="O35" s="188" t="n"/>
-      <c r="P35" s="188" t="n"/>
-      <c r="Q35" s="188" t="n"/>
-      <c r="R35" s="189" t="n"/>
-      <c r="S35" s="189" t="n"/>
-      <c r="T35" s="186" t="n"/>
-      <c r="U35" s="190" t="n"/>
+      <c r="A35" s="186" t="n"/>
+      <c r="B35" s="186" t="n"/>
+      <c r="C35" s="186" t="n"/>
+      <c r="D35" s="193" t="n"/>
+      <c r="E35" s="193" t="n"/>
+      <c r="F35" s="193" t="n"/>
+      <c r="G35" s="194" t="n"/>
+      <c r="H35" s="194" t="n"/>
+      <c r="I35" s="194" t="n"/>
+      <c r="J35" s="194" t="n"/>
+      <c r="K35" s="194" t="n"/>
+      <c r="L35" s="195" t="n"/>
+      <c r="M35" s="195" t="n"/>
+      <c r="N35" s="188" t="n"/>
+      <c r="O35" s="190" t="n"/>
+      <c r="P35" s="190" t="n"/>
+      <c r="Q35" s="190" t="n"/>
+      <c r="R35" s="191" t="n"/>
+      <c r="S35" s="191" t="n"/>
+      <c r="T35" s="188" t="n"/>
+      <c r="U35" s="192" t="n"/>
       <c r="V35" s="54" t="n"/>
       <c r="W35" s="55" t="n"/>
       <c r="X35" s="55" t="n"/>
@@ -39626,27 +39683,27 @@
       <c r="EM35" s="55" t="n"/>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="104">
-      <c r="A36" s="184" t="n"/>
-      <c r="B36" s="184" t="n"/>
-      <c r="C36" s="184" t="n"/>
-      <c r="D36" s="191" t="n"/>
-      <c r="E36" s="191" t="n"/>
-      <c r="F36" s="191" t="n"/>
-      <c r="G36" s="192" t="n"/>
-      <c r="H36" s="192" t="n"/>
-      <c r="I36" s="192" t="n"/>
-      <c r="J36" s="192" t="n"/>
-      <c r="K36" s="192" t="n"/>
-      <c r="L36" s="193" t="n"/>
-      <c r="M36" s="193" t="n"/>
-      <c r="N36" s="186" t="n"/>
-      <c r="O36" s="188" t="n"/>
-      <c r="P36" s="188" t="n"/>
-      <c r="Q36" s="188" t="n"/>
-      <c r="R36" s="189" t="n"/>
-      <c r="S36" s="189" t="n"/>
-      <c r="T36" s="186" t="n"/>
-      <c r="U36" s="190" t="n"/>
+      <c r="A36" s="186" t="n"/>
+      <c r="B36" s="186" t="n"/>
+      <c r="C36" s="186" t="n"/>
+      <c r="D36" s="193" t="n"/>
+      <c r="E36" s="193" t="n"/>
+      <c r="F36" s="193" t="n"/>
+      <c r="G36" s="194" t="n"/>
+      <c r="H36" s="194" t="n"/>
+      <c r="I36" s="194" t="n"/>
+      <c r="J36" s="194" t="n"/>
+      <c r="K36" s="194" t="n"/>
+      <c r="L36" s="195" t="n"/>
+      <c r="M36" s="195" t="n"/>
+      <c r="N36" s="188" t="n"/>
+      <c r="O36" s="190" t="n"/>
+      <c r="P36" s="190" t="n"/>
+      <c r="Q36" s="190" t="n"/>
+      <c r="R36" s="191" t="n"/>
+      <c r="S36" s="191" t="n"/>
+      <c r="T36" s="188" t="n"/>
+      <c r="U36" s="192" t="n"/>
       <c r="V36" s="54" t="n"/>
       <c r="W36" s="55" t="n"/>
       <c r="X36" s="55" t="n"/>
@@ -39771,27 +39828,27 @@
       <c r="EM36" s="55" t="n"/>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="104">
-      <c r="A37" s="184" t="n"/>
-      <c r="B37" s="184" t="n"/>
-      <c r="C37" s="184" t="n"/>
-      <c r="D37" s="191" t="n"/>
-      <c r="E37" s="191" t="n"/>
-      <c r="F37" s="191" t="n"/>
-      <c r="G37" s="192" t="n"/>
-      <c r="H37" s="192" t="n"/>
-      <c r="I37" s="192" t="n"/>
-      <c r="J37" s="192" t="n"/>
-      <c r="K37" s="192" t="n"/>
-      <c r="L37" s="193" t="n"/>
-      <c r="M37" s="193" t="n"/>
-      <c r="N37" s="186" t="n"/>
-      <c r="O37" s="188" t="n"/>
-      <c r="P37" s="188" t="n"/>
-      <c r="Q37" s="188" t="n"/>
-      <c r="R37" s="189" t="n"/>
-      <c r="S37" s="189" t="n"/>
-      <c r="T37" s="186" t="n"/>
-      <c r="U37" s="194" t="n"/>
+      <c r="A37" s="186" t="n"/>
+      <c r="B37" s="186" t="n"/>
+      <c r="C37" s="186" t="n"/>
+      <c r="D37" s="193" t="n"/>
+      <c r="E37" s="193" t="n"/>
+      <c r="F37" s="193" t="n"/>
+      <c r="G37" s="194" t="n"/>
+      <c r="H37" s="194" t="n"/>
+      <c r="I37" s="194" t="n"/>
+      <c r="J37" s="194" t="n"/>
+      <c r="K37" s="194" t="n"/>
+      <c r="L37" s="195" t="n"/>
+      <c r="M37" s="195" t="n"/>
+      <c r="N37" s="188" t="n"/>
+      <c r="O37" s="190" t="n"/>
+      <c r="P37" s="190" t="n"/>
+      <c r="Q37" s="190" t="n"/>
+      <c r="R37" s="191" t="n"/>
+      <c r="S37" s="191" t="n"/>
+      <c r="T37" s="188" t="n"/>
+      <c r="U37" s="196" t="n"/>
       <c r="V37" s="54" t="n"/>
       <c r="W37" s="55" t="n"/>
       <c r="X37" s="55" t="n"/>
@@ -39916,27 +39973,27 @@
       <c r="EM37" s="55" t="n"/>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="104">
-      <c r="A38" s="184" t="n"/>
-      <c r="B38" s="184" t="n"/>
-      <c r="C38" s="184" t="n"/>
-      <c r="D38" s="191" t="n"/>
-      <c r="E38" s="191" t="n"/>
-      <c r="F38" s="191" t="n"/>
-      <c r="G38" s="192" t="n"/>
-      <c r="H38" s="192" t="n"/>
-      <c r="I38" s="192" t="n"/>
-      <c r="J38" s="192" t="n"/>
-      <c r="K38" s="192" t="n"/>
-      <c r="L38" s="193" t="n"/>
-      <c r="M38" s="193" t="n"/>
-      <c r="N38" s="186" t="n"/>
-      <c r="O38" s="188" t="n"/>
-      <c r="P38" s="188" t="n"/>
-      <c r="Q38" s="188" t="n"/>
-      <c r="R38" s="189" t="n"/>
-      <c r="S38" s="189" t="n"/>
-      <c r="T38" s="186" t="n"/>
-      <c r="U38" s="190" t="n"/>
+      <c r="A38" s="186" t="n"/>
+      <c r="B38" s="186" t="n"/>
+      <c r="C38" s="186" t="n"/>
+      <c r="D38" s="193" t="n"/>
+      <c r="E38" s="193" t="n"/>
+      <c r="F38" s="193" t="n"/>
+      <c r="G38" s="194" t="n"/>
+      <c r="H38" s="194" t="n"/>
+      <c r="I38" s="194" t="n"/>
+      <c r="J38" s="194" t="n"/>
+      <c r="K38" s="194" t="n"/>
+      <c r="L38" s="195" t="n"/>
+      <c r="M38" s="195" t="n"/>
+      <c r="N38" s="188" t="n"/>
+      <c r="O38" s="190" t="n"/>
+      <c r="P38" s="190" t="n"/>
+      <c r="Q38" s="190" t="n"/>
+      <c r="R38" s="191" t="n"/>
+      <c r="S38" s="191" t="n"/>
+      <c r="T38" s="188" t="n"/>
+      <c r="U38" s="192" t="n"/>
       <c r="V38" s="54" t="n"/>
       <c r="W38" s="55" t="n"/>
       <c r="X38" s="55" t="n"/>
@@ -40061,27 +40118,27 @@
       <c r="EM38" s="55" t="n"/>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="104">
-      <c r="A39" s="184" t="n"/>
-      <c r="B39" s="184" t="n"/>
-      <c r="C39" s="184" t="n"/>
-      <c r="D39" s="191" t="n"/>
-      <c r="E39" s="191" t="n"/>
-      <c r="F39" s="191" t="n"/>
-      <c r="G39" s="192" t="n"/>
-      <c r="H39" s="192" t="n"/>
-      <c r="I39" s="192" t="n"/>
-      <c r="J39" s="192" t="n"/>
-      <c r="K39" s="192" t="n"/>
-      <c r="L39" s="193" t="n"/>
-      <c r="M39" s="193" t="n"/>
-      <c r="N39" s="186" t="n"/>
-      <c r="O39" s="188" t="n"/>
-      <c r="P39" s="188" t="n"/>
-      <c r="Q39" s="188" t="n"/>
-      <c r="R39" s="189" t="n"/>
-      <c r="S39" s="189" t="n"/>
-      <c r="T39" s="186" t="n"/>
-      <c r="U39" s="190" t="n"/>
+      <c r="A39" s="186" t="n"/>
+      <c r="B39" s="186" t="n"/>
+      <c r="C39" s="186" t="n"/>
+      <c r="D39" s="193" t="n"/>
+      <c r="E39" s="193" t="n"/>
+      <c r="F39" s="193" t="n"/>
+      <c r="G39" s="194" t="n"/>
+      <c r="H39" s="194" t="n"/>
+      <c r="I39" s="194" t="n"/>
+      <c r="J39" s="194" t="n"/>
+      <c r="K39" s="194" t="n"/>
+      <c r="L39" s="195" t="n"/>
+      <c r="M39" s="195" t="n"/>
+      <c r="N39" s="188" t="n"/>
+      <c r="O39" s="190" t="n"/>
+      <c r="P39" s="190" t="n"/>
+      <c r="Q39" s="190" t="n"/>
+      <c r="R39" s="191" t="n"/>
+      <c r="S39" s="191" t="n"/>
+      <c r="T39" s="188" t="n"/>
+      <c r="U39" s="192" t="n"/>
       <c r="V39" s="54" t="n"/>
       <c r="W39" s="55" t="n"/>
       <c r="X39" s="55" t="n"/>
@@ -40206,27 +40263,27 @@
       <c r="EM39" s="55" t="n"/>
     </row>
     <row r="40" collapsed="1" ht="14.25" customHeight="1" s="104">
-      <c r="A40" s="184" t="n"/>
-      <c r="B40" s="184" t="n"/>
-      <c r="C40" s="184" t="n"/>
-      <c r="D40" s="185" t="n"/>
-      <c r="E40" s="185" t="n"/>
-      <c r="F40" s="185" t="n"/>
-      <c r="G40" s="186" t="n"/>
-      <c r="H40" s="186" t="n"/>
-      <c r="I40" s="186" t="n"/>
-      <c r="J40" s="186" t="n"/>
-      <c r="K40" s="186" t="n"/>
-      <c r="L40" s="187" t="n"/>
-      <c r="M40" s="187" t="n"/>
-      <c r="N40" s="186" t="n"/>
-      <c r="O40" s="188" t="n"/>
-      <c r="P40" s="188" t="n"/>
-      <c r="Q40" s="188" t="n"/>
-      <c r="R40" s="189" t="n"/>
-      <c r="S40" s="189" t="n"/>
-      <c r="T40" s="186" t="n"/>
-      <c r="U40" s="190" t="n"/>
+      <c r="A40" s="186" t="n"/>
+      <c r="B40" s="186" t="n"/>
+      <c r="C40" s="186" t="n"/>
+      <c r="D40" s="187" t="n"/>
+      <c r="E40" s="187" t="n"/>
+      <c r="F40" s="187" t="n"/>
+      <c r="G40" s="188" t="n"/>
+      <c r="H40" s="188" t="n"/>
+      <c r="I40" s="188" t="n"/>
+      <c r="J40" s="188" t="n"/>
+      <c r="K40" s="188" t="n"/>
+      <c r="L40" s="189" t="n"/>
+      <c r="M40" s="189" t="n"/>
+      <c r="N40" s="188" t="n"/>
+      <c r="O40" s="190" t="n"/>
+      <c r="P40" s="190" t="n"/>
+      <c r="Q40" s="190" t="n"/>
+      <c r="R40" s="191" t="n"/>
+      <c r="S40" s="191" t="n"/>
+      <c r="T40" s="188" t="n"/>
+      <c r="U40" s="192" t="n"/>
       <c r="V40" s="54" t="n"/>
       <c r="W40" s="55" t="n"/>
       <c r="X40" s="55" t="n"/>
@@ -40351,27 +40408,27 @@
       <c r="EM40" s="55" t="n"/>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="104">
-      <c r="A41" s="184" t="n"/>
-      <c r="B41" s="184" t="n"/>
-      <c r="C41" s="184" t="n"/>
-      <c r="D41" s="185" t="n"/>
-      <c r="E41" s="185" t="n"/>
-      <c r="F41" s="185" t="n"/>
-      <c r="G41" s="186" t="n"/>
-      <c r="H41" s="187" t="n"/>
-      <c r="I41" s="186" t="n"/>
-      <c r="J41" s="186" t="n"/>
-      <c r="K41" s="186" t="n"/>
-      <c r="L41" s="187" t="n"/>
-      <c r="M41" s="187" t="n"/>
-      <c r="N41" s="186" t="n"/>
-      <c r="O41" s="188" t="n"/>
-      <c r="P41" s="188" t="n"/>
-      <c r="Q41" s="188" t="n"/>
-      <c r="R41" s="189" t="n"/>
-      <c r="S41" s="189" t="n"/>
-      <c r="T41" s="186" t="n"/>
-      <c r="U41" s="190" t="n"/>
+      <c r="A41" s="186" t="n"/>
+      <c r="B41" s="186" t="n"/>
+      <c r="C41" s="186" t="n"/>
+      <c r="D41" s="187" t="n"/>
+      <c r="E41" s="187" t="n"/>
+      <c r="F41" s="187" t="n"/>
+      <c r="G41" s="188" t="n"/>
+      <c r="H41" s="189" t="n"/>
+      <c r="I41" s="188" t="n"/>
+      <c r="J41" s="188" t="n"/>
+      <c r="K41" s="188" t="n"/>
+      <c r="L41" s="189" t="n"/>
+      <c r="M41" s="189" t="n"/>
+      <c r="N41" s="188" t="n"/>
+      <c r="O41" s="190" t="n"/>
+      <c r="P41" s="190" t="n"/>
+      <c r="Q41" s="190" t="n"/>
+      <c r="R41" s="191" t="n"/>
+      <c r="S41" s="191" t="n"/>
+      <c r="T41" s="188" t="n"/>
+      <c r="U41" s="192" t="n"/>
       <c r="V41" s="54" t="n"/>
       <c r="W41" s="55" t="n"/>
       <c r="X41" s="55" t="n"/>
@@ -40496,27 +40553,27 @@
       <c r="EM41" s="55" t="n"/>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="104">
-      <c r="A42" s="184" t="n"/>
-      <c r="B42" s="184" t="n"/>
-      <c r="C42" s="184" t="n"/>
-      <c r="D42" s="185" t="n"/>
-      <c r="E42" s="185" t="n"/>
-      <c r="F42" s="185" t="n"/>
-      <c r="G42" s="186" t="n"/>
-      <c r="H42" s="187" t="n"/>
-      <c r="I42" s="186" t="n"/>
-      <c r="J42" s="186" t="n"/>
-      <c r="K42" s="186" t="n"/>
-      <c r="L42" s="187" t="n"/>
-      <c r="M42" s="187" t="n"/>
-      <c r="N42" s="186" t="n"/>
-      <c r="O42" s="188" t="n"/>
-      <c r="P42" s="188" t="n"/>
-      <c r="Q42" s="188" t="n"/>
-      <c r="R42" s="189" t="n"/>
-      <c r="S42" s="189" t="n"/>
-      <c r="T42" s="186" t="n"/>
-      <c r="U42" s="190" t="n"/>
+      <c r="A42" s="186" t="n"/>
+      <c r="B42" s="186" t="n"/>
+      <c r="C42" s="186" t="n"/>
+      <c r="D42" s="187" t="n"/>
+      <c r="E42" s="187" t="n"/>
+      <c r="F42" s="187" t="n"/>
+      <c r="G42" s="188" t="n"/>
+      <c r="H42" s="189" t="n"/>
+      <c r="I42" s="188" t="n"/>
+      <c r="J42" s="188" t="n"/>
+      <c r="K42" s="188" t="n"/>
+      <c r="L42" s="189" t="n"/>
+      <c r="M42" s="189" t="n"/>
+      <c r="N42" s="188" t="n"/>
+      <c r="O42" s="190" t="n"/>
+      <c r="P42" s="190" t="n"/>
+      <c r="Q42" s="190" t="n"/>
+      <c r="R42" s="191" t="n"/>
+      <c r="S42" s="191" t="n"/>
+      <c r="T42" s="188" t="n"/>
+      <c r="U42" s="192" t="n"/>
       <c r="V42" s="54" t="n"/>
       <c r="W42" s="55" t="n"/>
       <c r="X42" s="55" t="n"/>
@@ -40641,27 +40698,27 @@
       <c r="EM42" s="55" t="n"/>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="104">
-      <c r="A43" s="184" t="n"/>
-      <c r="B43" s="184" t="n"/>
-      <c r="C43" s="184" t="n"/>
-      <c r="D43" s="185" t="n"/>
-      <c r="E43" s="185" t="n"/>
-      <c r="F43" s="185" t="n"/>
-      <c r="G43" s="186" t="n"/>
-      <c r="H43" s="186" t="n"/>
-      <c r="I43" s="186" t="n"/>
-      <c r="J43" s="186" t="n"/>
-      <c r="K43" s="186" t="n"/>
-      <c r="L43" s="187" t="n"/>
-      <c r="M43" s="187" t="n"/>
-      <c r="N43" s="186" t="n"/>
-      <c r="O43" s="188" t="n"/>
-      <c r="P43" s="188" t="n"/>
-      <c r="Q43" s="188" t="n"/>
-      <c r="R43" s="189" t="n"/>
-      <c r="S43" s="189" t="n"/>
-      <c r="T43" s="186" t="n"/>
-      <c r="U43" s="190" t="n"/>
+      <c r="A43" s="186" t="n"/>
+      <c r="B43" s="186" t="n"/>
+      <c r="C43" s="186" t="n"/>
+      <c r="D43" s="187" t="n"/>
+      <c r="E43" s="187" t="n"/>
+      <c r="F43" s="187" t="n"/>
+      <c r="G43" s="188" t="n"/>
+      <c r="H43" s="188" t="n"/>
+      <c r="I43" s="188" t="n"/>
+      <c r="J43" s="188" t="n"/>
+      <c r="K43" s="188" t="n"/>
+      <c r="L43" s="189" t="n"/>
+      <c r="M43" s="189" t="n"/>
+      <c r="N43" s="188" t="n"/>
+      <c r="O43" s="190" t="n"/>
+      <c r="P43" s="190" t="n"/>
+      <c r="Q43" s="190" t="n"/>
+      <c r="R43" s="191" t="n"/>
+      <c r="S43" s="191" t="n"/>
+      <c r="T43" s="188" t="n"/>
+      <c r="U43" s="192" t="n"/>
       <c r="V43" s="54" t="n"/>
       <c r="W43" s="55" t="n"/>
       <c r="X43" s="55" t="n"/>
@@ -40786,27 +40843,27 @@
       <c r="EM43" s="55" t="n"/>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="104">
-      <c r="A44" s="184" t="n"/>
-      <c r="B44" s="184" t="n"/>
-      <c r="C44" s="184" t="n"/>
-      <c r="D44" s="185" t="n"/>
-      <c r="E44" s="185" t="n"/>
-      <c r="F44" s="185" t="n"/>
-      <c r="G44" s="186" t="n"/>
-      <c r="H44" s="186" t="n"/>
-      <c r="I44" s="186" t="n"/>
-      <c r="J44" s="186" t="n"/>
-      <c r="K44" s="186" t="n"/>
-      <c r="L44" s="187" t="n"/>
-      <c r="M44" s="187" t="n"/>
-      <c r="N44" s="186" t="n"/>
-      <c r="O44" s="188" t="n"/>
-      <c r="P44" s="188" t="n"/>
-      <c r="Q44" s="188" t="n"/>
-      <c r="R44" s="189" t="n"/>
-      <c r="S44" s="189" t="n"/>
-      <c r="T44" s="186" t="n"/>
-      <c r="U44" s="190" t="n"/>
+      <c r="A44" s="186" t="n"/>
+      <c r="B44" s="186" t="n"/>
+      <c r="C44" s="186" t="n"/>
+      <c r="D44" s="187" t="n"/>
+      <c r="E44" s="187" t="n"/>
+      <c r="F44" s="187" t="n"/>
+      <c r="G44" s="188" t="n"/>
+      <c r="H44" s="188" t="n"/>
+      <c r="I44" s="188" t="n"/>
+      <c r="J44" s="188" t="n"/>
+      <c r="K44" s="188" t="n"/>
+      <c r="L44" s="189" t="n"/>
+      <c r="M44" s="189" t="n"/>
+      <c r="N44" s="188" t="n"/>
+      <c r="O44" s="190" t="n"/>
+      <c r="P44" s="190" t="n"/>
+      <c r="Q44" s="190" t="n"/>
+      <c r="R44" s="191" t="n"/>
+      <c r="S44" s="191" t="n"/>
+      <c r="T44" s="188" t="n"/>
+      <c r="U44" s="192" t="n"/>
       <c r="V44" s="54" t="n"/>
       <c r="W44" s="55" t="n"/>
       <c r="X44" s="55" t="n"/>
@@ -40931,27 +40988,27 @@
       <c r="EM44" s="55" t="n"/>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="104">
-      <c r="A45" s="184" t="n"/>
-      <c r="B45" s="184" t="n"/>
-      <c r="C45" s="184" t="n"/>
-      <c r="D45" s="185" t="n"/>
-      <c r="E45" s="185" t="n"/>
-      <c r="F45" s="185" t="n"/>
-      <c r="G45" s="186" t="n"/>
-      <c r="H45" s="186" t="n"/>
-      <c r="I45" s="186" t="n"/>
-      <c r="J45" s="186" t="n"/>
-      <c r="K45" s="186" t="n"/>
-      <c r="L45" s="187" t="n"/>
-      <c r="M45" s="187" t="n"/>
-      <c r="N45" s="186" t="n"/>
-      <c r="O45" s="188" t="n"/>
-      <c r="P45" s="188" t="n"/>
-      <c r="Q45" s="188" t="n"/>
-      <c r="R45" s="189" t="n"/>
-      <c r="S45" s="189" t="n"/>
-      <c r="T45" s="186" t="n"/>
-      <c r="U45" s="190" t="n"/>
+      <c r="A45" s="186" t="n"/>
+      <c r="B45" s="186" t="n"/>
+      <c r="C45" s="186" t="n"/>
+      <c r="D45" s="187" t="n"/>
+      <c r="E45" s="187" t="n"/>
+      <c r="F45" s="187" t="n"/>
+      <c r="G45" s="188" t="n"/>
+      <c r="H45" s="188" t="n"/>
+      <c r="I45" s="188" t="n"/>
+      <c r="J45" s="188" t="n"/>
+      <c r="K45" s="188" t="n"/>
+      <c r="L45" s="189" t="n"/>
+      <c r="M45" s="189" t="n"/>
+      <c r="N45" s="188" t="n"/>
+      <c r="O45" s="190" t="n"/>
+      <c r="P45" s="190" t="n"/>
+      <c r="Q45" s="190" t="n"/>
+      <c r="R45" s="191" t="n"/>
+      <c r="S45" s="191" t="n"/>
+      <c r="T45" s="188" t="n"/>
+      <c r="U45" s="192" t="n"/>
       <c r="V45" s="54" t="n"/>
       <c r="W45" s="55" t="n"/>
       <c r="X45" s="55" t="n"/>
@@ -41076,27 +41133,27 @@
       <c r="EM45" s="55" t="n"/>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="104">
-      <c r="A46" s="184" t="n"/>
-      <c r="B46" s="184" t="n"/>
-      <c r="C46" s="184" t="n"/>
-      <c r="D46" s="185" t="n"/>
-      <c r="E46" s="185" t="n"/>
-      <c r="F46" s="185" t="n"/>
-      <c r="G46" s="186" t="n"/>
-      <c r="H46" s="186" t="n"/>
-      <c r="I46" s="186" t="n"/>
-      <c r="J46" s="186" t="n"/>
-      <c r="K46" s="186" t="n"/>
-      <c r="L46" s="187" t="n"/>
-      <c r="M46" s="187" t="n"/>
-      <c r="N46" s="186" t="n"/>
-      <c r="O46" s="188" t="n"/>
-      <c r="P46" s="188" t="n"/>
-      <c r="Q46" s="188" t="n"/>
-      <c r="R46" s="189" t="n"/>
-      <c r="S46" s="189" t="n"/>
-      <c r="T46" s="186" t="n"/>
-      <c r="U46" s="190" t="n"/>
+      <c r="A46" s="186" t="n"/>
+      <c r="B46" s="186" t="n"/>
+      <c r="C46" s="186" t="n"/>
+      <c r="D46" s="187" t="n"/>
+      <c r="E46" s="187" t="n"/>
+      <c r="F46" s="187" t="n"/>
+      <c r="G46" s="188" t="n"/>
+      <c r="H46" s="188" t="n"/>
+      <c r="I46" s="188" t="n"/>
+      <c r="J46" s="188" t="n"/>
+      <c r="K46" s="188" t="n"/>
+      <c r="L46" s="189" t="n"/>
+      <c r="M46" s="189" t="n"/>
+      <c r="N46" s="188" t="n"/>
+      <c r="O46" s="190" t="n"/>
+      <c r="P46" s="190" t="n"/>
+      <c r="Q46" s="190" t="n"/>
+      <c r="R46" s="191" t="n"/>
+      <c r="S46" s="191" t="n"/>
+      <c r="T46" s="188" t="n"/>
+      <c r="U46" s="192" t="n"/>
       <c r="V46" s="54" t="n"/>
       <c r="W46" s="55" t="n"/>
       <c r="X46" s="55" t="n"/>
@@ -41221,27 +41278,27 @@
       <c r="EM46" s="55" t="n"/>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="104">
-      <c r="A47" s="184" t="n"/>
-      <c r="B47" s="184" t="n"/>
-      <c r="C47" s="184" t="n"/>
-      <c r="D47" s="185" t="n"/>
-      <c r="E47" s="185" t="n"/>
-      <c r="F47" s="185" t="n"/>
-      <c r="G47" s="186" t="n"/>
-      <c r="H47" s="186" t="n"/>
-      <c r="I47" s="186" t="n"/>
-      <c r="J47" s="186" t="n"/>
-      <c r="K47" s="186" t="n"/>
-      <c r="L47" s="187" t="n"/>
-      <c r="M47" s="187" t="n"/>
-      <c r="N47" s="186" t="n"/>
-      <c r="O47" s="188" t="n"/>
-      <c r="P47" s="188" t="n"/>
-      <c r="Q47" s="188" t="n"/>
-      <c r="R47" s="189" t="n"/>
-      <c r="S47" s="189" t="n"/>
-      <c r="T47" s="186" t="n"/>
-      <c r="U47" s="190" t="n"/>
+      <c r="A47" s="186" t="n"/>
+      <c r="B47" s="186" t="n"/>
+      <c r="C47" s="186" t="n"/>
+      <c r="D47" s="187" t="n"/>
+      <c r="E47" s="187" t="n"/>
+      <c r="F47" s="187" t="n"/>
+      <c r="G47" s="188" t="n"/>
+      <c r="H47" s="188" t="n"/>
+      <c r="I47" s="188" t="n"/>
+      <c r="J47" s="188" t="n"/>
+      <c r="K47" s="188" t="n"/>
+      <c r="L47" s="189" t="n"/>
+      <c r="M47" s="189" t="n"/>
+      <c r="N47" s="188" t="n"/>
+      <c r="O47" s="190" t="n"/>
+      <c r="P47" s="190" t="n"/>
+      <c r="Q47" s="190" t="n"/>
+      <c r="R47" s="191" t="n"/>
+      <c r="S47" s="191" t="n"/>
+      <c r="T47" s="188" t="n"/>
+      <c r="U47" s="192" t="n"/>
       <c r="V47" s="54" t="n"/>
       <c r="W47" s="55" t="n"/>
       <c r="X47" s="55" t="n"/>
@@ -41366,27 +41423,27 @@
       <c r="EM47" s="55" t="n"/>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="104">
-      <c r="A48" s="184" t="n"/>
-      <c r="B48" s="184" t="n"/>
-      <c r="C48" s="184" t="n"/>
-      <c r="D48" s="185" t="n"/>
-      <c r="E48" s="185" t="n"/>
-      <c r="F48" s="185" t="n"/>
-      <c r="G48" s="186" t="n"/>
-      <c r="H48" s="186" t="n"/>
-      <c r="I48" s="186" t="n"/>
-      <c r="J48" s="186" t="n"/>
-      <c r="K48" s="186" t="n"/>
-      <c r="L48" s="187" t="n"/>
-      <c r="M48" s="187" t="n"/>
-      <c r="N48" s="186" t="n"/>
-      <c r="O48" s="188" t="n"/>
-      <c r="P48" s="188" t="n"/>
-      <c r="Q48" s="188" t="n"/>
-      <c r="R48" s="189" t="n"/>
-      <c r="S48" s="189" t="n"/>
-      <c r="T48" s="186" t="n"/>
-      <c r="U48" s="190" t="n"/>
+      <c r="A48" s="186" t="n"/>
+      <c r="B48" s="186" t="n"/>
+      <c r="C48" s="186" t="n"/>
+      <c r="D48" s="187" t="n"/>
+      <c r="E48" s="187" t="n"/>
+      <c r="F48" s="187" t="n"/>
+      <c r="G48" s="188" t="n"/>
+      <c r="H48" s="188" t="n"/>
+      <c r="I48" s="188" t="n"/>
+      <c r="J48" s="188" t="n"/>
+      <c r="K48" s="188" t="n"/>
+      <c r="L48" s="189" t="n"/>
+      <c r="M48" s="189" t="n"/>
+      <c r="N48" s="188" t="n"/>
+      <c r="O48" s="190" t="n"/>
+      <c r="P48" s="190" t="n"/>
+      <c r="Q48" s="190" t="n"/>
+      <c r="R48" s="191" t="n"/>
+      <c r="S48" s="191" t="n"/>
+      <c r="T48" s="188" t="n"/>
+      <c r="U48" s="192" t="n"/>
       <c r="V48" s="54" t="n"/>
       <c r="W48" s="55" t="n"/>
       <c r="X48" s="55" t="n"/>
@@ -41511,27 +41568,27 @@
       <c r="EM48" s="55" t="n"/>
     </row>
     <row r="49" ht="14.25" customHeight="1" s="104">
-      <c r="A49" s="184" t="n"/>
-      <c r="B49" s="184" t="n"/>
-      <c r="C49" s="184" t="n"/>
-      <c r="D49" s="185" t="n"/>
-      <c r="E49" s="185" t="n"/>
-      <c r="F49" s="185" t="n"/>
-      <c r="G49" s="186" t="n"/>
-      <c r="H49" s="186" t="n"/>
-      <c r="I49" s="186" t="n"/>
-      <c r="J49" s="186" t="n"/>
-      <c r="K49" s="186" t="n"/>
-      <c r="L49" s="187" t="n"/>
-      <c r="M49" s="187" t="n"/>
-      <c r="N49" s="186" t="n"/>
-      <c r="O49" s="188" t="n"/>
-      <c r="P49" s="188" t="n"/>
-      <c r="Q49" s="188" t="n"/>
-      <c r="R49" s="189" t="n"/>
-      <c r="S49" s="189" t="n"/>
-      <c r="T49" s="186" t="n"/>
-      <c r="U49" s="190" t="n"/>
+      <c r="A49" s="186" t="n"/>
+      <c r="B49" s="186" t="n"/>
+      <c r="C49" s="186" t="n"/>
+      <c r="D49" s="187" t="n"/>
+      <c r="E49" s="187" t="n"/>
+      <c r="F49" s="187" t="n"/>
+      <c r="G49" s="188" t="n"/>
+      <c r="H49" s="188" t="n"/>
+      <c r="I49" s="188" t="n"/>
+      <c r="J49" s="188" t="n"/>
+      <c r="K49" s="188" t="n"/>
+      <c r="L49" s="189" t="n"/>
+      <c r="M49" s="189" t="n"/>
+      <c r="N49" s="188" t="n"/>
+      <c r="O49" s="190" t="n"/>
+      <c r="P49" s="190" t="n"/>
+      <c r="Q49" s="190" t="n"/>
+      <c r="R49" s="191" t="n"/>
+      <c r="S49" s="191" t="n"/>
+      <c r="T49" s="188" t="n"/>
+      <c r="U49" s="192" t="n"/>
       <c r="V49" s="54" t="n"/>
       <c r="W49" s="55" t="n"/>
       <c r="X49" s="55" t="n"/>
@@ -41656,27 +41713,27 @@
       <c r="EM49" s="55" t="n"/>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="104">
-      <c r="A50" s="184" t="n"/>
-      <c r="B50" s="184" t="n"/>
-      <c r="C50" s="184" t="n"/>
-      <c r="D50" s="185" t="n"/>
-      <c r="E50" s="185" t="n"/>
-      <c r="F50" s="185" t="n"/>
-      <c r="G50" s="186" t="n"/>
-      <c r="H50" s="186" t="n"/>
-      <c r="I50" s="186" t="n"/>
-      <c r="J50" s="186" t="n"/>
-      <c r="K50" s="186" t="n"/>
-      <c r="L50" s="187" t="n"/>
-      <c r="M50" s="187" t="n"/>
-      <c r="N50" s="186" t="n"/>
-      <c r="O50" s="188" t="n"/>
-      <c r="P50" s="188" t="n"/>
-      <c r="Q50" s="188" t="n"/>
-      <c r="R50" s="189" t="n"/>
-      <c r="S50" s="189" t="n"/>
-      <c r="T50" s="186" t="n"/>
-      <c r="U50" s="190" t="n"/>
+      <c r="A50" s="186" t="n"/>
+      <c r="B50" s="186" t="n"/>
+      <c r="C50" s="186" t="n"/>
+      <c r="D50" s="187" t="n"/>
+      <c r="E50" s="187" t="n"/>
+      <c r="F50" s="187" t="n"/>
+      <c r="G50" s="188" t="n"/>
+      <c r="H50" s="188" t="n"/>
+      <c r="I50" s="188" t="n"/>
+      <c r="J50" s="188" t="n"/>
+      <c r="K50" s="188" t="n"/>
+      <c r="L50" s="189" t="n"/>
+      <c r="M50" s="189" t="n"/>
+      <c r="N50" s="188" t="n"/>
+      <c r="O50" s="190" t="n"/>
+      <c r="P50" s="190" t="n"/>
+      <c r="Q50" s="190" t="n"/>
+      <c r="R50" s="191" t="n"/>
+      <c r="S50" s="191" t="n"/>
+      <c r="T50" s="188" t="n"/>
+      <c r="U50" s="192" t="n"/>
       <c r="V50" s="54" t="n"/>
       <c r="W50" s="55" t="n"/>
       <c r="X50" s="55" t="n"/>
@@ -41801,27 +41858,27 @@
       <c r="EM50" s="55" t="n"/>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="104">
-      <c r="A51" s="184" t="n"/>
-      <c r="B51" s="184" t="n"/>
-      <c r="C51" s="184" t="n"/>
-      <c r="D51" s="185" t="n"/>
-      <c r="E51" s="185" t="n"/>
-      <c r="F51" s="185" t="n"/>
-      <c r="G51" s="186" t="n"/>
-      <c r="H51" s="186" t="n"/>
-      <c r="I51" s="186" t="n"/>
-      <c r="J51" s="186" t="n"/>
-      <c r="K51" s="186" t="n"/>
-      <c r="L51" s="187" t="n"/>
-      <c r="M51" s="187" t="n"/>
-      <c r="N51" s="186" t="n"/>
-      <c r="O51" s="188" t="n"/>
-      <c r="P51" s="188" t="n"/>
-      <c r="Q51" s="188" t="n"/>
-      <c r="R51" s="189" t="n"/>
-      <c r="S51" s="189" t="n"/>
-      <c r="T51" s="186" t="n"/>
-      <c r="U51" s="190" t="n"/>
+      <c r="A51" s="186" t="n"/>
+      <c r="B51" s="186" t="n"/>
+      <c r="C51" s="186" t="n"/>
+      <c r="D51" s="187" t="n"/>
+      <c r="E51" s="187" t="n"/>
+      <c r="F51" s="187" t="n"/>
+      <c r="G51" s="188" t="n"/>
+      <c r="H51" s="188" t="n"/>
+      <c r="I51" s="188" t="n"/>
+      <c r="J51" s="188" t="n"/>
+      <c r="K51" s="188" t="n"/>
+      <c r="L51" s="189" t="n"/>
+      <c r="M51" s="189" t="n"/>
+      <c r="N51" s="188" t="n"/>
+      <c r="O51" s="190" t="n"/>
+      <c r="P51" s="190" t="n"/>
+      <c r="Q51" s="190" t="n"/>
+      <c r="R51" s="191" t="n"/>
+      <c r="S51" s="191" t="n"/>
+      <c r="T51" s="188" t="n"/>
+      <c r="U51" s="192" t="n"/>
       <c r="V51" s="54" t="n"/>
       <c r="W51" s="55" t="n"/>
       <c r="X51" s="55" t="n"/>
@@ -41946,27 +42003,27 @@
       <c r="EM51" s="55" t="n"/>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="104">
-      <c r="A52" s="184" t="n"/>
-      <c r="B52" s="184" t="n"/>
-      <c r="C52" s="184" t="n"/>
-      <c r="D52" s="185" t="n"/>
-      <c r="E52" s="185" t="n"/>
-      <c r="F52" s="185" t="n"/>
-      <c r="G52" s="186" t="n"/>
-      <c r="H52" s="186" t="n"/>
-      <c r="I52" s="186" t="n"/>
-      <c r="J52" s="186" t="n"/>
-      <c r="K52" s="186" t="n"/>
-      <c r="L52" s="187" t="n"/>
-      <c r="M52" s="187" t="n"/>
-      <c r="N52" s="186" t="n"/>
-      <c r="O52" s="188" t="n"/>
-      <c r="P52" s="188" t="n"/>
-      <c r="Q52" s="188" t="n"/>
-      <c r="R52" s="189" t="n"/>
-      <c r="S52" s="189" t="n"/>
-      <c r="T52" s="186" t="n"/>
-      <c r="U52" s="190" t="n"/>
+      <c r="A52" s="186" t="n"/>
+      <c r="B52" s="186" t="n"/>
+      <c r="C52" s="186" t="n"/>
+      <c r="D52" s="187" t="n"/>
+      <c r="E52" s="187" t="n"/>
+      <c r="F52" s="187" t="n"/>
+      <c r="G52" s="188" t="n"/>
+      <c r="H52" s="188" t="n"/>
+      <c r="I52" s="188" t="n"/>
+      <c r="J52" s="188" t="n"/>
+      <c r="K52" s="188" t="n"/>
+      <c r="L52" s="189" t="n"/>
+      <c r="M52" s="189" t="n"/>
+      <c r="N52" s="188" t="n"/>
+      <c r="O52" s="190" t="n"/>
+      <c r="P52" s="190" t="n"/>
+      <c r="Q52" s="190" t="n"/>
+      <c r="R52" s="191" t="n"/>
+      <c r="S52" s="191" t="n"/>
+      <c r="T52" s="188" t="n"/>
+      <c r="U52" s="192" t="n"/>
       <c r="V52" s="54" t="n"/>
       <c r="W52" s="55" t="n"/>
       <c r="X52" s="55" t="n"/>
@@ -42091,27 +42148,27 @@
       <c r="EM52" s="55" t="n"/>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="104">
-      <c r="A53" s="184" t="n"/>
-      <c r="B53" s="184" t="n"/>
-      <c r="C53" s="184" t="n"/>
-      <c r="D53" s="185" t="n"/>
-      <c r="E53" s="185" t="n"/>
-      <c r="F53" s="185" t="n"/>
-      <c r="G53" s="186" t="n"/>
-      <c r="H53" s="186" t="n"/>
-      <c r="I53" s="186" t="n"/>
-      <c r="J53" s="186" t="n"/>
-      <c r="K53" s="186" t="n"/>
-      <c r="L53" s="187" t="n"/>
-      <c r="M53" s="187" t="n"/>
-      <c r="N53" s="186" t="n"/>
-      <c r="O53" s="188" t="n"/>
-      <c r="P53" s="188" t="n"/>
-      <c r="Q53" s="188" t="n"/>
-      <c r="R53" s="189" t="n"/>
-      <c r="S53" s="189" t="n"/>
-      <c r="T53" s="186" t="n"/>
-      <c r="U53" s="190" t="n"/>
+      <c r="A53" s="186" t="n"/>
+      <c r="B53" s="186" t="n"/>
+      <c r="C53" s="186" t="n"/>
+      <c r="D53" s="187" t="n"/>
+      <c r="E53" s="187" t="n"/>
+      <c r="F53" s="187" t="n"/>
+      <c r="G53" s="188" t="n"/>
+      <c r="H53" s="188" t="n"/>
+      <c r="I53" s="188" t="n"/>
+      <c r="J53" s="188" t="n"/>
+      <c r="K53" s="188" t="n"/>
+      <c r="L53" s="189" t="n"/>
+      <c r="M53" s="189" t="n"/>
+      <c r="N53" s="188" t="n"/>
+      <c r="O53" s="190" t="n"/>
+      <c r="P53" s="190" t="n"/>
+      <c r="Q53" s="190" t="n"/>
+      <c r="R53" s="191" t="n"/>
+      <c r="S53" s="191" t="n"/>
+      <c r="T53" s="188" t="n"/>
+      <c r="U53" s="192" t="n"/>
       <c r="V53" s="54" t="n"/>
       <c r="W53" s="55" t="n"/>
       <c r="X53" s="55" t="n"/>
@@ -42236,27 +42293,27 @@
       <c r="EM53" s="55" t="n"/>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="104">
-      <c r="A54" s="184" t="n"/>
-      <c r="B54" s="184" t="n"/>
-      <c r="C54" s="184" t="n"/>
-      <c r="D54" s="185" t="n"/>
-      <c r="E54" s="185" t="n"/>
-      <c r="F54" s="185" t="n"/>
-      <c r="G54" s="186" t="n"/>
-      <c r="H54" s="186" t="n"/>
-      <c r="I54" s="186" t="n"/>
-      <c r="J54" s="186" t="n"/>
-      <c r="K54" s="186" t="n"/>
-      <c r="L54" s="187" t="n"/>
-      <c r="M54" s="187" t="n"/>
-      <c r="N54" s="186" t="n"/>
-      <c r="O54" s="188" t="n"/>
-      <c r="P54" s="188" t="n"/>
-      <c r="Q54" s="188" t="n"/>
-      <c r="R54" s="189" t="n"/>
-      <c r="S54" s="189" t="n"/>
-      <c r="T54" s="186" t="n"/>
-      <c r="U54" s="190" t="n"/>
+      <c r="A54" s="186" t="n"/>
+      <c r="B54" s="186" t="n"/>
+      <c r="C54" s="186" t="n"/>
+      <c r="D54" s="187" t="n"/>
+      <c r="E54" s="187" t="n"/>
+      <c r="F54" s="187" t="n"/>
+      <c r="G54" s="188" t="n"/>
+      <c r="H54" s="188" t="n"/>
+      <c r="I54" s="188" t="n"/>
+      <c r="J54" s="188" t="n"/>
+      <c r="K54" s="188" t="n"/>
+      <c r="L54" s="189" t="n"/>
+      <c r="M54" s="189" t="n"/>
+      <c r="N54" s="188" t="n"/>
+      <c r="O54" s="190" t="n"/>
+      <c r="P54" s="190" t="n"/>
+      <c r="Q54" s="190" t="n"/>
+      <c r="R54" s="191" t="n"/>
+      <c r="S54" s="191" t="n"/>
+      <c r="T54" s="188" t="n"/>
+      <c r="U54" s="192" t="n"/>
       <c r="V54" s="54" t="n"/>
       <c r="W54" s="55" t="n"/>
       <c r="X54" s="55" t="n"/>
@@ -42381,27 +42438,27 @@
       <c r="EM54" s="55" t="n"/>
     </row>
     <row r="55" ht="14.25" customHeight="1" s="104">
-      <c r="A55" s="184" t="n"/>
-      <c r="B55" s="184" t="n"/>
-      <c r="C55" s="184" t="n"/>
-      <c r="D55" s="185" t="n"/>
-      <c r="E55" s="185" t="n"/>
-      <c r="F55" s="185" t="n"/>
-      <c r="G55" s="186" t="n"/>
-      <c r="H55" s="186" t="n"/>
-      <c r="I55" s="186" t="n"/>
-      <c r="J55" s="186" t="n"/>
-      <c r="K55" s="186" t="n"/>
-      <c r="L55" s="187" t="n"/>
-      <c r="M55" s="187" t="n"/>
-      <c r="N55" s="186" t="n"/>
-      <c r="O55" s="188" t="n"/>
-      <c r="P55" s="188" t="n"/>
-      <c r="Q55" s="188" t="n"/>
-      <c r="R55" s="189" t="n"/>
-      <c r="S55" s="189" t="n"/>
-      <c r="T55" s="186" t="n"/>
-      <c r="U55" s="190" t="n"/>
+      <c r="A55" s="186" t="n"/>
+      <c r="B55" s="186" t="n"/>
+      <c r="C55" s="186" t="n"/>
+      <c r="D55" s="187" t="n"/>
+      <c r="E55" s="187" t="n"/>
+      <c r="F55" s="187" t="n"/>
+      <c r="G55" s="188" t="n"/>
+      <c r="H55" s="188" t="n"/>
+      <c r="I55" s="188" t="n"/>
+      <c r="J55" s="188" t="n"/>
+      <c r="K55" s="188" t="n"/>
+      <c r="L55" s="189" t="n"/>
+      <c r="M55" s="189" t="n"/>
+      <c r="N55" s="188" t="n"/>
+      <c r="O55" s="190" t="n"/>
+      <c r="P55" s="190" t="n"/>
+      <c r="Q55" s="190" t="n"/>
+      <c r="R55" s="191" t="n"/>
+      <c r="S55" s="191" t="n"/>
+      <c r="T55" s="188" t="n"/>
+      <c r="U55" s="192" t="n"/>
       <c r="V55" s="54" t="n"/>
       <c r="W55" s="55" t="n"/>
       <c r="X55" s="55" t="n"/>
@@ -42526,27 +42583,27 @@
       <c r="EM55" s="55" t="n"/>
     </row>
     <row r="56" ht="14.25" customHeight="1" s="104">
-      <c r="A56" s="184" t="n"/>
-      <c r="B56" s="184" t="n"/>
-      <c r="C56" s="184" t="n"/>
-      <c r="D56" s="185" t="n"/>
-      <c r="E56" s="185" t="n"/>
-      <c r="F56" s="185" t="n"/>
-      <c r="G56" s="186" t="n"/>
-      <c r="H56" s="186" t="n"/>
-      <c r="I56" s="186" t="n"/>
-      <c r="J56" s="186" t="n"/>
-      <c r="K56" s="186" t="n"/>
-      <c r="L56" s="187" t="n"/>
-      <c r="M56" s="187" t="n"/>
-      <c r="N56" s="186" t="n"/>
-      <c r="O56" s="188" t="n"/>
-      <c r="P56" s="188" t="n"/>
-      <c r="Q56" s="188" t="n"/>
-      <c r="R56" s="189" t="n"/>
-      <c r="S56" s="189" t="n"/>
-      <c r="T56" s="186" t="n"/>
-      <c r="U56" s="190" t="n"/>
+      <c r="A56" s="186" t="n"/>
+      <c r="B56" s="186" t="n"/>
+      <c r="C56" s="186" t="n"/>
+      <c r="D56" s="187" t="n"/>
+      <c r="E56" s="187" t="n"/>
+      <c r="F56" s="187" t="n"/>
+      <c r="G56" s="188" t="n"/>
+      <c r="H56" s="188" t="n"/>
+      <c r="I56" s="188" t="n"/>
+      <c r="J56" s="188" t="n"/>
+      <c r="K56" s="188" t="n"/>
+      <c r="L56" s="189" t="n"/>
+      <c r="M56" s="189" t="n"/>
+      <c r="N56" s="188" t="n"/>
+      <c r="O56" s="190" t="n"/>
+      <c r="P56" s="190" t="n"/>
+      <c r="Q56" s="190" t="n"/>
+      <c r="R56" s="191" t="n"/>
+      <c r="S56" s="191" t="n"/>
+      <c r="T56" s="188" t="n"/>
+      <c r="U56" s="192" t="n"/>
       <c r="V56" s="54" t="n"/>
       <c r="W56" s="55" t="n"/>
       <c r="X56" s="55" t="n"/>
@@ -42671,27 +42728,27 @@
       <c r="EM56" s="55" t="n"/>
     </row>
     <row r="57" ht="14.25" customHeight="1" s="104">
-      <c r="A57" s="184" t="n"/>
-      <c r="B57" s="184" t="n"/>
-      <c r="C57" s="184" t="n"/>
-      <c r="D57" s="185" t="n"/>
-      <c r="E57" s="185" t="n"/>
-      <c r="F57" s="185" t="n"/>
-      <c r="G57" s="186" t="n"/>
-      <c r="H57" s="186" t="n"/>
-      <c r="I57" s="186" t="n"/>
-      <c r="J57" s="186" t="n"/>
-      <c r="K57" s="186" t="n"/>
-      <c r="L57" s="187" t="n"/>
-      <c r="M57" s="187" t="n"/>
-      <c r="N57" s="186" t="n"/>
-      <c r="O57" s="188" t="n"/>
-      <c r="P57" s="188" t="n"/>
-      <c r="Q57" s="188" t="n"/>
-      <c r="R57" s="189" t="n"/>
-      <c r="S57" s="189" t="n"/>
-      <c r="T57" s="186" t="n"/>
-      <c r="U57" s="190" t="n"/>
+      <c r="A57" s="186" t="n"/>
+      <c r="B57" s="186" t="n"/>
+      <c r="C57" s="186" t="n"/>
+      <c r="D57" s="187" t="n"/>
+      <c r="E57" s="187" t="n"/>
+      <c r="F57" s="187" t="n"/>
+      <c r="G57" s="188" t="n"/>
+      <c r="H57" s="188" t="n"/>
+      <c r="I57" s="188" t="n"/>
+      <c r="J57" s="188" t="n"/>
+      <c r="K57" s="188" t="n"/>
+      <c r="L57" s="189" t="n"/>
+      <c r="M57" s="189" t="n"/>
+      <c r="N57" s="188" t="n"/>
+      <c r="O57" s="190" t="n"/>
+      <c r="P57" s="190" t="n"/>
+      <c r="Q57" s="190" t="n"/>
+      <c r="R57" s="191" t="n"/>
+      <c r="S57" s="191" t="n"/>
+      <c r="T57" s="188" t="n"/>
+      <c r="U57" s="192" t="n"/>
       <c r="V57" s="54" t="n"/>
       <c r="W57" s="55" t="n"/>
       <c r="X57" s="55" t="n"/>
@@ -42816,27 +42873,27 @@
       <c r="EM57" s="55" t="n"/>
     </row>
     <row r="58" ht="14.25" customHeight="1" s="104">
-      <c r="A58" s="184" t="n"/>
-      <c r="B58" s="184" t="n"/>
-      <c r="C58" s="184" t="n"/>
-      <c r="D58" s="185" t="n"/>
-      <c r="E58" s="185" t="n"/>
-      <c r="F58" s="185" t="n"/>
-      <c r="G58" s="186" t="n"/>
-      <c r="H58" s="186" t="n"/>
-      <c r="I58" s="186" t="n"/>
-      <c r="J58" s="186" t="n"/>
-      <c r="K58" s="186" t="n"/>
-      <c r="L58" s="187" t="n"/>
-      <c r="M58" s="187" t="n"/>
-      <c r="N58" s="186" t="n"/>
-      <c r="O58" s="188" t="n"/>
-      <c r="P58" s="188" t="n"/>
-      <c r="Q58" s="188" t="n"/>
-      <c r="R58" s="189" t="n"/>
-      <c r="S58" s="189" t="n"/>
-      <c r="T58" s="186" t="n"/>
-      <c r="U58" s="190" t="n"/>
+      <c r="A58" s="186" t="n"/>
+      <c r="B58" s="186" t="n"/>
+      <c r="C58" s="186" t="n"/>
+      <c r="D58" s="187" t="n"/>
+      <c r="E58" s="187" t="n"/>
+      <c r="F58" s="187" t="n"/>
+      <c r="G58" s="188" t="n"/>
+      <c r="H58" s="188" t="n"/>
+      <c r="I58" s="188" t="n"/>
+      <c r="J58" s="188" t="n"/>
+      <c r="K58" s="188" t="n"/>
+      <c r="L58" s="189" t="n"/>
+      <c r="M58" s="189" t="n"/>
+      <c r="N58" s="188" t="n"/>
+      <c r="O58" s="190" t="n"/>
+      <c r="P58" s="190" t="n"/>
+      <c r="Q58" s="190" t="n"/>
+      <c r="R58" s="191" t="n"/>
+      <c r="S58" s="191" t="n"/>
+      <c r="T58" s="188" t="n"/>
+      <c r="U58" s="192" t="n"/>
       <c r="V58" s="54" t="n"/>
       <c r="W58" s="55" t="n"/>
       <c r="X58" s="55" t="n"/>
@@ -42961,27 +43018,27 @@
       <c r="EM58" s="55" t="n"/>
     </row>
     <row r="59" ht="14.25" customHeight="1" s="104">
-      <c r="A59" s="184" t="n"/>
-      <c r="B59" s="184" t="n"/>
-      <c r="C59" s="184" t="n"/>
-      <c r="D59" s="185" t="n"/>
-      <c r="E59" s="185" t="n"/>
-      <c r="F59" s="185" t="n"/>
-      <c r="G59" s="186" t="n"/>
-      <c r="H59" s="186" t="n"/>
-      <c r="I59" s="186" t="n"/>
-      <c r="J59" s="186" t="n"/>
-      <c r="K59" s="186" t="n"/>
-      <c r="L59" s="187" t="n"/>
-      <c r="M59" s="187" t="n"/>
-      <c r="N59" s="186" t="n"/>
-      <c r="O59" s="188" t="n"/>
-      <c r="P59" s="188" t="n"/>
-      <c r="Q59" s="188" t="n"/>
-      <c r="R59" s="189" t="n"/>
-      <c r="S59" s="189" t="n"/>
-      <c r="T59" s="186" t="n"/>
-      <c r="U59" s="190" t="n"/>
+      <c r="A59" s="186" t="n"/>
+      <c r="B59" s="186" t="n"/>
+      <c r="C59" s="186" t="n"/>
+      <c r="D59" s="187" t="n"/>
+      <c r="E59" s="187" t="n"/>
+      <c r="F59" s="187" t="n"/>
+      <c r="G59" s="188" t="n"/>
+      <c r="H59" s="188" t="n"/>
+      <c r="I59" s="188" t="n"/>
+      <c r="J59" s="188" t="n"/>
+      <c r="K59" s="188" t="n"/>
+      <c r="L59" s="189" t="n"/>
+      <c r="M59" s="189" t="n"/>
+      <c r="N59" s="188" t="n"/>
+      <c r="O59" s="190" t="n"/>
+      <c r="P59" s="190" t="n"/>
+      <c r="Q59" s="190" t="n"/>
+      <c r="R59" s="191" t="n"/>
+      <c r="S59" s="191" t="n"/>
+      <c r="T59" s="188" t="n"/>
+      <c r="U59" s="192" t="n"/>
       <c r="V59" s="54" t="n"/>
       <c r="W59" s="55" t="n"/>
       <c r="X59" s="55" t="n"/>
@@ -43106,27 +43163,27 @@
       <c r="EM59" s="55" t="n"/>
     </row>
     <row r="60" ht="14.25" customHeight="1" s="104">
-      <c r="A60" s="184" t="n"/>
-      <c r="B60" s="184" t="n"/>
-      <c r="C60" s="184" t="n"/>
-      <c r="D60" s="185" t="n"/>
-      <c r="E60" s="185" t="n"/>
-      <c r="F60" s="185" t="n"/>
-      <c r="G60" s="186" t="n"/>
-      <c r="H60" s="186" t="n"/>
-      <c r="I60" s="186" t="n"/>
-      <c r="J60" s="186" t="n"/>
-      <c r="K60" s="186" t="n"/>
-      <c r="L60" s="187" t="n"/>
-      <c r="M60" s="187" t="n"/>
-      <c r="N60" s="186" t="n"/>
-      <c r="O60" s="188" t="n"/>
-      <c r="P60" s="188" t="n"/>
-      <c r="Q60" s="188" t="n"/>
-      <c r="R60" s="189" t="n"/>
-      <c r="S60" s="189" t="n"/>
-      <c r="T60" s="186" t="n"/>
-      <c r="U60" s="190" t="n"/>
+      <c r="A60" s="186" t="n"/>
+      <c r="B60" s="186" t="n"/>
+      <c r="C60" s="186" t="n"/>
+      <c r="D60" s="187" t="n"/>
+      <c r="E60" s="187" t="n"/>
+      <c r="F60" s="187" t="n"/>
+      <c r="G60" s="188" t="n"/>
+      <c r="H60" s="188" t="n"/>
+      <c r="I60" s="188" t="n"/>
+      <c r="J60" s="188" t="n"/>
+      <c r="K60" s="188" t="n"/>
+      <c r="L60" s="189" t="n"/>
+      <c r="M60" s="189" t="n"/>
+      <c r="N60" s="188" t="n"/>
+      <c r="O60" s="190" t="n"/>
+      <c r="P60" s="190" t="n"/>
+      <c r="Q60" s="190" t="n"/>
+      <c r="R60" s="191" t="n"/>
+      <c r="S60" s="191" t="n"/>
+      <c r="T60" s="188" t="n"/>
+      <c r="U60" s="192" t="n"/>
       <c r="V60" s="54" t="n"/>
       <c r="W60" s="55" t="n"/>
       <c r="X60" s="55" t="n"/>
@@ -43251,27 +43308,27 @@
       <c r="EM60" s="55" t="n"/>
     </row>
     <row r="61" ht="14.25" customHeight="1" s="104">
-      <c r="A61" s="184" t="n"/>
-      <c r="B61" s="184" t="n"/>
-      <c r="C61" s="184" t="n"/>
-      <c r="D61" s="185" t="n"/>
-      <c r="E61" s="185" t="n"/>
-      <c r="F61" s="185" t="n"/>
-      <c r="G61" s="186" t="n"/>
-      <c r="H61" s="186" t="n"/>
-      <c r="I61" s="186" t="n"/>
-      <c r="J61" s="186" t="n"/>
-      <c r="K61" s="186" t="n"/>
-      <c r="L61" s="187" t="n"/>
-      <c r="M61" s="187" t="n"/>
-      <c r="N61" s="186" t="n"/>
-      <c r="O61" s="188" t="n"/>
-      <c r="P61" s="188" t="n"/>
-      <c r="Q61" s="188" t="n"/>
-      <c r="R61" s="189" t="n"/>
-      <c r="S61" s="189" t="n"/>
-      <c r="T61" s="186" t="n"/>
-      <c r="U61" s="190" t="n"/>
+      <c r="A61" s="186" t="n"/>
+      <c r="B61" s="186" t="n"/>
+      <c r="C61" s="186" t="n"/>
+      <c r="D61" s="187" t="n"/>
+      <c r="E61" s="187" t="n"/>
+      <c r="F61" s="187" t="n"/>
+      <c r="G61" s="188" t="n"/>
+      <c r="H61" s="188" t="n"/>
+      <c r="I61" s="188" t="n"/>
+      <c r="J61" s="188" t="n"/>
+      <c r="K61" s="188" t="n"/>
+      <c r="L61" s="189" t="n"/>
+      <c r="M61" s="189" t="n"/>
+      <c r="N61" s="188" t="n"/>
+      <c r="O61" s="190" t="n"/>
+      <c r="P61" s="190" t="n"/>
+      <c r="Q61" s="190" t="n"/>
+      <c r="R61" s="191" t="n"/>
+      <c r="S61" s="191" t="n"/>
+      <c r="T61" s="188" t="n"/>
+      <c r="U61" s="192" t="n"/>
       <c r="V61" s="54" t="n"/>
       <c r="W61" s="55" t="n"/>
       <c r="X61" s="55" t="n"/>
@@ -43396,27 +43453,27 @@
       <c r="EM61" s="55" t="n"/>
     </row>
     <row r="62" ht="14.25" customHeight="1" s="104">
-      <c r="A62" s="184" t="n"/>
-      <c r="B62" s="184" t="n"/>
-      <c r="C62" s="184" t="n"/>
-      <c r="D62" s="185" t="n"/>
-      <c r="E62" s="185" t="n"/>
-      <c r="F62" s="185" t="n"/>
-      <c r="G62" s="186" t="n"/>
-      <c r="H62" s="186" t="n"/>
-      <c r="I62" s="186" t="n"/>
-      <c r="J62" s="186" t="n"/>
-      <c r="K62" s="186" t="n"/>
-      <c r="L62" s="187" t="n"/>
-      <c r="M62" s="187" t="n"/>
-      <c r="N62" s="186" t="n"/>
-      <c r="O62" s="188" t="n"/>
-      <c r="P62" s="188" t="n"/>
-      <c r="Q62" s="188" t="n"/>
-      <c r="R62" s="189" t="n"/>
-      <c r="S62" s="189" t="n"/>
-      <c r="T62" s="186" t="n"/>
-      <c r="U62" s="190" t="n"/>
+      <c r="A62" s="186" t="n"/>
+      <c r="B62" s="186" t="n"/>
+      <c r="C62" s="186" t="n"/>
+      <c r="D62" s="187" t="n"/>
+      <c r="E62" s="187" t="n"/>
+      <c r="F62" s="187" t="n"/>
+      <c r="G62" s="188" t="n"/>
+      <c r="H62" s="188" t="n"/>
+      <c r="I62" s="188" t="n"/>
+      <c r="J62" s="188" t="n"/>
+      <c r="K62" s="188" t="n"/>
+      <c r="L62" s="189" t="n"/>
+      <c r="M62" s="189" t="n"/>
+      <c r="N62" s="188" t="n"/>
+      <c r="O62" s="190" t="n"/>
+      <c r="P62" s="190" t="n"/>
+      <c r="Q62" s="190" t="n"/>
+      <c r="R62" s="191" t="n"/>
+      <c r="S62" s="191" t="n"/>
+      <c r="T62" s="188" t="n"/>
+      <c r="U62" s="192" t="n"/>
       <c r="V62" s="54" t="n"/>
       <c r="W62" s="55" t="n"/>
       <c r="X62" s="55" t="n"/>
@@ -43541,27 +43598,27 @@
       <c r="EM62" s="55" t="n"/>
     </row>
     <row r="63" ht="14.25" customHeight="1" s="104">
-      <c r="A63" s="184" t="n"/>
-      <c r="B63" s="184" t="n"/>
-      <c r="C63" s="184" t="n"/>
-      <c r="D63" s="185" t="n"/>
-      <c r="E63" s="185" t="n"/>
-      <c r="F63" s="185" t="n"/>
-      <c r="G63" s="186" t="n"/>
-      <c r="H63" s="186" t="n"/>
-      <c r="I63" s="186" t="n"/>
-      <c r="J63" s="186" t="n"/>
-      <c r="K63" s="186" t="n"/>
-      <c r="L63" s="187" t="n"/>
-      <c r="M63" s="187" t="n"/>
-      <c r="N63" s="186" t="n"/>
-      <c r="O63" s="188" t="n"/>
-      <c r="P63" s="188" t="n"/>
-      <c r="Q63" s="188" t="n"/>
-      <c r="R63" s="189" t="n"/>
-      <c r="S63" s="189" t="n"/>
-      <c r="T63" s="186" t="n"/>
-      <c r="U63" s="190" t="n"/>
+      <c r="A63" s="186" t="n"/>
+      <c r="B63" s="186" t="n"/>
+      <c r="C63" s="186" t="n"/>
+      <c r="D63" s="187" t="n"/>
+      <c r="E63" s="187" t="n"/>
+      <c r="F63" s="187" t="n"/>
+      <c r="G63" s="188" t="n"/>
+      <c r="H63" s="188" t="n"/>
+      <c r="I63" s="188" t="n"/>
+      <c r="J63" s="188" t="n"/>
+      <c r="K63" s="188" t="n"/>
+      <c r="L63" s="189" t="n"/>
+      <c r="M63" s="189" t="n"/>
+      <c r="N63" s="188" t="n"/>
+      <c r="O63" s="190" t="n"/>
+      <c r="P63" s="190" t="n"/>
+      <c r="Q63" s="190" t="n"/>
+      <c r="R63" s="191" t="n"/>
+      <c r="S63" s="191" t="n"/>
+      <c r="T63" s="188" t="n"/>
+      <c r="U63" s="192" t="n"/>
       <c r="V63" s="54" t="n"/>
       <c r="W63" s="55" t="n"/>
       <c r="X63" s="55" t="n"/>
@@ -43686,27 +43743,27 @@
       <c r="EM63" s="55" t="n"/>
     </row>
     <row r="64" ht="14.25" customHeight="1" s="104">
-      <c r="A64" s="184" t="n"/>
-      <c r="B64" s="184" t="n"/>
-      <c r="C64" s="184" t="n"/>
-      <c r="D64" s="185" t="n"/>
-      <c r="E64" s="185" t="n"/>
-      <c r="F64" s="185" t="n"/>
-      <c r="G64" s="186" t="n"/>
-      <c r="H64" s="186" t="n"/>
-      <c r="I64" s="186" t="n"/>
-      <c r="J64" s="186" t="n"/>
-      <c r="K64" s="186" t="n"/>
-      <c r="L64" s="187" t="n"/>
-      <c r="M64" s="187" t="n"/>
-      <c r="N64" s="186" t="n"/>
-      <c r="O64" s="188" t="n"/>
-      <c r="P64" s="188" t="n"/>
-      <c r="Q64" s="188" t="n"/>
-      <c r="R64" s="189" t="n"/>
-      <c r="S64" s="189" t="n"/>
-      <c r="T64" s="186" t="n"/>
-      <c r="U64" s="190" t="n"/>
+      <c r="A64" s="186" t="n"/>
+      <c r="B64" s="186" t="n"/>
+      <c r="C64" s="186" t="n"/>
+      <c r="D64" s="187" t="n"/>
+      <c r="E64" s="187" t="n"/>
+      <c r="F64" s="187" t="n"/>
+      <c r="G64" s="188" t="n"/>
+      <c r="H64" s="188" t="n"/>
+      <c r="I64" s="188" t="n"/>
+      <c r="J64" s="188" t="n"/>
+      <c r="K64" s="188" t="n"/>
+      <c r="L64" s="189" t="n"/>
+      <c r="M64" s="189" t="n"/>
+      <c r="N64" s="188" t="n"/>
+      <c r="O64" s="190" t="n"/>
+      <c r="P64" s="190" t="n"/>
+      <c r="Q64" s="190" t="n"/>
+      <c r="R64" s="191" t="n"/>
+      <c r="S64" s="191" t="n"/>
+      <c r="T64" s="188" t="n"/>
+      <c r="U64" s="192" t="n"/>
       <c r="V64" s="54" t="n"/>
       <c r="W64" s="55" t="n"/>
       <c r="X64" s="55" t="n"/>
@@ -43831,27 +43888,27 @@
       <c r="EM64" s="55" t="n"/>
     </row>
     <row r="65" ht="14.25" customHeight="1" s="104">
-      <c r="A65" s="184" t="n"/>
-      <c r="B65" s="184" t="n"/>
-      <c r="C65" s="184" t="n"/>
-      <c r="D65" s="185" t="n"/>
-      <c r="E65" s="185" t="n"/>
-      <c r="F65" s="185" t="n"/>
-      <c r="G65" s="186" t="n"/>
-      <c r="H65" s="186" t="n"/>
-      <c r="I65" s="186" t="n"/>
-      <c r="J65" s="186" t="n"/>
-      <c r="K65" s="186" t="n"/>
-      <c r="L65" s="187" t="n"/>
-      <c r="M65" s="187" t="n"/>
-      <c r="N65" s="186" t="n"/>
-      <c r="O65" s="188" t="n"/>
-      <c r="P65" s="188" t="n"/>
-      <c r="Q65" s="188" t="n"/>
-      <c r="R65" s="189" t="n"/>
-      <c r="S65" s="189" t="n"/>
-      <c r="T65" s="186" t="n"/>
-      <c r="U65" s="190" t="n"/>
+      <c r="A65" s="186" t="n"/>
+      <c r="B65" s="186" t="n"/>
+      <c r="C65" s="186" t="n"/>
+      <c r="D65" s="187" t="n"/>
+      <c r="E65" s="187" t="n"/>
+      <c r="F65" s="187" t="n"/>
+      <c r="G65" s="188" t="n"/>
+      <c r="H65" s="188" t="n"/>
+      <c r="I65" s="188" t="n"/>
+      <c r="J65" s="188" t="n"/>
+      <c r="K65" s="188" t="n"/>
+      <c r="L65" s="189" t="n"/>
+      <c r="M65" s="189" t="n"/>
+      <c r="N65" s="188" t="n"/>
+      <c r="O65" s="190" t="n"/>
+      <c r="P65" s="190" t="n"/>
+      <c r="Q65" s="190" t="n"/>
+      <c r="R65" s="191" t="n"/>
+      <c r="S65" s="191" t="n"/>
+      <c r="T65" s="188" t="n"/>
+      <c r="U65" s="192" t="n"/>
       <c r="V65" s="54" t="n"/>
       <c r="W65" s="55" t="n"/>
       <c r="X65" s="55" t="n"/>
@@ -43976,27 +44033,27 @@
       <c r="EM65" s="55" t="n"/>
     </row>
     <row r="66" ht="14.25" customHeight="1" s="104">
-      <c r="A66" s="184" t="n"/>
-      <c r="B66" s="184" t="n"/>
-      <c r="C66" s="184" t="n"/>
-      <c r="D66" s="185" t="n"/>
-      <c r="E66" s="185" t="n"/>
-      <c r="F66" s="185" t="n"/>
-      <c r="G66" s="186" t="n"/>
-      <c r="H66" s="186" t="n"/>
-      <c r="I66" s="186" t="n"/>
-      <c r="J66" s="186" t="n"/>
-      <c r="K66" s="186" t="n"/>
-      <c r="L66" s="187" t="n"/>
-      <c r="M66" s="187" t="n"/>
-      <c r="N66" s="186" t="n"/>
-      <c r="O66" s="188" t="n"/>
-      <c r="P66" s="188" t="n"/>
-      <c r="Q66" s="188" t="n"/>
-      <c r="R66" s="189" t="n"/>
-      <c r="S66" s="189" t="n"/>
-      <c r="T66" s="186" t="n"/>
-      <c r="U66" s="190" t="n"/>
+      <c r="A66" s="186" t="n"/>
+      <c r="B66" s="186" t="n"/>
+      <c r="C66" s="186" t="n"/>
+      <c r="D66" s="187" t="n"/>
+      <c r="E66" s="187" t="n"/>
+      <c r="F66" s="187" t="n"/>
+      <c r="G66" s="188" t="n"/>
+      <c r="H66" s="188" t="n"/>
+      <c r="I66" s="188" t="n"/>
+      <c r="J66" s="188" t="n"/>
+      <c r="K66" s="188" t="n"/>
+      <c r="L66" s="189" t="n"/>
+      <c r="M66" s="189" t="n"/>
+      <c r="N66" s="188" t="n"/>
+      <c r="O66" s="190" t="n"/>
+      <c r="P66" s="190" t="n"/>
+      <c r="Q66" s="190" t="n"/>
+      <c r="R66" s="191" t="n"/>
+      <c r="S66" s="191" t="n"/>
+      <c r="T66" s="188" t="n"/>
+      <c r="U66" s="192" t="n"/>
       <c r="V66" s="54" t="n"/>
       <c r="W66" s="55" t="n"/>
       <c r="X66" s="55" t="n"/>
@@ -45216,7 +45273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45230,12 +45287,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="195" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B1" s="195" t="inlineStr">
+      <c r="B1" s="139" t="inlineStr">
         <is>
           <t>명칭</t>
         </is>

--- a/skills/wbs-generator/template/WBS_template.xlsx
+++ b/skills/wbs-generator/template/WBS_template.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="표지" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="사용안내" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="요약" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="WBS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="공휴일" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="요약" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="WBS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="공휴일" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="HOLIDAYS">#REF!</definedName>
-    <definedName name="HOLIDAYS" localSheetId="3">#REF!</definedName>
+    <definedName name="HOLIDAYS" localSheetId="4">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -29819,7 +29820,7 @@
     <row r="4">
       <c r="B4" s="135" t="inlineStr">
         <is>
-          <t>프로젝트 작업분해구조(WBS)입니다. 시트 구성: 표지 · 사용안내 · 요약 · WBS · 공휴일</t>
+          <t>프로젝트 작업분해구조(WBS)입니다. 시트 구성: 표지 · 사용안내 · 개정이력 · 요약 · WBS · 공휴일</t>
         </is>
       </c>
     </row>
@@ -29977,6 +29978,55 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="104" min="1" max="1"/>
+    <col width="14" customWidth="1" style="104" min="2" max="2"/>
+    <col width="12" customWidth="1" style="104" min="3" max="3"/>
+    <col width="55" customWidth="1" style="104" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="138" t="inlineStr">
+        <is>
+          <t>개정이력</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="139" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="B3" s="139" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="C3" s="139" t="inlineStr">
+        <is>
+          <t>작성자</t>
+        </is>
+      </c>
+      <c r="D3" s="139" t="inlineStr">
+        <is>
+          <t>변경 내용</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30031,7 +30081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45273,7 +45323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
